--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="16034" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="19482" uniqueCount="840">
   <si>
     <t>Year</t>
   </si>
@@ -2417,6 +2417,123 @@
   </si>
   <si>
     <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wensday_10447\fracture\Fracture_20260422_203122_1_2.csv</t>
+  </si>
+  <si>
+    <t>wednesday_10442</t>
+  </si>
+  <si>
+    <t>wednesday_10443</t>
+  </si>
+  <si>
+    <t>wednesday_10447</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\compression\COMPRESSION_20260422_163210_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\compression\COMPRESSION_20260422_163210_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\tension\TENSION_20260422_164517_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\tension\TENSION_20260422_164517_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\fracture\Fracture_20260422_170352_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\fracture\Fracture_20260422_170352_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\fracture\Fracture_20260422_170352_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\fracture\Fracture_20260422_170352_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\fracture\Fracture_20260422_170352_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\fracture\Fracture_20260422_170352_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\fracture\Fracture_20260422_170352_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10442\fracture\Fracture_20260422_170352_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\compression\COMPRESSION_20260422_133560_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\compression\COMPRESSION_20260422_133560_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\tension\TENSION_20260422_135940_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\tension\TENSION_20260422_135940_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\fracture\Fracture_20260422_141258_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\fracture\Fracture_20260422_141258_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\fracture\Fracture_20260422_141258_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\fracture\Fracture_20260422_141258_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\fracture\Fracture_20260422_141258_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\fracture\Fracture_20260422_141258_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\fracture\Fracture_20260422_141258_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10443\fracture\Fracture_20260422_141258_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\compression\COMPRESSION_20260422_193341_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\compression\COMPRESSION_20260422_194554_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\tension\TENSION_20260422_195602_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\tension\TENSION_20260422_200525_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\fracture\Fracture_20260422_202647_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\fracture\Fracture_20260422_201627_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\fracture\Fracture_20260422_202917_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\fracture\Fracture_20260422_201454_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\fracture\Fracture_20260422_201902_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\fracture\Fracture_20260422_202534_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\fracture\Fracture_20260422_202154_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2026_organized\batch2\wednesday\wednesday_10447\fracture\Fracture_20260422_203122_1_2.csv</t>
   </si>
 </sst>
 </file>
@@ -2468,12 +2585,12 @@
     <col min="1" max="1" width="14.08984375" customWidth="true"/>
     <col min="2" max="2" width="6.54296875" customWidth="true"/>
     <col min="3" max="3" width="10.36328125" customWidth="true"/>
-    <col min="4" max="4" width="14.26953125" customWidth="true"/>
+    <col min="4" max="4" width="16.36328125" customWidth="true"/>
     <col min="5" max="5" width="11.81640625" customWidth="true"/>
     <col min="6" max="6" width="11.90625" customWidth="true"/>
     <col min="7" max="7" width="7.90625" customWidth="true"/>
     <col min="8" max="8" width="36.26953125" customWidth="true"/>
-    <col min="9" max="9" width="165.453125" customWidth="true"/>
+    <col min="9" max="9" width="167.54296875" customWidth="true"/>
     <col min="10" max="10" width="9.453125" customWidth="true"/>
   </cols>
   <sheetData>
@@ -10340,13 +10457,13 @@
         <v>40</v>
       </c>
       <c r="H246" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J246" s="0">
-        <v>431.4341</v>
+        <v>429.82010000000002</v>
       </c>
     </row>
     <row r="247">
@@ -10372,13 +10489,13 @@
         <v>40</v>
       </c>
       <c r="H247" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J247" s="0">
-        <v>429.82010000000002</v>
+        <v>421.38249999999999</v>
       </c>
     </row>
     <row r="248">
@@ -10404,13 +10521,13 @@
         <v>40</v>
       </c>
       <c r="H248" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="J248" s="0">
-        <v>421.38249999999999</v>
+        <v>417.74880000000002</v>
       </c>
     </row>
     <row r="249">
@@ -10436,13 +10553,13 @@
         <v>40</v>
       </c>
       <c r="H249" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="J249" s="0">
-        <v>417.74880000000002</v>
+        <v>393.11059999999998</v>
       </c>
     </row>
     <row r="250">
@@ -10468,13 +10585,13 @@
         <v>41</v>
       </c>
       <c r="H250" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="J250" s="0">
-        <v>393.11059999999998</v>
+        <v>392.10489999999999</v>
       </c>
     </row>
     <row r="251">
@@ -10500,13 +10617,13 @@
         <v>41</v>
       </c>
       <c r="H251" s="0" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J251" s="0">
-        <v>392.10489999999999</v>
+        <v>387.5043</v>
       </c>
     </row>
     <row r="252">
@@ -10532,13 +10649,13 @@
         <v>41</v>
       </c>
       <c r="H252" s="0" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="J252" s="0">
-        <v>387.5043</v>
+        <v>215.23259999999999</v>
       </c>
     </row>
     <row r="253">
@@ -10549,28 +10666,28 @@
         <v>4</v>
       </c>
       <c r="C253" s="0" t="s">
-        <v>7</v>
+        <v>655</v>
       </c>
       <c r="D253" s="0" t="s">
-        <v>24</v>
+        <v>801</v>
       </c>
       <c r="E253" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G253" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H253" s="0" t="s">
-        <v>256</v>
+        <v>693</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>557</v>
+        <v>804</v>
       </c>
       <c r="J253" s="0">
-        <v>215.23259999999999</v>
+        <v>6179.7012000000004</v>
       </c>
     </row>
     <row r="254">
@@ -10584,25 +10701,25 @@
         <v>655</v>
       </c>
       <c r="D254" s="0" t="s">
-        <v>656</v>
+        <v>801</v>
       </c>
       <c r="E254" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F254" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G254" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H254" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>765</v>
+        <v>805</v>
       </c>
       <c r="J254" s="0">
-        <v>6179.7012000000004</v>
+        <v>2590.0304999999999</v>
       </c>
     </row>
     <row r="255">
@@ -10616,25 +10733,25 @@
         <v>655</v>
       </c>
       <c r="D255" s="0" t="s">
-        <v>656</v>
+        <v>801</v>
       </c>
       <c r="E255" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G255" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H255" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>766</v>
+        <v>806</v>
       </c>
       <c r="J255" s="0">
-        <v>2590.0304999999999</v>
+        <v>1052.7577000000001</v>
       </c>
     </row>
     <row r="256">
@@ -10648,25 +10765,25 @@
         <v>655</v>
       </c>
       <c r="D256" s="0" t="s">
-        <v>656</v>
+        <v>801</v>
       </c>
       <c r="E256" s="0" t="s">
         <v>28</v>
       </c>
       <c r="F256" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G256" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H256" s="0" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>767</v>
+        <v>807</v>
       </c>
       <c r="J256" s="0">
-        <v>1052.7577000000001</v>
+        <v>663.33749999999998</v>
       </c>
     </row>
     <row r="257">
@@ -10680,25 +10797,25 @@
         <v>655</v>
       </c>
       <c r="D257" s="0" t="s">
-        <v>656</v>
+        <v>801</v>
       </c>
       <c r="E257" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G257" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H257" s="0" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>768</v>
+        <v>808</v>
       </c>
       <c r="J257" s="0">
-        <v>663.33749999999998</v>
+        <v>506.81569999999999</v>
       </c>
     </row>
     <row r="258">
@@ -10712,25 +10829,25 @@
         <v>655</v>
       </c>
       <c r="D258" s="0" t="s">
-        <v>656</v>
+        <v>801</v>
       </c>
       <c r="E258" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G258" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H258" s="0" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>769</v>
+        <v>809</v>
       </c>
       <c r="J258" s="0">
-        <v>506.81569999999999</v>
+        <v>408.8279</v>
       </c>
     </row>
     <row r="259">
@@ -10744,25 +10861,25 @@
         <v>655</v>
       </c>
       <c r="D259" s="0" t="s">
-        <v>656</v>
+        <v>801</v>
       </c>
       <c r="E259" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F259" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G259" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H259" s="0" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>770</v>
+        <v>810</v>
       </c>
       <c r="J259" s="0">
-        <v>408.8279</v>
+        <v>402.4606</v>
       </c>
     </row>
     <row r="260">
@@ -10776,25 +10893,25 @@
         <v>655</v>
       </c>
       <c r="D260" s="0" t="s">
-        <v>656</v>
+        <v>801</v>
       </c>
       <c r="E260" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F260" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G260" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H260" s="0" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>771</v>
+        <v>811</v>
       </c>
       <c r="J260" s="0">
-        <v>402.4606</v>
+        <v>395.95499999999999</v>
       </c>
     </row>
     <row r="261">
@@ -10808,25 +10925,25 @@
         <v>655</v>
       </c>
       <c r="D261" s="0" t="s">
-        <v>656</v>
+        <v>801</v>
       </c>
       <c r="E261" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F261" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G261" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H261" s="0" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>772</v>
+        <v>812</v>
       </c>
       <c r="J261" s="0">
-        <v>395.95499999999999</v>
+        <v>384.18630000000002</v>
       </c>
     </row>
     <row r="262">
@@ -10840,25 +10957,25 @@
         <v>655</v>
       </c>
       <c r="D262" s="0" t="s">
-        <v>656</v>
+        <v>801</v>
       </c>
       <c r="E262" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F262" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G262" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H262" s="0" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>773</v>
+        <v>813</v>
       </c>
       <c r="J262" s="0">
-        <v>384.18630000000002</v>
+        <v>337.53550000000001</v>
       </c>
     </row>
     <row r="263">
@@ -10872,25 +10989,25 @@
         <v>655</v>
       </c>
       <c r="D263" s="0" t="s">
-        <v>656</v>
+        <v>801</v>
       </c>
       <c r="E263" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F263" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G263" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H263" s="0" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>774</v>
+        <v>814</v>
       </c>
       <c r="J263" s="0">
-        <v>337.53550000000001</v>
+        <v>304.91230000000002</v>
       </c>
     </row>
     <row r="264">
@@ -10904,25 +11021,25 @@
         <v>655</v>
       </c>
       <c r="D264" s="0" t="s">
-        <v>656</v>
+        <v>801</v>
       </c>
       <c r="E264" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F264" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G264" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H264" s="0" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>775</v>
+        <v>815</v>
       </c>
       <c r="J264" s="0">
-        <v>304.91230000000002</v>
+        <v>125.54000000000001</v>
       </c>
     </row>
     <row r="265">
@@ -10936,25 +11053,25 @@
         <v>655</v>
       </c>
       <c r="D265" s="0" t="s">
-        <v>656</v>
+        <v>802</v>
       </c>
       <c r="E265" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F265" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G265" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H265" s="0" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>776</v>
+        <v>816</v>
       </c>
       <c r="J265" s="0">
-        <v>125.54000000000001</v>
+        <v>5385.1138000000001</v>
       </c>
     </row>
     <row r="266">
@@ -10968,25 +11085,25 @@
         <v>655</v>
       </c>
       <c r="D266" s="0" t="s">
-        <v>657</v>
+        <v>802</v>
       </c>
       <c r="E266" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F266" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G266" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H266" s="0" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>777</v>
+        <v>817</v>
       </c>
       <c r="J266" s="0">
-        <v>5385.1138000000001</v>
+        <v>2843.9126000000001</v>
       </c>
     </row>
     <row r="267">
@@ -11000,25 +11117,25 @@
         <v>655</v>
       </c>
       <c r="D267" s="0" t="s">
-        <v>657</v>
+        <v>802</v>
       </c>
       <c r="E267" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F267" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G267" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H267" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>778</v>
+        <v>818</v>
       </c>
       <c r="J267" s="0">
-        <v>2843.9126000000001</v>
+        <v>710.74549999999999</v>
       </c>
     </row>
     <row r="268">
@@ -11032,25 +11149,25 @@
         <v>655</v>
       </c>
       <c r="D268" s="0" t="s">
-        <v>657</v>
+        <v>802</v>
       </c>
       <c r="E268" s="0" t="s">
         <v>28</v>
       </c>
       <c r="F268" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G268" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H268" s="0" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>779</v>
+        <v>819</v>
       </c>
       <c r="J268" s="0">
-        <v>710.74549999999999</v>
+        <v>550.2423</v>
       </c>
     </row>
     <row r="269">
@@ -11064,25 +11181,25 @@
         <v>655</v>
       </c>
       <c r="D269" s="0" t="s">
-        <v>657</v>
+        <v>802</v>
       </c>
       <c r="E269" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F269" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G269" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H269" s="0" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>780</v>
+        <v>820</v>
       </c>
       <c r="J269" s="0">
-        <v>550.2423</v>
+        <v>438.92590000000001</v>
       </c>
     </row>
     <row r="270">
@@ -11096,25 +11213,25 @@
         <v>655</v>
       </c>
       <c r="D270" s="0" t="s">
-        <v>657</v>
+        <v>802</v>
       </c>
       <c r="E270" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F270" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G270" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H270" s="0" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>781</v>
+        <v>821</v>
       </c>
       <c r="J270" s="0">
-        <v>438.92590000000001</v>
+        <v>423.42290000000003</v>
       </c>
     </row>
     <row r="271">
@@ -11128,25 +11245,25 @@
         <v>655</v>
       </c>
       <c r="D271" s="0" t="s">
-        <v>657</v>
+        <v>802</v>
       </c>
       <c r="E271" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F271" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G271" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H271" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>782</v>
+        <v>822</v>
       </c>
       <c r="J271" s="0">
-        <v>423.42290000000003</v>
+        <v>403.89089999999999</v>
       </c>
     </row>
     <row r="272">
@@ -11160,25 +11277,25 @@
         <v>655</v>
       </c>
       <c r="D272" s="0" t="s">
-        <v>657</v>
+        <v>802</v>
       </c>
       <c r="E272" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F272" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G272" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H272" s="0" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>783</v>
+        <v>823</v>
       </c>
       <c r="J272" s="0">
-        <v>403.89089999999999</v>
+        <v>391.21699999999999</v>
       </c>
     </row>
     <row r="273">
@@ -11192,25 +11309,25 @@
         <v>655</v>
       </c>
       <c r="D273" s="0" t="s">
-        <v>657</v>
+        <v>802</v>
       </c>
       <c r="E273" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F273" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G273" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H273" s="0" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>784</v>
+        <v>824</v>
       </c>
       <c r="J273" s="0">
-        <v>391.21699999999999</v>
+        <v>383.9436</v>
       </c>
     </row>
     <row r="274">
@@ -11224,25 +11341,25 @@
         <v>655</v>
       </c>
       <c r="D274" s="0" t="s">
-        <v>657</v>
+        <v>802</v>
       </c>
       <c r="E274" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F274" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G274" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H274" s="0" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>785</v>
+        <v>825</v>
       </c>
       <c r="J274" s="0">
-        <v>383.9436</v>
+        <v>312.447</v>
       </c>
     </row>
     <row r="275">
@@ -11256,25 +11373,25 @@
         <v>655</v>
       </c>
       <c r="D275" s="0" t="s">
-        <v>657</v>
+        <v>802</v>
       </c>
       <c r="E275" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F275" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G275" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H275" s="0" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>786</v>
+        <v>826</v>
       </c>
       <c r="J275" s="0">
-        <v>312.447</v>
+        <v>309.3852</v>
       </c>
     </row>
     <row r="276">
@@ -11288,25 +11405,25 @@
         <v>655</v>
       </c>
       <c r="D276" s="0" t="s">
-        <v>657</v>
+        <v>802</v>
       </c>
       <c r="E276" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F276" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G276" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H276" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>787</v>
+        <v>827</v>
       </c>
       <c r="J276" s="0">
-        <v>309.3852</v>
+        <v>235.6891</v>
       </c>
     </row>
     <row r="277">
@@ -11320,25 +11437,25 @@
         <v>655</v>
       </c>
       <c r="D277" s="0" t="s">
-        <v>657</v>
+        <v>803</v>
       </c>
       <c r="E277" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F277" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G277" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H277" s="0" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>788</v>
+        <v>828</v>
       </c>
       <c r="J277" s="0">
-        <v>235.6891</v>
+        <v>6293.9867999999997</v>
       </c>
     </row>
     <row r="278">
@@ -11352,25 +11469,25 @@
         <v>655</v>
       </c>
       <c r="D278" s="0" t="s">
-        <v>658</v>
+        <v>803</v>
       </c>
       <c r="E278" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F278" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G278" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H278" s="0" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>789</v>
+        <v>829</v>
       </c>
       <c r="J278" s="0">
-        <v>6293.9867999999997</v>
+        <v>5358.5902999999999</v>
       </c>
     </row>
     <row r="279">
@@ -11384,25 +11501,25 @@
         <v>655</v>
       </c>
       <c r="D279" s="0" t="s">
-        <v>658</v>
+        <v>803</v>
       </c>
       <c r="E279" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G279" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H279" s="0" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>790</v>
+        <v>830</v>
       </c>
       <c r="J279" s="0">
-        <v>5358.5902999999999</v>
+        <v>577.04179999999997</v>
       </c>
     </row>
     <row r="280">
@@ -11416,25 +11533,25 @@
         <v>655</v>
       </c>
       <c r="D280" s="0" t="s">
-        <v>658</v>
+        <v>803</v>
       </c>
       <c r="E280" s="0" t="s">
         <v>28</v>
       </c>
       <c r="F280" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G280" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H280" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>791</v>
+        <v>831</v>
       </c>
       <c r="J280" s="0">
-        <v>577.04179999999997</v>
+        <v>518.29719999999998</v>
       </c>
     </row>
     <row r="281">
@@ -11448,25 +11565,25 @@
         <v>655</v>
       </c>
       <c r="D281" s="0" t="s">
-        <v>658</v>
+        <v>803</v>
       </c>
       <c r="E281" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F281" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G281" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>792</v>
+        <v>832</v>
       </c>
       <c r="J281" s="0">
-        <v>518.29719999999998</v>
+        <v>427.73379999999997</v>
       </c>
     </row>
     <row r="282">
@@ -11480,25 +11597,25 @@
         <v>655</v>
       </c>
       <c r="D282" s="0" t="s">
-        <v>658</v>
+        <v>803</v>
       </c>
       <c r="E282" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F282" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G282" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H282" s="0" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>793</v>
+        <v>833</v>
       </c>
       <c r="J282" s="0">
-        <v>427.73379999999997</v>
+        <v>404.26459999999997</v>
       </c>
     </row>
     <row r="283">
@@ -11512,25 +11629,25 @@
         <v>655</v>
       </c>
       <c r="D283" s="0" t="s">
-        <v>658</v>
+        <v>803</v>
       </c>
       <c r="E283" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F283" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G283" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H283" s="0" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>794</v>
+        <v>834</v>
       </c>
       <c r="J283" s="0">
-        <v>404.26459999999997</v>
+        <v>398.51589999999999</v>
       </c>
     </row>
     <row r="284">
@@ -11544,25 +11661,25 @@
         <v>655</v>
       </c>
       <c r="D284" s="0" t="s">
-        <v>658</v>
+        <v>803</v>
       </c>
       <c r="E284" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F284" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G284" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H284" s="0" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>795</v>
+        <v>835</v>
       </c>
       <c r="J284" s="0">
-        <v>398.51589999999999</v>
+        <v>392.9486</v>
       </c>
     </row>
     <row r="285">
@@ -11576,25 +11693,25 @@
         <v>655</v>
       </c>
       <c r="D285" s="0" t="s">
-        <v>658</v>
+        <v>803</v>
       </c>
       <c r="E285" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F285" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G285" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H285" s="0" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>796</v>
+        <v>836</v>
       </c>
       <c r="J285" s="0">
-        <v>392.9486</v>
+        <v>382.86340000000001</v>
       </c>
     </row>
     <row r="286">
@@ -11608,25 +11725,25 @@
         <v>655</v>
       </c>
       <c r="D286" s="0" t="s">
-        <v>658</v>
+        <v>803</v>
       </c>
       <c r="E286" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F286" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G286" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H286" s="0" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>797</v>
+        <v>837</v>
       </c>
       <c r="J286" s="0">
-        <v>382.86340000000001</v>
+        <v>368.97640000000001</v>
       </c>
     </row>
     <row r="287">
@@ -11640,25 +11757,25 @@
         <v>655</v>
       </c>
       <c r="D287" s="0" t="s">
-        <v>658</v>
+        <v>803</v>
       </c>
       <c r="E287" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F287" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G287" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H287" s="0" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>798</v>
+        <v>838</v>
       </c>
       <c r="J287" s="0">
-        <v>368.97640000000001</v>
+        <v>347.17689999999999</v>
       </c>
     </row>
     <row r="288">
@@ -11672,25 +11789,25 @@
         <v>655</v>
       </c>
       <c r="D288" s="0" t="s">
-        <v>658</v>
+        <v>803</v>
       </c>
       <c r="E288" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F288" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G288" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H288" s="0" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>799</v>
+        <v>839</v>
       </c>
       <c r="J288" s="0">
-        <v>347.17689999999999</v>
+        <v>328.54599999999999</v>
       </c>
     </row>
     <row r="289">
@@ -11701,28 +11818,28 @@
         <v>4</v>
       </c>
       <c r="C289" s="0" t="s">
-        <v>655</v>
+        <v>8</v>
       </c>
       <c r="D289" s="0" t="s">
-        <v>658</v>
+        <v>15</v>
       </c>
       <c r="E289" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F289" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G289" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H289" s="0" t="s">
-        <v>728</v>
+        <v>257</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>800</v>
+        <v>558</v>
       </c>
       <c r="J289" s="0">
-        <v>328.54599999999999</v>
+        <v>5568.125</v>
       </c>
     </row>
     <row r="290">
@@ -11742,19 +11859,19 @@
         <v>27</v>
       </c>
       <c r="F290" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G290" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H290" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="J290" s="0">
-        <v>5568.125</v>
+        <v>2316.6012999999998</v>
       </c>
     </row>
     <row r="291">
@@ -11771,22 +11888,22 @@
         <v>15</v>
       </c>
       <c r="E291" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F291" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G291" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H291" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J291" s="0">
-        <v>2316.6012999999998</v>
+        <v>504.78460000000001</v>
       </c>
     </row>
     <row r="292">
@@ -11806,19 +11923,19 @@
         <v>28</v>
       </c>
       <c r="F292" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G292" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H292" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="J292" s="0">
-        <v>504.78460000000001</v>
+        <v>445.50999999999999</v>
       </c>
     </row>
     <row r="293">
@@ -11835,22 +11952,22 @@
         <v>15</v>
       </c>
       <c r="E293" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F293" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G293" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H293" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="J293" s="0">
-        <v>445.50999999999999</v>
+        <v>401.56920000000002</v>
       </c>
     </row>
     <row r="294">
@@ -11870,19 +11987,19 @@
         <v>29</v>
       </c>
       <c r="F294" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G294" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H294" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="J294" s="0">
-        <v>401.56920000000002</v>
+        <v>392.42399999999998</v>
       </c>
     </row>
     <row r="295">
@@ -11902,19 +12019,19 @@
         <v>29</v>
       </c>
       <c r="F295" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G295" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H295" s="0" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="J295" s="0">
-        <v>392.42399999999998</v>
+        <v>368.18880000000001</v>
       </c>
     </row>
     <row r="296">
@@ -11934,19 +12051,19 @@
         <v>29</v>
       </c>
       <c r="F296" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G296" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H296" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="J296" s="0">
-        <v>368.18880000000001</v>
+        <v>366.78320000000002</v>
       </c>
     </row>
     <row r="297">
@@ -11966,19 +12083,19 @@
         <v>29</v>
       </c>
       <c r="F297" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G297" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H297" s="0" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="J297" s="0">
-        <v>366.78320000000002</v>
+        <v>361.8997</v>
       </c>
     </row>
     <row r="298">
@@ -11998,19 +12115,19 @@
         <v>29</v>
       </c>
       <c r="F298" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G298" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H298" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="J298" s="0">
-        <v>361.8997</v>
+        <v>322.42989999999998</v>
       </c>
     </row>
     <row r="299">
@@ -12030,19 +12147,19 @@
         <v>29</v>
       </c>
       <c r="F299" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G299" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H299" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J299" s="0">
-        <v>322.42989999999998</v>
+        <v>308.6019</v>
       </c>
     </row>
     <row r="300">
@@ -12062,19 +12179,19 @@
         <v>29</v>
       </c>
       <c r="F300" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G300" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H300" s="0" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="J300" s="0">
-        <v>308.6019</v>
+        <v>260.48289999999997</v>
       </c>
     </row>
     <row r="301">
@@ -12088,25 +12205,25 @@
         <v>8</v>
       </c>
       <c r="D301" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E301" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F301" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G301" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H301" s="0" t="s">
-        <v>268</v>
+        <v>103</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="J301" s="0">
-        <v>260.48289999999997</v>
+        <v>6411.3008</v>
       </c>
     </row>
     <row r="302">
@@ -12126,19 +12243,19 @@
         <v>27</v>
       </c>
       <c r="F302" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G302" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H302" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="J302" s="0">
-        <v>6411.3008</v>
+        <v>5363.7114000000001</v>
       </c>
     </row>
     <row r="303">
@@ -12155,22 +12272,22 @@
         <v>16</v>
       </c>
       <c r="E303" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F303" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G303" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H303" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="J303" s="0">
-        <v>5363.7114000000001</v>
+        <v>561.40689999999995</v>
       </c>
     </row>
     <row r="304">
@@ -12190,19 +12307,19 @@
         <v>28</v>
       </c>
       <c r="F304" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G304" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H304" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="J304" s="0">
-        <v>561.40689999999995</v>
+        <v>495.09269999999998</v>
       </c>
     </row>
     <row r="305">
@@ -12219,22 +12336,22 @@
         <v>16</v>
       </c>
       <c r="E305" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F305" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G305" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H305" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J305" s="0">
-        <v>495.09269999999998</v>
+        <v>465.0847</v>
       </c>
     </row>
     <row r="306">
@@ -12254,19 +12371,19 @@
         <v>29</v>
       </c>
       <c r="F306" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G306" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H306" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="J306" s="0">
-        <v>465.0847</v>
+        <v>432.71969999999999</v>
       </c>
     </row>
     <row r="307">
@@ -12286,19 +12403,19 @@
         <v>29</v>
       </c>
       <c r="F307" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G307" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H307" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="J307" s="0">
-        <v>432.71969999999999</v>
+        <v>403.6884</v>
       </c>
     </row>
     <row r="308">
@@ -12318,19 +12435,19 @@
         <v>29</v>
       </c>
       <c r="F308" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G308" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H308" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="J308" s="0">
-        <v>403.6884</v>
+        <v>393.85660000000001</v>
       </c>
     </row>
     <row r="309">
@@ -12350,19 +12467,19 @@
         <v>29</v>
       </c>
       <c r="F309" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G309" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H309" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="J309" s="0">
-        <v>393.85660000000001</v>
+        <v>328.83640000000003</v>
       </c>
     </row>
     <row r="310">
@@ -12382,19 +12499,19 @@
         <v>29</v>
       </c>
       <c r="F310" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G310" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H310" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="J310" s="0">
-        <v>328.83640000000003</v>
+        <v>289.99919999999997</v>
       </c>
     </row>
     <row r="311">
@@ -12414,19 +12531,19 @@
         <v>29</v>
       </c>
       <c r="F311" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G311" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H311" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="J311" s="0">
-        <v>289.99919999999997</v>
+        <v>253.50819999999999</v>
       </c>
     </row>
     <row r="312">
@@ -12446,19 +12563,19 @@
         <v>29</v>
       </c>
       <c r="F312" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G312" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H312" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="J312" s="0">
-        <v>253.50819999999999</v>
+        <v>156.39179999999999</v>
       </c>
     </row>
     <row r="313">
@@ -12472,25 +12589,25 @@
         <v>8</v>
       </c>
       <c r="D313" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E313" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F313" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G313" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H313" s="0" t="s">
-        <v>114</v>
+        <v>269</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="J313" s="0">
-        <v>156.39179999999999</v>
+        <v>5610.5132000000003</v>
       </c>
     </row>
     <row r="314">
@@ -12510,19 +12627,19 @@
         <v>27</v>
       </c>
       <c r="F314" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G314" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H314" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="J314" s="0">
-        <v>5610.5132000000003</v>
+        <v>2526.6718999999998</v>
       </c>
     </row>
     <row r="315">
@@ -12539,22 +12656,22 @@
         <v>17</v>
       </c>
       <c r="E315" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F315" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G315" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H315" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="J315" s="0">
-        <v>2526.6718999999998</v>
+        <v>663.2672</v>
       </c>
     </row>
     <row r="316">
@@ -12574,19 +12691,19 @@
         <v>28</v>
       </c>
       <c r="F316" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G316" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H316" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="J316" s="0">
-        <v>663.2672</v>
+        <v>553.69179999999994</v>
       </c>
     </row>
     <row r="317">
@@ -12603,22 +12720,22 @@
         <v>17</v>
       </c>
       <c r="E317" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F317" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G317" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H317" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="J317" s="0">
-        <v>553.69179999999994</v>
+        <v>436.38159999999999</v>
       </c>
     </row>
     <row r="318">
@@ -12638,19 +12755,19 @@
         <v>29</v>
       </c>
       <c r="F318" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G318" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H318" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="J318" s="0">
-        <v>436.38159999999999</v>
+        <v>411.78269999999998</v>
       </c>
     </row>
     <row r="319">
@@ -12670,19 +12787,19 @@
         <v>29</v>
       </c>
       <c r="F319" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G319" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H319" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="J319" s="0">
-        <v>411.78269999999998</v>
+        <v>407.44670000000002</v>
       </c>
     </row>
     <row r="320">
@@ -12702,19 +12819,19 @@
         <v>29</v>
       </c>
       <c r="F320" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G320" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H320" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="J320" s="0">
-        <v>407.44670000000002</v>
+        <v>390.17970000000003</v>
       </c>
     </row>
     <row r="321">
@@ -12734,19 +12851,19 @@
         <v>29</v>
       </c>
       <c r="F321" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G321" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H321" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="J321" s="0">
-        <v>390.17970000000003</v>
+        <v>379.34300000000002</v>
       </c>
     </row>
     <row r="322">
@@ -12766,19 +12883,19 @@
         <v>29</v>
       </c>
       <c r="F322" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G322" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H322" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="J322" s="0">
-        <v>379.34300000000002</v>
+        <v>378.32549999999998</v>
       </c>
     </row>
     <row r="323">
@@ -12798,19 +12915,19 @@
         <v>29</v>
       </c>
       <c r="F323" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G323" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H323" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="J323" s="0">
-        <v>378.32549999999998</v>
+        <v>248.1077</v>
       </c>
     </row>
     <row r="324">
@@ -12830,19 +12947,19 @@
         <v>29</v>
       </c>
       <c r="F324" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G324" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H324" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J324" s="0">
-        <v>248.1077</v>
+        <v>155.72280000000001</v>
       </c>
     </row>
     <row r="325">
@@ -12856,25 +12973,25 @@
         <v>8</v>
       </c>
       <c r="D325" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E325" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F325" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G325" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H325" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="J325" s="0">
-        <v>155.72280000000001</v>
+        <v>6378.5679</v>
       </c>
     </row>
     <row r="326">
@@ -12894,19 +13011,19 @@
         <v>27</v>
       </c>
       <c r="F326" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G326" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H326" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="J326" s="0">
-        <v>6378.5679</v>
+        <v>3677.8054000000002</v>
       </c>
     </row>
     <row r="327">
@@ -12923,22 +13040,22 @@
         <v>25</v>
       </c>
       <c r="E327" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F327" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G327" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H327" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="J327" s="0">
-        <v>3677.8054000000002</v>
+        <v>990.75639999999999</v>
       </c>
     </row>
     <row r="328">
@@ -12958,19 +13075,19 @@
         <v>28</v>
       </c>
       <c r="F328" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G328" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H328" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="J328" s="0">
-        <v>990.75639999999999</v>
+        <v>912.61609999999996</v>
       </c>
     </row>
     <row r="329">
@@ -12987,22 +13104,22 @@
         <v>25</v>
       </c>
       <c r="E329" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F329" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G329" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H329" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="J329" s="0">
-        <v>912.61609999999996</v>
+        <v>448.30200000000002</v>
       </c>
     </row>
     <row r="330">
@@ -13022,19 +13139,19 @@
         <v>29</v>
       </c>
       <c r="F330" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G330" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H330" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="J330" s="0">
-        <v>448.30200000000002</v>
+        <v>415.84109999999998</v>
       </c>
     </row>
     <row r="331">
@@ -13054,19 +13171,19 @@
         <v>29</v>
       </c>
       <c r="F331" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G331" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H331" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="J331" s="0">
-        <v>415.84109999999998</v>
+        <v>380.94420000000002</v>
       </c>
     </row>
     <row r="332">
@@ -13086,19 +13203,19 @@
         <v>29</v>
       </c>
       <c r="F332" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G332" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H332" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="J332" s="0">
-        <v>380.94420000000002</v>
+        <v>359.60860000000002</v>
       </c>
     </row>
     <row r="333">
@@ -13118,19 +13235,19 @@
         <v>29</v>
       </c>
       <c r="F333" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G333" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H333" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="J333" s="0">
-        <v>359.60860000000002</v>
+        <v>338.8168</v>
       </c>
     </row>
     <row r="334">
@@ -13150,19 +13267,19 @@
         <v>29</v>
       </c>
       <c r="F334" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G334" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H334" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J334" s="0">
-        <v>338.8168</v>
+        <v>320.63470000000001</v>
       </c>
     </row>
     <row r="335">
@@ -13182,19 +13299,19 @@
         <v>29</v>
       </c>
       <c r="F335" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G335" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H335" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J335" s="0">
-        <v>320.63470000000001</v>
+        <v>287.04489999999999</v>
       </c>
     </row>
     <row r="336">
@@ -13214,19 +13331,19 @@
         <v>29</v>
       </c>
       <c r="F336" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G336" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H336" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J336" s="0">
-        <v>287.04489999999999</v>
+        <v>107.8788</v>
       </c>
     </row>
     <row r="337">
@@ -13237,28 +13354,28 @@
         <v>4</v>
       </c>
       <c r="C337" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D337" s="0" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E337" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F337" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G337" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H337" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="J337" s="0">
-        <v>107.8788</v>
+        <v>5099.2568000000001</v>
       </c>
     </row>
     <row r="338">
@@ -13278,19 +13395,19 @@
         <v>27</v>
       </c>
       <c r="F338" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G338" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H338" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="J338" s="0">
-        <v>5099.2568000000001</v>
+        <v>2383.1239999999998</v>
       </c>
     </row>
     <row r="339">
@@ -13307,22 +13424,22 @@
         <v>18</v>
       </c>
       <c r="E339" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F339" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G339" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H339" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="J339" s="0">
-        <v>2383.1239999999998</v>
+        <v>670.93709999999999</v>
       </c>
     </row>
     <row r="340">
@@ -13342,19 +13459,19 @@
         <v>28</v>
       </c>
       <c r="F340" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G340" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H340" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="J340" s="0">
-        <v>670.93709999999999</v>
+        <v>459.24430000000001</v>
       </c>
     </row>
     <row r="341">
@@ -13371,22 +13488,22 @@
         <v>18</v>
       </c>
       <c r="E341" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F341" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G341" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H341" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="J341" s="0">
-        <v>459.24430000000001</v>
+        <v>415.84710000000001</v>
       </c>
     </row>
     <row r="342">
@@ -13406,19 +13523,19 @@
         <v>29</v>
       </c>
       <c r="F342" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G342" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H342" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="J342" s="0">
-        <v>415.84710000000001</v>
+        <v>404.09039999999999</v>
       </c>
     </row>
     <row r="343">
@@ -13438,19 +13555,19 @@
         <v>29</v>
       </c>
       <c r="F343" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G343" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H343" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="J343" s="0">
-        <v>404.09039999999999</v>
+        <v>370.1207</v>
       </c>
     </row>
     <row r="344">
@@ -13470,19 +13587,19 @@
         <v>29</v>
       </c>
       <c r="F344" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G344" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H344" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="J344" s="0">
-        <v>370.1207</v>
+        <v>369.87549999999999</v>
       </c>
     </row>
     <row r="345">
@@ -13502,19 +13619,19 @@
         <v>29</v>
       </c>
       <c r="F345" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G345" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H345" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J345" s="0">
-        <v>369.87549999999999</v>
+        <v>332.15789999999998</v>
       </c>
     </row>
     <row r="346">
@@ -13534,19 +13651,19 @@
         <v>29</v>
       </c>
       <c r="F346" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G346" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H346" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J346" s="0">
-        <v>332.15789999999998</v>
+        <v>310.02600000000001</v>
       </c>
     </row>
     <row r="347">
@@ -13566,19 +13683,19 @@
         <v>29</v>
       </c>
       <c r="F347" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G347" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H347" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="J347" s="0">
-        <v>310.02600000000001</v>
+        <v>137.19120000000001</v>
       </c>
     </row>
     <row r="348">
@@ -13598,19 +13715,19 @@
         <v>29</v>
       </c>
       <c r="F348" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G348" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H348" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="J348" s="0">
-        <v>137.19120000000001</v>
+        <v>21.848400000000002</v>
       </c>
     </row>
     <row r="349">
@@ -13624,25 +13741,25 @@
         <v>9</v>
       </c>
       <c r="D349" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E349" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F349" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G349" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H349" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="J349" s="0">
-        <v>21.848400000000002</v>
+        <v>6147.9931999999999</v>
       </c>
     </row>
     <row r="350">
@@ -13662,19 +13779,19 @@
         <v>27</v>
       </c>
       <c r="F350" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G350" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H350" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="J350" s="0">
-        <v>6147.9931999999999</v>
+        <v>4509.7578000000003</v>
       </c>
     </row>
     <row r="351">
@@ -13691,22 +13808,22 @@
         <v>19</v>
       </c>
       <c r="E351" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F351" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G351" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H351" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="J351" s="0">
-        <v>4509.7578000000003</v>
+        <v>999.82090000000005</v>
       </c>
     </row>
     <row r="352">
@@ -13726,19 +13843,19 @@
         <v>28</v>
       </c>
       <c r="F352" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G352" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H352" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="J352" s="0">
-        <v>999.82090000000005</v>
+        <v>829.32470000000001</v>
       </c>
     </row>
     <row r="353">
@@ -13755,22 +13872,22 @@
         <v>19</v>
       </c>
       <c r="E353" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F353" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G353" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H353" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I353" s="0" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="J353" s="0">
-        <v>829.32470000000001</v>
+        <v>460.868</v>
       </c>
     </row>
     <row r="354">
@@ -13790,19 +13907,19 @@
         <v>29</v>
       </c>
       <c r="F354" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G354" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H354" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I354" s="0" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="J354" s="0">
-        <v>460.868</v>
+        <v>418.91930000000002</v>
       </c>
     </row>
     <row r="355">
@@ -13822,19 +13939,19 @@
         <v>29</v>
       </c>
       <c r="F355" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G355" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H355" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I355" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="J355" s="0">
-        <v>418.91930000000002</v>
+        <v>377.29809999999998</v>
       </c>
     </row>
     <row r="356">
@@ -13854,19 +13971,19 @@
         <v>29</v>
       </c>
       <c r="F356" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G356" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H356" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I356" s="0" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="J356" s="0">
-        <v>377.29809999999998</v>
+        <v>376.07799999999998</v>
       </c>
     </row>
     <row r="357">
@@ -13886,19 +14003,19 @@
         <v>29</v>
       </c>
       <c r="F357" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G357" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H357" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I357" s="0" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="J357" s="0">
-        <v>376.07799999999998</v>
+        <v>345.4522</v>
       </c>
     </row>
     <row r="358">
@@ -13918,19 +14035,19 @@
         <v>29</v>
       </c>
       <c r="F358" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G358" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H358" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I358" s="0" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="J358" s="0">
-        <v>345.4522</v>
+        <v>333.1805</v>
       </c>
     </row>
     <row r="359">
@@ -13950,19 +14067,19 @@
         <v>29</v>
       </c>
       <c r="F359" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G359" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H359" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I359" s="0" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="J359" s="0">
-        <v>333.1805</v>
+        <v>297.38940000000002</v>
       </c>
     </row>
     <row r="360">
@@ -13982,19 +14099,19 @@
         <v>29</v>
       </c>
       <c r="F360" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G360" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H360" s="0" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I360" s="0" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="J360" s="0">
-        <v>297.38940000000002</v>
+        <v>196.88849999999999</v>
       </c>
     </row>
     <row r="361">
@@ -14008,25 +14125,25 @@
         <v>9</v>
       </c>
       <c r="D361" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E361" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F361" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G361" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H361" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I361" s="0" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="J361" s="0">
-        <v>196.88849999999999</v>
+        <v>5372.8154000000004</v>
       </c>
     </row>
     <row r="362">
@@ -14046,19 +14163,19 @@
         <v>27</v>
       </c>
       <c r="F362" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G362" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H362" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I362" s="0" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="J362" s="0">
-        <v>5372.8154000000004</v>
+        <v>5089.0283</v>
       </c>
     </row>
     <row r="363">
@@ -14075,22 +14192,22 @@
         <v>20</v>
       </c>
       <c r="E363" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F363" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G363" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H363" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I363" s="0" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="J363" s="0">
-        <v>5089.0283</v>
+        <v>623.85149999999999</v>
       </c>
     </row>
     <row r="364">
@@ -14110,19 +14227,19 @@
         <v>28</v>
       </c>
       <c r="F364" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G364" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H364" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I364" s="0" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="J364" s="0">
-        <v>623.85149999999999</v>
+        <v>173.3056</v>
       </c>
     </row>
     <row r="365">
@@ -14139,22 +14256,22 @@
         <v>20</v>
       </c>
       <c r="E365" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F365" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G365" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H365" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I365" s="0" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="J365" s="0">
-        <v>173.3056</v>
+        <v>414.66230000000002</v>
       </c>
     </row>
     <row r="366">
@@ -14174,19 +14291,19 @@
         <v>29</v>
       </c>
       <c r="F366" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G366" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H366" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I366" s="0" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="J366" s="0">
-        <v>414.66230000000002</v>
+        <v>403.9067</v>
       </c>
     </row>
     <row r="367">
@@ -14206,19 +14323,19 @@
         <v>29</v>
       </c>
       <c r="F367" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G367" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H367" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I367" s="0" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="J367" s="0">
-        <v>403.9067</v>
+        <v>374.75290000000001</v>
       </c>
     </row>
     <row r="368">
@@ -14238,19 +14355,19 @@
         <v>29</v>
       </c>
       <c r="F368" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G368" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H368" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I368" s="0" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="J368" s="0">
-        <v>374.75290000000001</v>
+        <v>372.04629999999997</v>
       </c>
     </row>
     <row r="369">
@@ -14270,19 +14387,19 @@
         <v>29</v>
       </c>
       <c r="F369" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G369" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H369" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I369" s="0" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="J369" s="0">
-        <v>372.04629999999997</v>
+        <v>372.0009</v>
       </c>
     </row>
     <row r="370">
@@ -14302,19 +14419,19 @@
         <v>29</v>
       </c>
       <c r="F370" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G370" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H370" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I370" s="0" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="J370" s="0">
-        <v>372.0009</v>
+        <v>318.33179999999999</v>
       </c>
     </row>
     <row r="371">
@@ -14334,19 +14451,19 @@
         <v>29</v>
       </c>
       <c r="F371" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G371" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H371" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I371" s="0" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="J371" s="0">
-        <v>318.33179999999999</v>
+        <v>295.59719999999999</v>
       </c>
     </row>
     <row r="372">
@@ -14366,19 +14483,19 @@
         <v>29</v>
       </c>
       <c r="F372" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G372" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H372" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I372" s="0" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="J372" s="0">
-        <v>295.59719999999999</v>
+        <v>137.02930000000001</v>
       </c>
     </row>
     <row r="373">
@@ -14392,25 +14509,25 @@
         <v>9</v>
       </c>
       <c r="D373" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E373" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F373" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G373" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H373" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I373" s="0" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="J373" s="0">
-        <v>137.02930000000001</v>
+        <v>4746.6201000000001</v>
       </c>
     </row>
     <row r="374">
@@ -14430,19 +14547,19 @@
         <v>27</v>
       </c>
       <c r="F374" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G374" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H374" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I374" s="0" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="J374" s="0">
-        <v>4746.6201000000001</v>
+        <v>4426.7367999999997</v>
       </c>
     </row>
     <row r="375">
@@ -14459,22 +14576,22 @@
         <v>21</v>
       </c>
       <c r="E375" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F375" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G375" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H375" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I375" s="0" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="J375" s="0">
-        <v>4426.7367999999997</v>
+        <v>502.13749999999999</v>
       </c>
     </row>
     <row r="376">
@@ -14494,19 +14611,19 @@
         <v>28</v>
       </c>
       <c r="F376" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G376" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H376" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I376" s="0" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="J376" s="0">
-        <v>502.13749999999999</v>
+        <v>135.70679999999999</v>
       </c>
     </row>
     <row r="377">
@@ -14523,22 +14640,22 @@
         <v>21</v>
       </c>
       <c r="E377" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F377" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G377" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H377" s="0" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I377" s="0" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="J377" s="0">
-        <v>135.70679999999999</v>
+        <v>439.52850000000001</v>
       </c>
     </row>
     <row r="378">
@@ -14558,19 +14675,19 @@
         <v>29</v>
       </c>
       <c r="F378" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G378" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H378" s="0" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I378" s="0" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="J378" s="0">
-        <v>516.24180000000001</v>
+        <v>423.6062</v>
       </c>
     </row>
     <row r="379">
@@ -14590,19 +14707,19 @@
         <v>29</v>
       </c>
       <c r="F379" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G379" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H379" s="0" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="I379" s="0" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="J379" s="0">
-        <v>439.52850000000001</v>
+        <v>388.16570000000002</v>
       </c>
     </row>
     <row r="380">
@@ -14622,19 +14739,19 @@
         <v>29</v>
       </c>
       <c r="F380" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G380" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H380" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I380" s="0" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="J380" s="0">
-        <v>423.6062</v>
+        <v>361.62639999999999</v>
       </c>
     </row>
     <row r="381">
@@ -14654,19 +14771,19 @@
         <v>29</v>
       </c>
       <c r="F381" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G381" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H381" s="0" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I381" s="0" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="J381" s="0">
-        <v>388.16570000000002</v>
+        <v>319.28989999999999</v>
       </c>
     </row>
     <row r="382">
@@ -14686,19 +14803,19 @@
         <v>29</v>
       </c>
       <c r="F382" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G382" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H382" s="0" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I382" s="0" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="J382" s="0">
-        <v>361.62639999999999</v>
+        <v>283.29320000000001</v>
       </c>
     </row>
     <row r="383">
@@ -14718,19 +14835,19 @@
         <v>29</v>
       </c>
       <c r="F383" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G383" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H383" s="0" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="I383" s="0" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="J383" s="0">
-        <v>319.28989999999999</v>
+        <v>254.66130000000001</v>
       </c>
     </row>
     <row r="384">

--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36299" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="42907" uniqueCount="875">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="42907" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="46193" uniqueCount="875">
   <si>
     <t>Year</t>
   </si>
@@ -3897,22 +3897,22 @@
         <v>14</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J38" s="0">
-        <v>388.709</v>
+        <v>448.01760000000002</v>
       </c>
     </row>
     <row r="39">
@@ -3932,19 +3932,19 @@
         <v>29</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G39" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J39" s="0">
-        <v>448.01760000000002</v>
+        <v>429.6198</v>
       </c>
     </row>
     <row r="40">
@@ -3964,19 +3964,19 @@
         <v>29</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G40" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J40" s="0">
-        <v>429.6198</v>
+        <v>406.0299</v>
       </c>
     </row>
     <row r="41">
@@ -3996,19 +3996,19 @@
         <v>29</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G41" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J41" s="0">
-        <v>406.0299</v>
+        <v>405.92529999999999</v>
       </c>
     </row>
     <row r="42">
@@ -4028,19 +4028,19 @@
         <v>29</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J42" s="0">
-        <v>405.92529999999999</v>
+        <v>403.39850000000001</v>
       </c>
     </row>
     <row r="43">
@@ -4060,19 +4060,19 @@
         <v>29</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G43" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J43" s="0">
-        <v>403.39850000000001</v>
+        <v>381.14350000000002</v>
       </c>
     </row>
     <row r="44">
@@ -4092,19 +4092,19 @@
         <v>29</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G44" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J44" s="0">
-        <v>381.14350000000002</v>
+        <v>254.68129999999999</v>
       </c>
     </row>
     <row r="45">
@@ -4124,19 +4124,19 @@
         <v>29</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G45" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J45" s="0">
-        <v>254.68129999999999</v>
+        <v>166.26730000000001</v>
       </c>
     </row>
     <row r="46">
@@ -4147,28 +4147,28 @@
         <v>3</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>7</v>
+        <v>655</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>14</v>
+        <v>801</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>90</v>
+        <v>659</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>389</v>
+        <v>840</v>
       </c>
       <c r="J46" s="0">
-        <v>166.26730000000001</v>
+        <v>5173.3311000000003</v>
       </c>
     </row>
     <row r="47">
@@ -4188,19 +4188,19 @@
         <v>27</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="J47" s="0">
-        <v>5173.3311000000003</v>
+        <v>3079.3002999999999</v>
       </c>
     </row>
     <row r="48">
@@ -4217,22 +4217,22 @@
         <v>801</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="J48" s="0">
-        <v>3079.3002999999999</v>
+        <v>562.13390000000004</v>
       </c>
     </row>
     <row r="49">
@@ -4249,7 +4249,7 @@
         <v>801</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F49" s="0" t="s">
         <v>31</v>
@@ -4258,13 +4258,13 @@
         <v>40</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="J49" s="0">
-        <v>562.13390000000004</v>
+        <v>424.15600000000001</v>
       </c>
     </row>
     <row r="50">
@@ -4284,19 +4284,19 @@
         <v>29</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G50" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="J50" s="0">
-        <v>424.15600000000001</v>
+        <v>387.75049999999999</v>
       </c>
     </row>
     <row r="51">
@@ -4316,19 +4316,19 @@
         <v>29</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G51" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="J51" s="0">
-        <v>387.75049999999999</v>
+        <v>348.00529999999998</v>
       </c>
     </row>
     <row r="52">
@@ -4348,19 +4348,19 @@
         <v>29</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G52" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="J52" s="0">
-        <v>348.00529999999998</v>
+        <v>332.44470000000001</v>
       </c>
     </row>
     <row r="53">
@@ -4380,19 +4380,19 @@
         <v>29</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="J53" s="0">
-        <v>332.44470000000001</v>
+        <v>320.80650000000003</v>
       </c>
     </row>
     <row r="54">
@@ -4412,19 +4412,19 @@
         <v>29</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G54" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="J54" s="0">
-        <v>320.80650000000003</v>
+        <v>310.77530000000002</v>
       </c>
     </row>
     <row r="55">
@@ -4444,19 +4444,19 @@
         <v>29</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G55" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="J55" s="0">
-        <v>310.77530000000002</v>
+        <v>255.58779999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4476,19 +4476,19 @@
         <v>29</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G56" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="J56" s="0">
-        <v>255.58779999999999</v>
+        <v>224.2235</v>
       </c>
     </row>
     <row r="57">
@@ -4502,25 +4502,25 @@
         <v>655</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="J57" s="0">
-        <v>224.2235</v>
+        <v>6088.3633</v>
       </c>
     </row>
     <row r="58">
@@ -4540,19 +4540,19 @@
         <v>27</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="J58" s="0">
-        <v>6088.3633</v>
+        <v>5077.0581000000002</v>
       </c>
     </row>
     <row r="59">
@@ -4569,22 +4569,22 @@
         <v>802</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="J59" s="0">
-        <v>5077.0581000000002</v>
+        <v>728.97640000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4604,19 +4604,19 @@
         <v>28</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="J60" s="0">
-        <v>728.97640000000001</v>
+        <v>681.9529</v>
       </c>
     </row>
     <row r="61">
@@ -4633,22 +4633,22 @@
         <v>802</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="J61" s="0">
-        <v>681.9529</v>
+        <v>460.65499999999997</v>
       </c>
     </row>
     <row r="62">
@@ -4668,19 +4668,19 @@
         <v>29</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G62" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="J62" s="0">
-        <v>460.65499999999997</v>
+        <v>406.1062</v>
       </c>
     </row>
     <row r="63">
@@ -4700,19 +4700,19 @@
         <v>29</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G63" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="J63" s="0">
-        <v>406.1062</v>
+        <v>382.6694</v>
       </c>
     </row>
     <row r="64">
@@ -4732,19 +4732,19 @@
         <v>29</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G64" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="J64" s="0">
-        <v>382.6694</v>
+        <v>369.21839999999998</v>
       </c>
     </row>
     <row r="65">
@@ -4764,19 +4764,19 @@
         <v>29</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="J65" s="0">
-        <v>369.21839999999998</v>
+        <v>341.30959999999999</v>
       </c>
     </row>
     <row r="66">
@@ -4796,19 +4796,19 @@
         <v>29</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G66" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="J66" s="0">
-        <v>341.30959999999999</v>
+        <v>319.78870000000001</v>
       </c>
     </row>
     <row r="67">
@@ -4828,19 +4828,19 @@
         <v>29</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="J67" s="0">
-        <v>319.78870000000001</v>
+        <v>289.6028</v>
       </c>
     </row>
     <row r="68">
@@ -4860,19 +4860,19 @@
         <v>29</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G68" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="J68" s="0">
-        <v>289.6028</v>
+        <v>284.9262</v>
       </c>
     </row>
     <row r="69">
@@ -4886,25 +4886,25 @@
         <v>655</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="J69" s="0">
-        <v>284.9262</v>
+        <v>5367.4771000000001</v>
       </c>
     </row>
     <row r="70">
@@ -4924,19 +4924,19 @@
         <v>27</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="J70" s="0">
-        <v>5367.4771000000001</v>
+        <v>3219.1161999999999</v>
       </c>
     </row>
     <row r="71">
@@ -4953,22 +4953,22 @@
         <v>803</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>684</v>
+        <v>307</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="J71" s="0">
-        <v>3219.1161999999999</v>
+        <v>999.82090000000005</v>
       </c>
     </row>
     <row r="72">
@@ -4988,19 +4988,19 @@
         <v>28</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="J72" s="0">
-        <v>999.82090000000005</v>
+        <v>829.32470000000001</v>
       </c>
     </row>
     <row r="73">
@@ -5017,22 +5017,22 @@
         <v>803</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>308</v>
+        <v>685</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="J73" s="0">
-        <v>829.32470000000001</v>
+        <v>434.72210000000001</v>
       </c>
     </row>
     <row r="74">
@@ -5052,19 +5052,19 @@
         <v>29</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G74" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="J74" s="0">
-        <v>434.72210000000001</v>
+        <v>420.51510000000002</v>
       </c>
     </row>
     <row r="75">
@@ -5084,19 +5084,19 @@
         <v>29</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G75" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="J75" s="0">
-        <v>420.51510000000002</v>
+        <v>416.28559999999999</v>
       </c>
     </row>
     <row r="76">
@@ -5116,19 +5116,19 @@
         <v>29</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G76" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="J76" s="0">
-        <v>416.28559999999999</v>
+        <v>400.9085</v>
       </c>
     </row>
     <row r="77">
@@ -5148,19 +5148,19 @@
         <v>29</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="J77" s="0">
-        <v>400.9085</v>
+        <v>360.4205</v>
       </c>
     </row>
     <row r="78">
@@ -5180,19 +5180,19 @@
         <v>29</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G78" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="J78" s="0">
-        <v>360.4205</v>
+        <v>305.30689999999999</v>
       </c>
     </row>
     <row r="79">
@@ -5212,19 +5212,19 @@
         <v>29</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G79" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="J79" s="0">
-        <v>305.30689999999999</v>
+        <v>293.2808</v>
       </c>
     </row>
     <row r="80">
@@ -5244,19 +5244,19 @@
         <v>29</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G80" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="J80" s="0">
-        <v>293.2808</v>
+        <v>247.7748</v>
       </c>
     </row>
     <row r="81">
@@ -5267,28 +5267,28 @@
         <v>3</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>655</v>
+        <v>8</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>803</v>
+        <v>15</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>692</v>
+        <v>91</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>874</v>
+        <v>390</v>
       </c>
       <c r="J81" s="0">
-        <v>247.7748</v>
+        <v>5813.3739999999998</v>
       </c>
     </row>
     <row r="82">
@@ -5308,19 +5308,19 @@
         <v>27</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J82" s="0">
-        <v>5813.3739999999998</v>
+        <v>3499.9191999999998</v>
       </c>
     </row>
     <row r="83">
@@ -5337,22 +5337,22 @@
         <v>15</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J83" s="0">
-        <v>3499.9191999999998</v>
+        <v>643.7663</v>
       </c>
     </row>
     <row r="84">
@@ -5372,19 +5372,19 @@
         <v>28</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J84" s="0">
-        <v>643.7663</v>
+        <v>507.9119</v>
       </c>
     </row>
     <row r="85">
@@ -5401,22 +5401,22 @@
         <v>15</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J85" s="0">
-        <v>507.9119</v>
+        <v>413.24200000000002</v>
       </c>
     </row>
     <row r="86">
@@ -5436,19 +5436,19 @@
         <v>29</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G86" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J86" s="0">
-        <v>413.24200000000002</v>
+        <v>412.743</v>
       </c>
     </row>
     <row r="87">
@@ -5468,19 +5468,19 @@
         <v>29</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G87" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J87" s="0">
-        <v>412.743</v>
+        <v>365.9803</v>
       </c>
     </row>
     <row r="88">
@@ -5500,19 +5500,19 @@
         <v>29</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G88" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J88" s="0">
-        <v>365.9803</v>
+        <v>362.68889999999999</v>
       </c>
     </row>
     <row r="89">
@@ -5532,19 +5532,19 @@
         <v>29</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J89" s="0">
-        <v>362.68889999999999</v>
+        <v>337.94470000000001</v>
       </c>
     </row>
     <row r="90">
@@ -5564,19 +5564,19 @@
         <v>29</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G90" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J90" s="0">
-        <v>337.94470000000001</v>
+        <v>275.04509999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5596,19 +5596,19 @@
         <v>29</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G91" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J91" s="0">
-        <v>275.04509999999999</v>
+        <v>253.987</v>
       </c>
     </row>
     <row r="92">
@@ -5628,19 +5628,19 @@
         <v>29</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G92" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J92" s="0">
-        <v>253.987</v>
+        <v>197.0513</v>
       </c>
     </row>
     <row r="93">
@@ -5654,25 +5654,25 @@
         <v>8</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J93" s="0">
-        <v>197.0513</v>
+        <v>6411.3008</v>
       </c>
     </row>
     <row r="94">
@@ -5692,19 +5692,19 @@
         <v>27</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J94" s="0">
-        <v>6411.3008</v>
+        <v>5363.7114000000001</v>
       </c>
     </row>
     <row r="95">
@@ -5721,22 +5721,22 @@
         <v>16</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J95" s="0">
-        <v>5363.7114000000001</v>
+        <v>495.09269999999998</v>
       </c>
     </row>
     <row r="96">
@@ -5753,7 +5753,7 @@
         <v>16</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F96" s="0" t="s">
         <v>31</v>
@@ -5762,13 +5762,13 @@
         <v>40</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J96" s="0">
-        <v>495.09269999999998</v>
+        <v>465.0847</v>
       </c>
     </row>
     <row r="97">
@@ -5788,19 +5788,19 @@
         <v>29</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G97" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J97" s="0">
-        <v>465.0847</v>
+        <v>432.71969999999999</v>
       </c>
     </row>
     <row r="98">
@@ -5820,19 +5820,19 @@
         <v>29</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G98" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J98" s="0">
-        <v>432.71969999999999</v>
+        <v>403.6884</v>
       </c>
     </row>
     <row r="99">
@@ -5852,19 +5852,19 @@
         <v>29</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G99" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J99" s="0">
-        <v>403.6884</v>
+        <v>393.85660000000001</v>
       </c>
     </row>
     <row r="100">
@@ -5884,19 +5884,19 @@
         <v>29</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J100" s="0">
-        <v>393.85660000000001</v>
+        <v>328.83640000000003</v>
       </c>
     </row>
     <row r="101">
@@ -5916,19 +5916,19 @@
         <v>29</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G101" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J101" s="0">
-        <v>328.83640000000003</v>
+        <v>289.99919999999997</v>
       </c>
     </row>
     <row r="102">
@@ -5948,19 +5948,19 @@
         <v>29</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G102" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J102" s="0">
-        <v>289.99919999999997</v>
+        <v>253.50819999999999</v>
       </c>
     </row>
     <row r="103">
@@ -5980,19 +5980,19 @@
         <v>29</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G103" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J103" s="0">
-        <v>253.50819999999999</v>
+        <v>156.39179999999999</v>
       </c>
     </row>
     <row r="104">
@@ -6006,25 +6006,25 @@
         <v>8</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E104" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J104" s="0">
-        <v>156.39179999999999</v>
+        <v>5347.2299999999996</v>
       </c>
     </row>
     <row r="105">
@@ -6041,7 +6041,7 @@
         <v>17</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F105" s="0" t="s">
         <v>31</v>
@@ -6050,13 +6050,13 @@
         <v>40</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="J105" s="0">
-        <v>5347.2299999999996</v>
+        <v>832.64940000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6076,19 +6076,19 @@
         <v>28</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J106" s="0">
-        <v>832.64940000000001</v>
+        <v>670.97080000000005</v>
       </c>
     </row>
     <row r="107">
@@ -6105,22 +6105,22 @@
         <v>17</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J107" s="0">
-        <v>670.97080000000005</v>
+        <v>452.6379</v>
       </c>
     </row>
     <row r="108">
@@ -6140,19 +6140,19 @@
         <v>29</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G108" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J108" s="0">
-        <v>452.6379</v>
+        <v>432.76639999999998</v>
       </c>
     </row>
     <row r="109">
@@ -6172,19 +6172,19 @@
         <v>29</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G109" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J109" s="0">
-        <v>432.76639999999998</v>
+        <v>430.21100000000001</v>
       </c>
     </row>
     <row r="110">
@@ -6204,19 +6204,19 @@
         <v>29</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G110" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J110" s="0">
-        <v>430.21100000000001</v>
+        <v>426.60840000000002</v>
       </c>
     </row>
     <row r="111">
@@ -6236,19 +6236,19 @@
         <v>29</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G111" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J111" s="0">
-        <v>426.60840000000002</v>
+        <v>408.17599999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6268,19 +6268,19 @@
         <v>29</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G112" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J112" s="0">
-        <v>408.17599999999999</v>
+        <v>393.9744</v>
       </c>
     </row>
     <row r="113">
@@ -6300,19 +6300,19 @@
         <v>29</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G113" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J113" s="0">
-        <v>393.9744</v>
+        <v>369.06290000000001</v>
       </c>
     </row>
     <row r="114">
@@ -6332,19 +6332,19 @@
         <v>29</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G114" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J114" s="0">
-        <v>369.06290000000001</v>
+        <v>363.61939999999999</v>
       </c>
     </row>
     <row r="115">
@@ -6355,28 +6355,28 @@
         <v>3</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J115" s="0">
-        <v>363.61939999999999</v>
+        <v>5889.4614000000001</v>
       </c>
     </row>
     <row r="116">
@@ -6396,19 +6396,19 @@
         <v>27</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J116" s="0">
-        <v>5889.4614000000001</v>
+        <v>2742.3312999999998</v>
       </c>
     </row>
     <row r="117">
@@ -6425,22 +6425,22 @@
         <v>18</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J117" s="0">
-        <v>2742.3312999999998</v>
+        <v>673.23270000000002</v>
       </c>
     </row>
     <row r="118">
@@ -6460,19 +6460,19 @@
         <v>28</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J118" s="0">
-        <v>673.23270000000002</v>
+        <v>548.54560000000004</v>
       </c>
     </row>
     <row r="119">
@@ -6489,22 +6489,22 @@
         <v>18</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J119" s="0">
-        <v>548.54560000000004</v>
+        <v>406.4975</v>
       </c>
     </row>
     <row r="120">
@@ -6524,19 +6524,19 @@
         <v>29</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G120" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J120" s="0">
-        <v>406.4975</v>
+        <v>370.59609999999998</v>
       </c>
     </row>
     <row r="121">
@@ -6556,19 +6556,19 @@
         <v>29</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G121" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J121" s="0">
-        <v>370.59609999999998</v>
+        <v>295.41489999999999</v>
       </c>
     </row>
     <row r="122">
@@ -6588,19 +6588,19 @@
         <v>29</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G122" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J122" s="0">
-        <v>295.41489999999999</v>
+        <v>294.39229999999998</v>
       </c>
     </row>
     <row r="123">
@@ -6620,19 +6620,19 @@
         <v>29</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J123" s="0">
-        <v>294.39229999999998</v>
+        <v>290.21879999999999</v>
       </c>
     </row>
     <row r="124">
@@ -6652,19 +6652,19 @@
         <v>29</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G124" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J124" s="0">
-        <v>290.21879999999999</v>
+        <v>241.96080000000001</v>
       </c>
     </row>
     <row r="125">
@@ -6684,19 +6684,19 @@
         <v>29</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G125" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J125" s="0">
-        <v>241.96080000000001</v>
+        <v>208.0266</v>
       </c>
     </row>
     <row r="126">
@@ -6710,25 +6710,25 @@
         <v>9</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="J126" s="0">
-        <v>208.0266</v>
+        <v>2255.5239000000001</v>
       </c>
     </row>
     <row r="127">
@@ -6745,7 +6745,7 @@
         <v>19</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F127" s="0" t="s">
         <v>31</v>
@@ -6754,13 +6754,13 @@
         <v>40</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J127" s="0">
-        <v>2255.5239000000001</v>
+        <v>784.23540000000003</v>
       </c>
     </row>
     <row r="128">
@@ -6780,19 +6780,19 @@
         <v>28</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G128" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J128" s="0">
-        <v>784.23540000000003</v>
+        <v>590.41420000000005</v>
       </c>
     </row>
     <row r="129">
@@ -6809,22 +6809,22 @@
         <v>19</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G129" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J129" s="0">
-        <v>590.41420000000005</v>
+        <v>431.26760000000002</v>
       </c>
     </row>
     <row r="130">
@@ -6844,19 +6844,19 @@
         <v>29</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G130" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J130" s="0">
-        <v>431.26760000000002</v>
+        <v>372.27710000000002</v>
       </c>
     </row>
     <row r="131">
@@ -6876,19 +6876,19 @@
         <v>29</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G131" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J131" s="0">
-        <v>372.27710000000002</v>
+        <v>370.83260000000001</v>
       </c>
     </row>
     <row r="132">
@@ -6908,19 +6908,19 @@
         <v>29</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G132" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J132" s="0">
-        <v>370.83260000000001</v>
+        <v>368.27210000000002</v>
       </c>
     </row>
     <row r="133">
@@ -6940,19 +6940,19 @@
         <v>29</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G133" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J133" s="0">
-        <v>368.27210000000002</v>
+        <v>345.15750000000003</v>
       </c>
     </row>
     <row r="134">
@@ -6972,19 +6972,19 @@
         <v>29</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G134" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J134" s="0">
-        <v>345.15750000000003</v>
+        <v>335.8723</v>
       </c>
     </row>
     <row r="135">
@@ -7004,19 +7004,19 @@
         <v>29</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H135" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J135" s="0">
-        <v>335.8723</v>
+        <v>309.04379999999998</v>
       </c>
     </row>
     <row r="136">
@@ -7036,19 +7036,19 @@
         <v>29</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G136" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J136" s="0">
-        <v>309.04379999999998</v>
+        <v>280.34730000000002</v>
       </c>
     </row>
     <row r="137">
@@ -7062,25 +7062,25 @@
         <v>9</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G137" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J137" s="0">
-        <v>280.34730000000002</v>
+        <v>6089.4750999999997</v>
       </c>
     </row>
     <row r="138">
@@ -7100,19 +7100,19 @@
         <v>27</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J138" s="0">
-        <v>6089.4750999999997</v>
+        <v>4801.2959000000001</v>
       </c>
     </row>
     <row r="139">
@@ -7129,22 +7129,22 @@
         <v>20</v>
       </c>
       <c r="E139" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G139" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H139" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J139" s="0">
-        <v>4801.2959000000001</v>
+        <v>729.38409999999999</v>
       </c>
     </row>
     <row r="140">
@@ -7161,7 +7161,7 @@
         <v>20</v>
       </c>
       <c r="E140" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F140" s="0" t="s">
         <v>31</v>
@@ -7170,13 +7170,13 @@
         <v>40</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="J140" s="0">
-        <v>729.38409999999999</v>
+        <v>414.8329</v>
       </c>
     </row>
     <row r="141">
@@ -7196,19 +7196,19 @@
         <v>29</v>
       </c>
       <c r="F141" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G141" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J141" s="0">
-        <v>414.8329</v>
+        <v>407.11009999999999</v>
       </c>
     </row>
     <row r="142">
@@ -7228,19 +7228,19 @@
         <v>29</v>
       </c>
       <c r="F142" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G142" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J142" s="0">
-        <v>407.11009999999999</v>
+        <v>390.21910000000003</v>
       </c>
     </row>
     <row r="143">
@@ -7260,19 +7260,19 @@
         <v>29</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G143" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J143" s="0">
-        <v>390.21910000000003</v>
+        <v>362.1839</v>
       </c>
     </row>
     <row r="144">
@@ -7292,19 +7292,19 @@
         <v>29</v>
       </c>
       <c r="F144" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G144" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J144" s="0">
-        <v>362.1839</v>
+        <v>349.2903</v>
       </c>
     </row>
     <row r="145">
@@ -7324,19 +7324,19 @@
         <v>29</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G145" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H145" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J145" s="0">
-        <v>349.2903</v>
+        <v>339.61919999999998</v>
       </c>
     </row>
     <row r="146">
@@ -7356,19 +7356,19 @@
         <v>29</v>
       </c>
       <c r="F146" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G146" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J146" s="0">
-        <v>339.61919999999998</v>
+        <v>321.077</v>
       </c>
     </row>
     <row r="147">
@@ -7388,19 +7388,19 @@
         <v>29</v>
       </c>
       <c r="F147" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G147" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H147" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J147" s="0">
-        <v>321.077</v>
+        <v>320.34030000000001</v>
       </c>
     </row>
     <row r="148">
@@ -7414,25 +7414,25 @@
         <v>9</v>
       </c>
       <c r="D148" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E148" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F148" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G148" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H148" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J148" s="0">
-        <v>320.34030000000001</v>
+        <v>4900.8388999999997</v>
       </c>
     </row>
     <row r="149">
@@ -7452,19 +7452,19 @@
         <v>27</v>
       </c>
       <c r="F149" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G149" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H149" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J149" s="0">
-        <v>4900.8388999999997</v>
+        <v>2991.1887000000002</v>
       </c>
     </row>
     <row r="150">
@@ -7481,22 +7481,22 @@
         <v>21</v>
       </c>
       <c r="E150" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F150" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G150" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J150" s="0">
-        <v>2991.1887000000002</v>
+        <v>694.42499999999996</v>
       </c>
     </row>
     <row r="151">
@@ -7516,19 +7516,19 @@
         <v>28</v>
       </c>
       <c r="F151" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G151" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H151" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J151" s="0">
-        <v>694.42499999999996</v>
+        <v>590.76210000000003</v>
       </c>
     </row>
     <row r="152">
@@ -7545,22 +7545,22 @@
         <v>21</v>
       </c>
       <c r="E152" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F152" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G152" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J152" s="0">
-        <v>590.76210000000003</v>
+        <v>434.02370000000002</v>
       </c>
     </row>
     <row r="153">
@@ -7580,19 +7580,19 @@
         <v>29</v>
       </c>
       <c r="F153" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G153" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H153" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J153" s="0">
-        <v>434.02370000000002</v>
+        <v>417.05189999999999</v>
       </c>
     </row>
     <row r="154">
@@ -7612,19 +7612,19 @@
         <v>29</v>
       </c>
       <c r="F154" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G154" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H154" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J154" s="0">
-        <v>417.05189999999999</v>
+        <v>407.86430000000001</v>
       </c>
     </row>
     <row r="155">
@@ -7644,19 +7644,19 @@
         <v>29</v>
       </c>
       <c r="F155" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G155" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H155" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J155" s="0">
-        <v>407.86430000000001</v>
+        <v>406.37779999999998</v>
       </c>
     </row>
     <row r="156">
@@ -7676,19 +7676,19 @@
         <v>29</v>
       </c>
       <c r="F156" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G156" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H156" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J156" s="0">
-        <v>406.37779999999998</v>
+        <v>379.51209999999998</v>
       </c>
     </row>
     <row r="157">
@@ -7708,19 +7708,19 @@
         <v>29</v>
       </c>
       <c r="F157" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G157" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H157" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J157" s="0">
-        <v>379.51209999999998</v>
+        <v>361.57029999999998</v>
       </c>
     </row>
     <row r="158">
@@ -7740,19 +7740,19 @@
         <v>29</v>
       </c>
       <c r="F158" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G158" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H158" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J158" s="0">
-        <v>361.57029999999998</v>
+        <v>324.36189999999999</v>
       </c>
     </row>
     <row r="159">
@@ -7760,31 +7760,31 @@
         <v>1</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C159" s="0" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D159" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E159" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F159" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G159" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H159" s="0" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="J159" s="0">
-        <v>324.36189999999999</v>
+        <v>2639.6545000000001</v>
       </c>
     </row>
     <row r="160">
@@ -7801,7 +7801,7 @@
         <v>22</v>
       </c>
       <c r="E160" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F160" s="0" t="s">
         <v>31</v>
@@ -7810,13 +7810,13 @@
         <v>40</v>
       </c>
       <c r="H160" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J160" s="0">
-        <v>2639.6545000000001</v>
+        <v>538.57830000000001</v>
       </c>
     </row>
     <row r="161">
@@ -7836,19 +7836,19 @@
         <v>28</v>
       </c>
       <c r="F161" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G161" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H161" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J161" s="0">
-        <v>538.57830000000001</v>
+        <v>439.68729999999999</v>
       </c>
     </row>
     <row r="162">
@@ -7865,22 +7865,22 @@
         <v>22</v>
       </c>
       <c r="E162" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F162" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G162" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H162" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J162" s="0">
-        <v>439.68729999999999</v>
+        <v>466.59890000000001</v>
       </c>
     </row>
     <row r="163">
@@ -7900,19 +7900,19 @@
         <v>29</v>
       </c>
       <c r="F163" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G163" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H163" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J163" s="0">
-        <v>466.59890000000001</v>
+        <v>348.95269999999999</v>
       </c>
     </row>
     <row r="164">
@@ -7932,19 +7932,19 @@
         <v>29</v>
       </c>
       <c r="F164" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G164" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H164" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J164" s="0">
-        <v>348.95269999999999</v>
+        <v>320.45060000000001</v>
       </c>
     </row>
     <row r="165">
@@ -7964,19 +7964,19 @@
         <v>29</v>
       </c>
       <c r="F165" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G165" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H165" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J165" s="0">
-        <v>320.45060000000001</v>
+        <v>306.95499999999999</v>
       </c>
     </row>
     <row r="166">
@@ -7996,19 +7996,19 @@
         <v>29</v>
       </c>
       <c r="F166" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G166" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H166" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J166" s="0">
-        <v>306.95499999999999</v>
+        <v>286.13639999999998</v>
       </c>
     </row>
     <row r="167">
@@ -8028,19 +8028,19 @@
         <v>29</v>
       </c>
       <c r="F167" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G167" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H167" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J167" s="0">
-        <v>286.13639999999998</v>
+        <v>270.46800000000002</v>
       </c>
     </row>
     <row r="168">
@@ -8060,19 +8060,19 @@
         <v>29</v>
       </c>
       <c r="F168" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G168" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H168" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J168" s="0">
-        <v>270.46800000000002</v>
+        <v>266.42959999999999</v>
       </c>
     </row>
     <row r="169">
@@ -8092,19 +8092,19 @@
         <v>29</v>
       </c>
       <c r="F169" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G169" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H169" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J169" s="0">
-        <v>266.42959999999999</v>
+        <v>198.7653</v>
       </c>
     </row>
     <row r="170">
@@ -8118,25 +8118,25 @@
         <v>6</v>
       </c>
       <c r="D170" s="0" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E170" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F170" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G170" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H170" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J170" s="0">
-        <v>198.7653</v>
+        <v>6949.5127000000002</v>
       </c>
     </row>
     <row r="171">
@@ -8156,19 +8156,19 @@
         <v>27</v>
       </c>
       <c r="F171" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G171" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H171" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J171" s="0">
-        <v>6949.5127000000002</v>
+        <v>1918.3168000000001</v>
       </c>
     </row>
     <row r="172">
@@ -8185,22 +8185,22 @@
         <v>11</v>
       </c>
       <c r="E172" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F172" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G172" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H172" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J172" s="0">
-        <v>1918.3168000000001</v>
+        <v>842.53420000000006</v>
       </c>
     </row>
     <row r="173">
@@ -8220,19 +8220,19 @@
         <v>28</v>
       </c>
       <c r="F173" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G173" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H173" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J173" s="0">
-        <v>842.53420000000006</v>
+        <v>625.51949999999999</v>
       </c>
     </row>
     <row r="174">
@@ -8249,22 +8249,22 @@
         <v>11</v>
       </c>
       <c r="E174" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F174" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G174" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H174" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J174" s="0">
-        <v>625.51949999999999</v>
+        <v>403.39569999999998</v>
       </c>
     </row>
     <row r="175">
@@ -8284,19 +8284,19 @@
         <v>29</v>
       </c>
       <c r="F175" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G175" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H175" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J175" s="0">
-        <v>403.39569999999998</v>
+        <v>401.83440000000002</v>
       </c>
     </row>
     <row r="176">
@@ -8316,19 +8316,19 @@
         <v>29</v>
       </c>
       <c r="F176" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G176" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H176" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J176" s="0">
-        <v>401.83440000000002</v>
+        <v>401.53390000000002</v>
       </c>
     </row>
     <row r="177">
@@ -8348,19 +8348,19 @@
         <v>29</v>
       </c>
       <c r="F177" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G177" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H177" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J177" s="0">
-        <v>401.53390000000002</v>
+        <v>325.73790000000002</v>
       </c>
     </row>
     <row r="178">
@@ -8380,19 +8380,19 @@
         <v>29</v>
       </c>
       <c r="F178" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G178" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H178" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J178" s="0">
-        <v>325.73790000000002</v>
+        <v>306.47129999999999</v>
       </c>
     </row>
     <row r="179">
@@ -8412,19 +8412,19 @@
         <v>29</v>
       </c>
       <c r="F179" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G179" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H179" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J179" s="0">
-        <v>306.47129999999999</v>
+        <v>297.54129999999998</v>
       </c>
     </row>
     <row r="180">
@@ -8444,19 +8444,19 @@
         <v>29</v>
       </c>
       <c r="F180" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G180" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H180" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J180" s="0">
-        <v>297.54129999999998</v>
+        <v>251.23050000000001</v>
       </c>
     </row>
     <row r="181">
@@ -8476,19 +8476,19 @@
         <v>29</v>
       </c>
       <c r="F181" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G181" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H181" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J181" s="0">
-        <v>251.23050000000001</v>
+        <v>104.34829999999999</v>
       </c>
     </row>
     <row r="182">
@@ -8502,25 +8502,25 @@
         <v>6</v>
       </c>
       <c r="D182" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E182" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F182" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G182" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H182" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J182" s="0">
-        <v>104.34829999999999</v>
+        <v>5196.1244999999999</v>
       </c>
     </row>
     <row r="183">
@@ -8540,19 +8540,19 @@
         <v>27</v>
       </c>
       <c r="F183" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G183" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H183" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J183" s="0">
-        <v>5196.1244999999999</v>
+        <v>2798.9209000000001</v>
       </c>
     </row>
     <row r="184">
@@ -8569,22 +8569,22 @@
         <v>12</v>
       </c>
       <c r="E184" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F184" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G184" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H184" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J184" s="0">
-        <v>2798.9209000000001</v>
+        <v>554.0693</v>
       </c>
     </row>
     <row r="185">
@@ -8604,19 +8604,19 @@
         <v>28</v>
       </c>
       <c r="F185" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G185" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H185" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J185" s="0">
-        <v>554.0693</v>
+        <v>97.465900000000005</v>
       </c>
     </row>
     <row r="186">
@@ -8633,22 +8633,22 @@
         <v>12</v>
       </c>
       <c r="E186" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F186" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G186" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H186" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J186" s="0">
-        <v>97.465900000000005</v>
+        <v>413.24349999999998</v>
       </c>
     </row>
     <row r="187">
@@ -8668,19 +8668,19 @@
         <v>29</v>
       </c>
       <c r="F187" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G187" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H187" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J187" s="0">
-        <v>413.24349999999998</v>
+        <v>390.69720000000001</v>
       </c>
     </row>
     <row r="188">
@@ -8700,19 +8700,19 @@
         <v>29</v>
       </c>
       <c r="F188" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G188" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H188" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J188" s="0">
-        <v>390.69720000000001</v>
+        <v>384.44110000000001</v>
       </c>
     </row>
     <row r="189">
@@ -8732,19 +8732,19 @@
         <v>29</v>
       </c>
       <c r="F189" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G189" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H189" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="J189" s="0">
-        <v>384.44110000000001</v>
+        <v>369.39760000000001</v>
       </c>
     </row>
     <row r="190">
@@ -8764,19 +8764,19 @@
         <v>29</v>
       </c>
       <c r="F190" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G190" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H190" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="J190" s="0">
-        <v>369.39760000000001</v>
+        <v>355.85449999999997</v>
       </c>
     </row>
     <row r="191">
@@ -8796,19 +8796,19 @@
         <v>29</v>
       </c>
       <c r="F191" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G191" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H191" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J191" s="0">
-        <v>355.85449999999997</v>
+        <v>332.20139999999998</v>
       </c>
     </row>
     <row r="192">
@@ -8828,19 +8828,19 @@
         <v>29</v>
       </c>
       <c r="F192" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G192" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J192" s="0">
-        <v>332.20139999999998</v>
+        <v>304.4751</v>
       </c>
     </row>
     <row r="193">
@@ -8860,19 +8860,19 @@
         <v>29</v>
       </c>
       <c r="F193" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G193" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H193" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J193" s="0">
-        <v>304.4751</v>
+        <v>263.24160000000001</v>
       </c>
     </row>
     <row r="194">
@@ -8883,28 +8883,28 @@
         <v>4</v>
       </c>
       <c r="C194" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D194" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E194" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F194" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G194" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H194" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J194" s="0">
-        <v>263.24160000000001</v>
+        <v>5598.6216000000004</v>
       </c>
     </row>
     <row r="195">
@@ -8924,19 +8924,19 @@
         <v>27</v>
       </c>
       <c r="F195" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G195" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H195" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="J195" s="0">
-        <v>5598.6216000000004</v>
+        <v>4298.6826000000001</v>
       </c>
     </row>
     <row r="196">
@@ -8953,22 +8953,22 @@
         <v>13</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F196" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G196" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H196" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J196" s="0">
-        <v>4298.6826000000001</v>
+        <v>831.18269999999996</v>
       </c>
     </row>
     <row r="197">
@@ -8988,19 +8988,19 @@
         <v>28</v>
       </c>
       <c r="F197" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G197" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H197" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="J197" s="0">
-        <v>831.18269999999996</v>
+        <v>746.42259999999999</v>
       </c>
     </row>
     <row r="198">
@@ -9017,22 +9017,22 @@
         <v>13</v>
       </c>
       <c r="E198" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F198" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G198" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H198" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J198" s="0">
-        <v>746.42259999999999</v>
+        <v>477.65440000000001</v>
       </c>
     </row>
     <row r="199">
@@ -9052,19 +9052,19 @@
         <v>29</v>
       </c>
       <c r="F199" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G199" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H199" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J199" s="0">
-        <v>477.65440000000001</v>
+        <v>455.09550000000002</v>
       </c>
     </row>
     <row r="200">
@@ -9084,19 +9084,19 @@
         <v>29</v>
       </c>
       <c r="F200" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G200" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H200" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J200" s="0">
-        <v>455.09550000000002</v>
+        <v>442.9828</v>
       </c>
     </row>
     <row r="201">
@@ -9116,19 +9116,19 @@
         <v>29</v>
       </c>
       <c r="F201" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G201" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J201" s="0">
-        <v>442.9828</v>
+        <v>403.95710000000003</v>
       </c>
     </row>
     <row r="202">
@@ -9148,19 +9148,19 @@
         <v>29</v>
       </c>
       <c r="F202" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G202" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H202" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J202" s="0">
-        <v>403.95710000000003</v>
+        <v>353.99869999999999</v>
       </c>
     </row>
     <row r="203">
@@ -9180,19 +9180,19 @@
         <v>29</v>
       </c>
       <c r="F203" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G203" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H203" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="J203" s="0">
-        <v>353.99869999999999</v>
+        <v>282.62110000000001</v>
       </c>
     </row>
     <row r="204">
@@ -9212,19 +9212,19 @@
         <v>29</v>
       </c>
       <c r="F204" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G204" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H204" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J204" s="0">
-        <v>282.62110000000001</v>
+        <v>251.0352</v>
       </c>
     </row>
     <row r="205">
@@ -9244,19 +9244,19 @@
         <v>29</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G205" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H205" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J205" s="0">
-        <v>251.0352</v>
+        <v>226.5855</v>
       </c>
     </row>
     <row r="206">
@@ -9270,25 +9270,25 @@
         <v>7</v>
       </c>
       <c r="D206" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E206" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F206" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G206" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H206" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="J206" s="0">
-        <v>226.5855</v>
+        <v>3073.4854</v>
       </c>
     </row>
     <row r="207">
@@ -9308,19 +9308,19 @@
         <v>27</v>
       </c>
       <c r="F207" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G207" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H207" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="J207" s="0">
-        <v>3073.4854</v>
+        <v>1817.3022000000001</v>
       </c>
     </row>
     <row r="208">
@@ -9337,22 +9337,22 @@
         <v>14</v>
       </c>
       <c r="E208" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F208" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G208" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H208" s="0" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J208" s="0">
-        <v>1817.3022000000001</v>
+        <v>831.18269999999996</v>
       </c>
     </row>
     <row r="209">
@@ -9369,7 +9369,7 @@
         <v>14</v>
       </c>
       <c r="E209" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F209" s="0" t="s">
         <v>31</v>
@@ -9378,13 +9378,13 @@
         <v>40</v>
       </c>
       <c r="H209" s="0" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J209" s="0">
-        <v>831.18269999999996</v>
+        <v>444.28719999999999</v>
       </c>
     </row>
     <row r="210">
@@ -9404,19 +9404,19 @@
         <v>29</v>
       </c>
       <c r="F210" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G210" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J210" s="0">
-        <v>444.28719999999999</v>
+        <v>406.01569999999998</v>
       </c>
     </row>
     <row r="211">
@@ -9436,19 +9436,19 @@
         <v>29</v>
       </c>
       <c r="F211" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G211" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H211" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="J211" s="0">
-        <v>406.01569999999998</v>
+        <v>377.0512</v>
       </c>
     </row>
     <row r="212">
@@ -9468,19 +9468,19 @@
         <v>29</v>
       </c>
       <c r="F212" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G212" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H212" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J212" s="0">
-        <v>377.0512</v>
+        <v>370.54059999999998</v>
       </c>
     </row>
     <row r="213">
@@ -9500,19 +9500,19 @@
         <v>29</v>
       </c>
       <c r="F213" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G213" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J213" s="0">
-        <v>370.54059999999998</v>
+        <v>364.45699999999999</v>
       </c>
     </row>
     <row r="214">
@@ -9532,19 +9532,19 @@
         <v>29</v>
       </c>
       <c r="F214" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G214" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J214" s="0">
-        <v>364.45699999999999</v>
+        <v>357.5231</v>
       </c>
     </row>
     <row r="215">
@@ -9564,19 +9564,19 @@
         <v>29</v>
       </c>
       <c r="F215" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G215" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="J215" s="0">
-        <v>357.5231</v>
+        <v>289.80360000000002</v>
       </c>
     </row>
     <row r="216">
@@ -9596,19 +9596,19 @@
         <v>29</v>
       </c>
       <c r="F216" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G216" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J216" s="0">
-        <v>289.80360000000002</v>
+        <v>205.23990000000001</v>
       </c>
     </row>
     <row r="217">
@@ -9622,25 +9622,25 @@
         <v>7</v>
       </c>
       <c r="D217" s="0" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F217" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G217" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="J217" s="0">
-        <v>205.23990000000001</v>
+        <v>5904.6377000000002</v>
       </c>
     </row>
     <row r="218">
@@ -9660,19 +9660,19 @@
         <v>27</v>
       </c>
       <c r="F218" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G218" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H218" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="J218" s="0">
-        <v>5904.6377000000002</v>
+        <v>4907.7012000000004</v>
       </c>
     </row>
     <row r="219">
@@ -9689,22 +9689,22 @@
         <v>23</v>
       </c>
       <c r="E219" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F219" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G219" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H219" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J219" s="0">
-        <v>4907.7012000000004</v>
+        <v>202.81960000000001</v>
       </c>
     </row>
     <row r="220">
@@ -9721,7 +9721,7 @@
         <v>23</v>
       </c>
       <c r="E220" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F220" s="0" t="s">
         <v>31</v>
@@ -9730,13 +9730,13 @@
         <v>40</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="J220" s="0">
-        <v>202.81960000000001</v>
+        <v>383.23849999999999</v>
       </c>
     </row>
     <row r="221">
@@ -9756,19 +9756,19 @@
         <v>29</v>
       </c>
       <c r="F221" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G221" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="J221" s="0">
-        <v>383.23849999999999</v>
+        <v>363.8911</v>
       </c>
     </row>
     <row r="222">
@@ -9788,19 +9788,19 @@
         <v>29</v>
       </c>
       <c r="F222" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G222" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J222" s="0">
-        <v>363.8911</v>
+        <v>355.88670000000002</v>
       </c>
     </row>
     <row r="223">
@@ -9820,19 +9820,19 @@
         <v>29</v>
       </c>
       <c r="F223" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G223" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H223" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J223" s="0">
-        <v>355.88670000000002</v>
+        <v>351.3347</v>
       </c>
     </row>
     <row r="224">
@@ -9852,19 +9852,19 @@
         <v>29</v>
       </c>
       <c r="F224" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G224" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H224" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="J224" s="0">
-        <v>351.3347</v>
+        <v>333.8578</v>
       </c>
     </row>
     <row r="225">
@@ -9884,19 +9884,19 @@
         <v>29</v>
       </c>
       <c r="F225" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G225" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H225" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="J225" s="0">
-        <v>333.8578</v>
+        <v>313.44380000000001</v>
       </c>
     </row>
     <row r="226">
@@ -9916,19 +9916,19 @@
         <v>29</v>
       </c>
       <c r="F226" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G226" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H226" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J226" s="0">
-        <v>313.44380000000001</v>
+        <v>238.27189999999999</v>
       </c>
     </row>
     <row r="227">
@@ -9948,19 +9948,19 @@
         <v>29</v>
       </c>
       <c r="F227" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G227" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H227" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J227" s="0">
-        <v>238.27189999999999</v>
+        <v>141.53020000000001</v>
       </c>
     </row>
     <row r="228">
@@ -9974,25 +9974,25 @@
         <v>7</v>
       </c>
       <c r="D228" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F228" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G228" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H228" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J228" s="0">
-        <v>141.53020000000001</v>
+        <v>6671.5464000000002</v>
       </c>
     </row>
     <row r="229">
@@ -10012,19 +10012,19 @@
         <v>27</v>
       </c>
       <c r="F229" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G229" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H229" s="0" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J229" s="0">
-        <v>6671.5464000000002</v>
+        <v>2604.8850000000002</v>
       </c>
     </row>
     <row r="230">
@@ -10041,22 +10041,22 @@
         <v>24</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F230" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G230" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H230" s="0" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="J230" s="0">
-        <v>2604.8850000000002</v>
+        <v>539.66269999999997</v>
       </c>
     </row>
     <row r="231">
@@ -10073,7 +10073,7 @@
         <v>24</v>
       </c>
       <c r="E231" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F231" s="0" t="s">
         <v>31</v>
@@ -10082,13 +10082,13 @@
         <v>40</v>
       </c>
       <c r="H231" s="0" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="J231" s="0">
-        <v>539.66269999999997</v>
+        <v>429.82010000000002</v>
       </c>
     </row>
     <row r="232">
@@ -10108,19 +10108,19 @@
         <v>29</v>
       </c>
       <c r="F232" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G232" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H232" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J232" s="0">
-        <v>429.82010000000002</v>
+        <v>421.38249999999999</v>
       </c>
     </row>
     <row r="233">
@@ -10140,19 +10140,19 @@
         <v>29</v>
       </c>
       <c r="F233" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G233" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H233" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="J233" s="0">
-        <v>421.38249999999999</v>
+        <v>417.74880000000002</v>
       </c>
     </row>
     <row r="234">
@@ -10172,19 +10172,19 @@
         <v>29</v>
       </c>
       <c r="F234" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G234" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H234" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="J234" s="0">
-        <v>417.74880000000002</v>
+        <v>393.11059999999998</v>
       </c>
     </row>
     <row r="235">
@@ -10204,19 +10204,19 @@
         <v>29</v>
       </c>
       <c r="F235" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G235" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H235" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="J235" s="0">
-        <v>393.11059999999998</v>
+        <v>392.10489999999999</v>
       </c>
     </row>
     <row r="236">
@@ -10236,19 +10236,19 @@
         <v>29</v>
       </c>
       <c r="F236" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G236" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H236" s="0" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J236" s="0">
-        <v>392.10489999999999</v>
+        <v>387.5043</v>
       </c>
     </row>
     <row r="237">
@@ -10268,19 +10268,19 @@
         <v>29</v>
       </c>
       <c r="F237" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G237" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H237" s="0" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="J237" s="0">
-        <v>387.5043</v>
+        <v>215.23259999999999</v>
       </c>
     </row>
     <row r="238">
@@ -10291,28 +10291,28 @@
         <v>4</v>
       </c>
       <c r="C238" s="0" t="s">
-        <v>7</v>
+        <v>655</v>
       </c>
       <c r="D238" s="0" t="s">
-        <v>24</v>
+        <v>801</v>
       </c>
       <c r="E238" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F238" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G238" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H238" s="0" t="s">
-        <v>256</v>
+        <v>693</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>557</v>
+        <v>804</v>
       </c>
       <c r="J238" s="0">
-        <v>215.23259999999999</v>
+        <v>6179.7012000000004</v>
       </c>
     </row>
     <row r="239">
@@ -10332,19 +10332,19 @@
         <v>27</v>
       </c>
       <c r="F239" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G239" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H239" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J239" s="0">
-        <v>6179.7012000000004</v>
+        <v>2590.0304999999999</v>
       </c>
     </row>
     <row r="240">
@@ -10361,22 +10361,22 @@
         <v>801</v>
       </c>
       <c r="E240" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F240" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G240" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H240" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="J240" s="0">
-        <v>2590.0304999999999</v>
+        <v>1052.7577000000001</v>
       </c>
     </row>
     <row r="241">
@@ -10396,19 +10396,19 @@
         <v>28</v>
       </c>
       <c r="F241" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G241" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H241" s="0" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="J241" s="0">
-        <v>1052.7577000000001</v>
+        <v>663.33749999999998</v>
       </c>
     </row>
     <row r="242">
@@ -10425,22 +10425,22 @@
         <v>801</v>
       </c>
       <c r="E242" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F242" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G242" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H242" s="0" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="J242" s="0">
-        <v>663.33749999999998</v>
+        <v>506.81569999999999</v>
       </c>
     </row>
     <row r="243">
@@ -10460,19 +10460,19 @@
         <v>29</v>
       </c>
       <c r="F243" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G243" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H243" s="0" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="J243" s="0">
-        <v>506.81569999999999</v>
+        <v>408.8279</v>
       </c>
     </row>
     <row r="244">
@@ -10492,19 +10492,19 @@
         <v>29</v>
       </c>
       <c r="F244" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G244" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H244" s="0" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="J244" s="0">
-        <v>408.8279</v>
+        <v>402.4606</v>
       </c>
     </row>
     <row r="245">
@@ -10524,19 +10524,19 @@
         <v>29</v>
       </c>
       <c r="F245" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G245" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H245" s="0" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="J245" s="0">
-        <v>402.4606</v>
+        <v>395.95499999999999</v>
       </c>
     </row>
     <row r="246">
@@ -10556,19 +10556,19 @@
         <v>29</v>
       </c>
       <c r="F246" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G246" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H246" s="0" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="J246" s="0">
-        <v>395.95499999999999</v>
+        <v>384.18630000000002</v>
       </c>
     </row>
     <row r="247">
@@ -10588,19 +10588,19 @@
         <v>29</v>
       </c>
       <c r="F247" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G247" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H247" s="0" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="J247" s="0">
-        <v>384.18630000000002</v>
+        <v>337.53550000000001</v>
       </c>
     </row>
     <row r="248">
@@ -10620,19 +10620,19 @@
         <v>29</v>
       </c>
       <c r="F248" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G248" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H248" s="0" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="J248" s="0">
-        <v>337.53550000000001</v>
+        <v>304.91230000000002</v>
       </c>
     </row>
     <row r="249">
@@ -10652,19 +10652,19 @@
         <v>29</v>
       </c>
       <c r="F249" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G249" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H249" s="0" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="J249" s="0">
-        <v>304.91230000000002</v>
+        <v>125.54000000000001</v>
       </c>
     </row>
     <row r="250">
@@ -10678,25 +10678,25 @@
         <v>655</v>
       </c>
       <c r="D250" s="0" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E250" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F250" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G250" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H250" s="0" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="J250" s="0">
-        <v>125.54000000000001</v>
+        <v>5385.1138000000001</v>
       </c>
     </row>
     <row r="251">
@@ -10716,19 +10716,19 @@
         <v>27</v>
       </c>
       <c r="F251" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G251" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H251" s="0" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="J251" s="0">
-        <v>5385.1138000000001</v>
+        <v>2843.9126000000001</v>
       </c>
     </row>
     <row r="252">
@@ -10745,22 +10745,22 @@
         <v>802</v>
       </c>
       <c r="E252" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F252" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G252" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H252" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="J252" s="0">
-        <v>2843.9126000000001</v>
+        <v>710.74549999999999</v>
       </c>
     </row>
     <row r="253">
@@ -10780,19 +10780,19 @@
         <v>28</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G253" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H253" s="0" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="J253" s="0">
-        <v>710.74549999999999</v>
+        <v>550.2423</v>
       </c>
     </row>
     <row r="254">
@@ -10809,22 +10809,22 @@
         <v>802</v>
       </c>
       <c r="E254" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F254" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G254" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H254" s="0" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="J254" s="0">
-        <v>550.2423</v>
+        <v>438.92590000000001</v>
       </c>
     </row>
     <row r="255">
@@ -10844,19 +10844,19 @@
         <v>29</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G255" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H255" s="0" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="J255" s="0">
-        <v>438.92590000000001</v>
+        <v>423.42290000000003</v>
       </c>
     </row>
     <row r="256">
@@ -10876,19 +10876,19 @@
         <v>29</v>
       </c>
       <c r="F256" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G256" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H256" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="J256" s="0">
-        <v>423.42290000000003</v>
+        <v>403.89089999999999</v>
       </c>
     </row>
     <row r="257">
@@ -10908,19 +10908,19 @@
         <v>29</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G257" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H257" s="0" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="J257" s="0">
-        <v>403.89089999999999</v>
+        <v>391.21699999999999</v>
       </c>
     </row>
     <row r="258">
@@ -10940,19 +10940,19 @@
         <v>29</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G258" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H258" s="0" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="J258" s="0">
-        <v>391.21699999999999</v>
+        <v>383.9436</v>
       </c>
     </row>
     <row r="259">
@@ -10972,19 +10972,19 @@
         <v>29</v>
       </c>
       <c r="F259" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G259" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H259" s="0" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="J259" s="0">
-        <v>383.9436</v>
+        <v>312.447</v>
       </c>
     </row>
     <row r="260">
@@ -11004,19 +11004,19 @@
         <v>29</v>
       </c>
       <c r="F260" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G260" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H260" s="0" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="J260" s="0">
-        <v>312.447</v>
+        <v>309.3852</v>
       </c>
     </row>
     <row r="261">
@@ -11036,19 +11036,19 @@
         <v>29</v>
       </c>
       <c r="F261" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G261" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H261" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="J261" s="0">
-        <v>309.3852</v>
+        <v>235.6891</v>
       </c>
     </row>
     <row r="262">
@@ -11062,25 +11062,25 @@
         <v>655</v>
       </c>
       <c r="D262" s="0" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E262" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F262" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G262" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H262" s="0" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="J262" s="0">
-        <v>235.6891</v>
+        <v>6293.9867999999997</v>
       </c>
     </row>
     <row r="263">
@@ -11100,19 +11100,19 @@
         <v>27</v>
       </c>
       <c r="F263" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G263" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H263" s="0" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="J263" s="0">
-        <v>6293.9867999999997</v>
+        <v>5358.5902999999999</v>
       </c>
     </row>
     <row r="264">
@@ -11129,22 +11129,22 @@
         <v>803</v>
       </c>
       <c r="E264" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F264" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G264" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H264" s="0" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="J264" s="0">
-        <v>5358.5902999999999</v>
+        <v>577.04179999999997</v>
       </c>
     </row>
     <row r="265">
@@ -11164,19 +11164,19 @@
         <v>28</v>
       </c>
       <c r="F265" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G265" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H265" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="J265" s="0">
-        <v>577.04179999999997</v>
+        <v>518.29719999999998</v>
       </c>
     </row>
     <row r="266">
@@ -11193,22 +11193,22 @@
         <v>803</v>
       </c>
       <c r="E266" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F266" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G266" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H266" s="0" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="J266" s="0">
-        <v>518.29719999999998</v>
+        <v>427.73379999999997</v>
       </c>
     </row>
     <row r="267">
@@ -11228,19 +11228,19 @@
         <v>29</v>
       </c>
       <c r="F267" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G267" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H267" s="0" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="J267" s="0">
-        <v>427.73379999999997</v>
+        <v>404.26459999999997</v>
       </c>
     </row>
     <row r="268">
@@ -11260,19 +11260,19 @@
         <v>29</v>
       </c>
       <c r="F268" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G268" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H268" s="0" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="J268" s="0">
-        <v>404.26459999999997</v>
+        <v>398.51589999999999</v>
       </c>
     </row>
     <row r="269">
@@ -11292,19 +11292,19 @@
         <v>29</v>
       </c>
       <c r="F269" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G269" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H269" s="0" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="J269" s="0">
-        <v>398.51589999999999</v>
+        <v>392.9486</v>
       </c>
     </row>
     <row r="270">
@@ -11324,19 +11324,19 @@
         <v>29</v>
       </c>
       <c r="F270" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G270" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H270" s="0" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="J270" s="0">
-        <v>392.9486</v>
+        <v>382.86340000000001</v>
       </c>
     </row>
     <row r="271">
@@ -11356,19 +11356,19 @@
         <v>29</v>
       </c>
       <c r="F271" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G271" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H271" s="0" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="J271" s="0">
-        <v>382.86340000000001</v>
+        <v>368.97640000000001</v>
       </c>
     </row>
     <row r="272">
@@ -11388,19 +11388,19 @@
         <v>29</v>
       </c>
       <c r="F272" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G272" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H272" s="0" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="J272" s="0">
-        <v>368.97640000000001</v>
+        <v>347.17689999999999</v>
       </c>
     </row>
     <row r="273">
@@ -11420,19 +11420,19 @@
         <v>29</v>
       </c>
       <c r="F273" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G273" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H273" s="0" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="J273" s="0">
-        <v>347.17689999999999</v>
+        <v>328.54599999999999</v>
       </c>
     </row>
     <row r="274">
@@ -11443,28 +11443,28 @@
         <v>4</v>
       </c>
       <c r="C274" s="0" t="s">
-        <v>655</v>
+        <v>8</v>
       </c>
       <c r="D274" s="0" t="s">
-        <v>803</v>
+        <v>15</v>
       </c>
       <c r="E274" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F274" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G274" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H274" s="0" t="s">
-        <v>728</v>
+        <v>257</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>839</v>
+        <v>558</v>
       </c>
       <c r="J274" s="0">
-        <v>328.54599999999999</v>
+        <v>5568.125</v>
       </c>
     </row>
     <row r="275">
@@ -11484,19 +11484,19 @@
         <v>27</v>
       </c>
       <c r="F275" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G275" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H275" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="J275" s="0">
-        <v>5568.125</v>
+        <v>2316.6012999999998</v>
       </c>
     </row>
     <row r="276">
@@ -11513,22 +11513,22 @@
         <v>15</v>
       </c>
       <c r="E276" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F276" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G276" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H276" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J276" s="0">
-        <v>2316.6012999999998</v>
+        <v>504.78460000000001</v>
       </c>
     </row>
     <row r="277">
@@ -11548,19 +11548,19 @@
         <v>28</v>
       </c>
       <c r="F277" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G277" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H277" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="J277" s="0">
-        <v>504.78460000000001</v>
+        <v>445.50999999999999</v>
       </c>
     </row>
     <row r="278">
@@ -11577,22 +11577,22 @@
         <v>15</v>
       </c>
       <c r="E278" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F278" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G278" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H278" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="J278" s="0">
-        <v>445.50999999999999</v>
+        <v>401.56920000000002</v>
       </c>
     </row>
     <row r="279">
@@ -11612,19 +11612,19 @@
         <v>29</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G279" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H279" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="J279" s="0">
-        <v>401.56920000000002</v>
+        <v>392.42399999999998</v>
       </c>
     </row>
     <row r="280">
@@ -11644,19 +11644,19 @@
         <v>29</v>
       </c>
       <c r="F280" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G280" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H280" s="0" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="J280" s="0">
-        <v>392.42399999999998</v>
+        <v>368.18880000000001</v>
       </c>
     </row>
     <row r="281">
@@ -11676,19 +11676,19 @@
         <v>29</v>
       </c>
       <c r="F281" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G281" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="J281" s="0">
-        <v>368.18880000000001</v>
+        <v>366.78320000000002</v>
       </c>
     </row>
     <row r="282">
@@ -11708,19 +11708,19 @@
         <v>29</v>
       </c>
       <c r="F282" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G282" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H282" s="0" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="J282" s="0">
-        <v>366.78320000000002</v>
+        <v>361.8997</v>
       </c>
     </row>
     <row r="283">
@@ -11740,19 +11740,19 @@
         <v>29</v>
       </c>
       <c r="F283" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G283" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H283" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="J283" s="0">
-        <v>361.8997</v>
+        <v>322.42989999999998</v>
       </c>
     </row>
     <row r="284">
@@ -11772,19 +11772,19 @@
         <v>29</v>
       </c>
       <c r="F284" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G284" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H284" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J284" s="0">
-        <v>322.42989999999998</v>
+        <v>308.6019</v>
       </c>
     </row>
     <row r="285">
@@ -11804,19 +11804,19 @@
         <v>29</v>
       </c>
       <c r="F285" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G285" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H285" s="0" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="J285" s="0">
-        <v>308.6019</v>
+        <v>260.48289999999997</v>
       </c>
     </row>
     <row r="286">
@@ -11830,25 +11830,25 @@
         <v>8</v>
       </c>
       <c r="D286" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E286" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F286" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G286" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H286" s="0" t="s">
-        <v>268</v>
+        <v>103</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="J286" s="0">
-        <v>260.48289999999997</v>
+        <v>6411.3008</v>
       </c>
     </row>
     <row r="287">
@@ -11868,19 +11868,19 @@
         <v>27</v>
       </c>
       <c r="F287" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G287" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H287" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="J287" s="0">
-        <v>6411.3008</v>
+        <v>5363.7114000000001</v>
       </c>
     </row>
     <row r="288">
@@ -11897,22 +11897,22 @@
         <v>16</v>
       </c>
       <c r="E288" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F288" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G288" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H288" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="J288" s="0">
-        <v>5363.7114000000001</v>
+        <v>561.40689999999995</v>
       </c>
     </row>
     <row r="289">
@@ -11929,7 +11929,7 @@
         <v>16</v>
       </c>
       <c r="E289" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F289" s="0" t="s">
         <v>31</v>
@@ -11938,13 +11938,13 @@
         <v>40</v>
       </c>
       <c r="H289" s="0" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="J289" s="0">
-        <v>561.40689999999995</v>
+        <v>465.0847</v>
       </c>
     </row>
     <row r="290">
@@ -11961,22 +11961,22 @@
         <v>16</v>
       </c>
       <c r="E290" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F290" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G290" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H290" s="0" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="J290" s="0">
-        <v>495.09269999999998</v>
+        <v>432.71969999999999</v>
       </c>
     </row>
     <row r="291">
@@ -11996,19 +11996,19 @@
         <v>29</v>
       </c>
       <c r="F291" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G291" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H291" s="0" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="J291" s="0">
-        <v>465.0847</v>
+        <v>403.6884</v>
       </c>
     </row>
     <row r="292">
@@ -12028,19 +12028,19 @@
         <v>29</v>
       </c>
       <c r="F292" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G292" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H292" s="0" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="J292" s="0">
-        <v>432.71969999999999</v>
+        <v>393.85660000000001</v>
       </c>
     </row>
     <row r="293">
@@ -12060,19 +12060,19 @@
         <v>29</v>
       </c>
       <c r="F293" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G293" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H293" s="0" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="J293" s="0">
-        <v>403.6884</v>
+        <v>328.83640000000003</v>
       </c>
     </row>
     <row r="294">
@@ -12092,19 +12092,19 @@
         <v>29</v>
       </c>
       <c r="F294" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G294" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H294" s="0" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="J294" s="0">
-        <v>393.85660000000001</v>
+        <v>289.99919999999997</v>
       </c>
     </row>
     <row r="295">
@@ -12124,19 +12124,19 @@
         <v>29</v>
       </c>
       <c r="F295" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G295" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H295" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="J295" s="0">
-        <v>328.83640000000003</v>
+        <v>253.50819999999999</v>
       </c>
     </row>
     <row r="296">
@@ -12156,19 +12156,19 @@
         <v>29</v>
       </c>
       <c r="F296" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G296" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H296" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="J296" s="0">
-        <v>289.99919999999997</v>
+        <v>156.39179999999999</v>
       </c>
     </row>
     <row r="297">
@@ -12182,25 +12182,25 @@
         <v>8</v>
       </c>
       <c r="D297" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E297" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F297" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G297" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H297" s="0" t="s">
-        <v>113</v>
+        <v>269</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="J297" s="0">
-        <v>253.50819999999999</v>
+        <v>5610.5132000000003</v>
       </c>
     </row>
     <row r="298">
@@ -12214,25 +12214,25 @@
         <v>8</v>
       </c>
       <c r="D298" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E298" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F298" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G298" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H298" s="0" t="s">
-        <v>114</v>
+        <v>270</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="J298" s="0">
-        <v>156.39179999999999</v>
+        <v>2526.6718999999998</v>
       </c>
     </row>
     <row r="299">
@@ -12249,7 +12249,7 @@
         <v>17</v>
       </c>
       <c r="E299" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F299" s="0" t="s">
         <v>31</v>
@@ -12258,13 +12258,13 @@
         <v>40</v>
       </c>
       <c r="H299" s="0" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="J299" s="0">
-        <v>5610.5132000000003</v>
+        <v>663.2672</v>
       </c>
     </row>
     <row r="300">
@@ -12281,7 +12281,7 @@
         <v>17</v>
       </c>
       <c r="E300" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F300" s="0" t="s">
         <v>32</v>
@@ -12290,13 +12290,13 @@
         <v>41</v>
       </c>
       <c r="H300" s="0" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="J300" s="0">
-        <v>2526.6718999999998</v>
+        <v>553.69179999999994</v>
       </c>
     </row>
     <row r="301">
@@ -12313,7 +12313,7 @@
         <v>17</v>
       </c>
       <c r="E301" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F301" s="0" t="s">
         <v>31</v>
@@ -12322,13 +12322,13 @@
         <v>40</v>
       </c>
       <c r="H301" s="0" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="J301" s="0">
-        <v>663.2672</v>
+        <v>436.38159999999999</v>
       </c>
     </row>
     <row r="302">
@@ -12345,22 +12345,22 @@
         <v>17</v>
       </c>
       <c r="E302" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F302" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G302" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H302" s="0" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="J302" s="0">
-        <v>553.69179999999994</v>
+        <v>411.78269999999998</v>
       </c>
     </row>
     <row r="303">
@@ -12380,19 +12380,19 @@
         <v>29</v>
       </c>
       <c r="F303" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G303" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H303" s="0" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="J303" s="0">
-        <v>436.38159999999999</v>
+        <v>407.44670000000002</v>
       </c>
     </row>
     <row r="304">
@@ -12412,19 +12412,19 @@
         <v>29</v>
       </c>
       <c r="F304" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G304" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H304" s="0" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="J304" s="0">
-        <v>411.78269999999998</v>
+        <v>390.17970000000003</v>
       </c>
     </row>
     <row r="305">
@@ -12444,19 +12444,19 @@
         <v>29</v>
       </c>
       <c r="F305" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G305" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H305" s="0" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="J305" s="0">
-        <v>407.44670000000002</v>
+        <v>379.34300000000002</v>
       </c>
     </row>
     <row r="306">
@@ -12476,19 +12476,19 @@
         <v>29</v>
       </c>
       <c r="F306" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G306" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H306" s="0" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="J306" s="0">
-        <v>390.17970000000003</v>
+        <v>378.32549999999998</v>
       </c>
     </row>
     <row r="307">
@@ -12508,19 +12508,19 @@
         <v>29</v>
       </c>
       <c r="F307" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G307" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H307" s="0" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="J307" s="0">
-        <v>379.34300000000002</v>
+        <v>248.1077</v>
       </c>
     </row>
     <row r="308">
@@ -12540,19 +12540,19 @@
         <v>29</v>
       </c>
       <c r="F308" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G308" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H308" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="J308" s="0">
-        <v>378.32549999999998</v>
+        <v>155.72280000000001</v>
       </c>
     </row>
     <row r="309">
@@ -12566,25 +12566,25 @@
         <v>8</v>
       </c>
       <c r="D309" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E309" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F309" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G309" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H309" s="0" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="J309" s="0">
-        <v>248.1077</v>
+        <v>6378.5679</v>
       </c>
     </row>
     <row r="310">
@@ -12598,25 +12598,25 @@
         <v>8</v>
       </c>
       <c r="D310" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E310" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F310" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G310" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H310" s="0" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="J310" s="0">
-        <v>155.72280000000001</v>
+        <v>3677.8054000000002</v>
       </c>
     </row>
     <row r="311">
@@ -12633,7 +12633,7 @@
         <v>25</v>
       </c>
       <c r="E311" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F311" s="0" t="s">
         <v>31</v>
@@ -12642,13 +12642,13 @@
         <v>40</v>
       </c>
       <c r="H311" s="0" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="J311" s="0">
-        <v>6378.5679</v>
+        <v>990.75639999999999</v>
       </c>
     </row>
     <row r="312">
@@ -12665,7 +12665,7 @@
         <v>25</v>
       </c>
       <c r="E312" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F312" s="0" t="s">
         <v>32</v>
@@ -12674,13 +12674,13 @@
         <v>41</v>
       </c>
       <c r="H312" s="0" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="J312" s="0">
-        <v>3677.8054000000002</v>
+        <v>912.61609999999996</v>
       </c>
     </row>
     <row r="313">
@@ -12697,7 +12697,7 @@
         <v>25</v>
       </c>
       <c r="E313" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F313" s="0" t="s">
         <v>31</v>
@@ -12706,13 +12706,13 @@
         <v>40</v>
       </c>
       <c r="H313" s="0" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="J313" s="0">
-        <v>990.75639999999999</v>
+        <v>448.30200000000002</v>
       </c>
     </row>
     <row r="314">
@@ -12729,22 +12729,22 @@
         <v>25</v>
       </c>
       <c r="E314" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F314" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G314" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H314" s="0" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="J314" s="0">
-        <v>912.61609999999996</v>
+        <v>415.84109999999998</v>
       </c>
     </row>
     <row r="315">
@@ -12764,19 +12764,19 @@
         <v>29</v>
       </c>
       <c r="F315" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G315" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H315" s="0" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="J315" s="0">
-        <v>448.30200000000002</v>
+        <v>380.94420000000002</v>
       </c>
     </row>
     <row r="316">
@@ -12796,19 +12796,19 @@
         <v>29</v>
       </c>
       <c r="F316" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G316" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H316" s="0" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="J316" s="0">
-        <v>415.84109999999998</v>
+        <v>359.60860000000002</v>
       </c>
     </row>
     <row r="317">
@@ -12828,19 +12828,19 @@
         <v>29</v>
       </c>
       <c r="F317" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G317" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H317" s="0" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="J317" s="0">
-        <v>380.94420000000002</v>
+        <v>338.8168</v>
       </c>
     </row>
     <row r="318">
@@ -12860,19 +12860,19 @@
         <v>29</v>
       </c>
       <c r="F318" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G318" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H318" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="J318" s="0">
-        <v>359.60860000000002</v>
+        <v>320.63470000000001</v>
       </c>
     </row>
     <row r="319">
@@ -12892,19 +12892,19 @@
         <v>29</v>
       </c>
       <c r="F319" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G319" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H319" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="J319" s="0">
-        <v>338.8168</v>
+        <v>287.04489999999999</v>
       </c>
     </row>
     <row r="320">
@@ -12924,19 +12924,19 @@
         <v>29</v>
       </c>
       <c r="F320" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G320" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H320" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="J320" s="0">
-        <v>320.63470000000001</v>
+        <v>107.8788</v>
       </c>
     </row>
     <row r="321">
@@ -12947,28 +12947,28 @@
         <v>4</v>
       </c>
       <c r="C321" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D321" s="0" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E321" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F321" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G321" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H321" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="J321" s="0">
-        <v>287.04489999999999</v>
+        <v>5099.2568000000001</v>
       </c>
     </row>
     <row r="322">
@@ -12979,28 +12979,28 @@
         <v>4</v>
       </c>
       <c r="C322" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D322" s="0" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E322" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F322" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G322" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H322" s="0" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="J322" s="0">
-        <v>107.8788</v>
+        <v>2383.1239999999998</v>
       </c>
     </row>
     <row r="323">
@@ -13017,7 +13017,7 @@
         <v>18</v>
       </c>
       <c r="E323" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F323" s="0" t="s">
         <v>31</v>
@@ -13026,13 +13026,13 @@
         <v>40</v>
       </c>
       <c r="H323" s="0" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="J323" s="0">
-        <v>5099.2568000000001</v>
+        <v>670.93709999999999</v>
       </c>
     </row>
     <row r="324">
@@ -13049,7 +13049,7 @@
         <v>18</v>
       </c>
       <c r="E324" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F324" s="0" t="s">
         <v>32</v>
@@ -13058,13 +13058,13 @@
         <v>41</v>
       </c>
       <c r="H324" s="0" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="J324" s="0">
-        <v>2383.1239999999998</v>
+        <v>459.24430000000001</v>
       </c>
     </row>
     <row r="325">
@@ -13081,7 +13081,7 @@
         <v>18</v>
       </c>
       <c r="E325" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F325" s="0" t="s">
         <v>31</v>
@@ -13090,13 +13090,13 @@
         <v>40</v>
       </c>
       <c r="H325" s="0" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="J325" s="0">
-        <v>670.93709999999999</v>
+        <v>415.84710000000001</v>
       </c>
     </row>
     <row r="326">
@@ -13113,22 +13113,22 @@
         <v>18</v>
       </c>
       <c r="E326" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F326" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G326" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H326" s="0" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="J326" s="0">
-        <v>459.24430000000001</v>
+        <v>404.09039999999999</v>
       </c>
     </row>
     <row r="327">
@@ -13148,19 +13148,19 @@
         <v>29</v>
       </c>
       <c r="F327" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G327" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H327" s="0" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="J327" s="0">
-        <v>415.84710000000001</v>
+        <v>370.1207</v>
       </c>
     </row>
     <row r="328">
@@ -13180,19 +13180,19 @@
         <v>29</v>
       </c>
       <c r="F328" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G328" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H328" s="0" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="J328" s="0">
-        <v>404.09039999999999</v>
+        <v>369.87549999999999</v>
       </c>
     </row>
     <row r="329">
@@ -13212,19 +13212,19 @@
         <v>29</v>
       </c>
       <c r="F329" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G329" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H329" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="J329" s="0">
-        <v>370.1207</v>
+        <v>332.15789999999998</v>
       </c>
     </row>
     <row r="330">
@@ -13244,19 +13244,19 @@
         <v>29</v>
       </c>
       <c r="F330" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G330" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H330" s="0" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="J330" s="0">
-        <v>369.87549999999999</v>
+        <v>310.02600000000001</v>
       </c>
     </row>
     <row r="331">
@@ -13276,19 +13276,19 @@
         <v>29</v>
       </c>
       <c r="F331" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G331" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H331" s="0" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="J331" s="0">
-        <v>332.15789999999998</v>
+        <v>137.19120000000001</v>
       </c>
     </row>
     <row r="332">
@@ -13302,25 +13302,25 @@
         <v>9</v>
       </c>
       <c r="D332" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E332" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F332" s="0" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G332" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H332" s="0" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="J332" s="0">
-        <v>310.02600000000001</v>
+        <v>6147.9931999999999</v>
       </c>
     </row>
     <row r="333">
@@ -13334,25 +13334,25 @@
         <v>9</v>
       </c>
       <c r="D333" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E333" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F333" s="0" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G333" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H333" s="0" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="J333" s="0">
-        <v>137.19120000000001</v>
+        <v>4509.7578000000003</v>
       </c>
     </row>
     <row r="334">
@@ -13369,7 +13369,7 @@
         <v>19</v>
       </c>
       <c r="E334" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F334" s="0" t="s">
         <v>31</v>
@@ -13378,13 +13378,13 @@
         <v>40</v>
       </c>
       <c r="H334" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="J334" s="0">
-        <v>6147.9931999999999</v>
+        <v>999.82090000000005</v>
       </c>
     </row>
     <row r="335">
@@ -13401,7 +13401,7 @@
         <v>19</v>
       </c>
       <c r="E335" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F335" s="0" t="s">
         <v>32</v>
@@ -13410,13 +13410,13 @@
         <v>41</v>
       </c>
       <c r="H335" s="0" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="J335" s="0">
-        <v>4509.7578000000003</v>
+        <v>829.32470000000001</v>
       </c>
     </row>
     <row r="336">
@@ -13433,7 +13433,7 @@
         <v>19</v>
       </c>
       <c r="E336" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F336" s="0" t="s">
         <v>31</v>
@@ -13442,13 +13442,13 @@
         <v>40</v>
       </c>
       <c r="H336" s="0" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="J336" s="0">
-        <v>999.82090000000005</v>
+        <v>460.868</v>
       </c>
     </row>
     <row r="337">
@@ -13465,22 +13465,22 @@
         <v>19</v>
       </c>
       <c r="E337" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F337" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G337" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H337" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="J337" s="0">
-        <v>829.32470000000001</v>
+        <v>418.91930000000002</v>
       </c>
     </row>
     <row r="338">
@@ -13500,19 +13500,19 @@
         <v>29</v>
       </c>
       <c r="F338" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G338" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H338" s="0" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="J338" s="0">
-        <v>460.868</v>
+        <v>377.29809999999998</v>
       </c>
     </row>
     <row r="339">
@@ -13532,19 +13532,19 @@
         <v>29</v>
       </c>
       <c r="F339" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G339" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H339" s="0" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="J339" s="0">
-        <v>418.91930000000002</v>
+        <v>376.07799999999998</v>
       </c>
     </row>
     <row r="340">
@@ -13564,19 +13564,19 @@
         <v>29</v>
       </c>
       <c r="F340" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G340" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H340" s="0" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="J340" s="0">
-        <v>377.29809999999998</v>
+        <v>345.4522</v>
       </c>
     </row>
     <row r="341">
@@ -13596,19 +13596,19 @@
         <v>29</v>
       </c>
       <c r="F341" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G341" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H341" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="J341" s="0">
-        <v>376.07799999999998</v>
+        <v>333.1805</v>
       </c>
     </row>
     <row r="342">
@@ -13628,19 +13628,19 @@
         <v>29</v>
       </c>
       <c r="F342" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G342" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H342" s="0" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="J342" s="0">
-        <v>345.4522</v>
+        <v>297.38940000000002</v>
       </c>
     </row>
     <row r="343">
@@ -13660,19 +13660,19 @@
         <v>29</v>
       </c>
       <c r="F343" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G343" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H343" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="J343" s="0">
-        <v>333.1805</v>
+        <v>196.88849999999999</v>
       </c>
     </row>
     <row r="344">
@@ -13686,25 +13686,25 @@
         <v>9</v>
       </c>
       <c r="D344" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E344" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F344" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G344" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H344" s="0" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="J344" s="0">
-        <v>297.38940000000002</v>
+        <v>5372.8154000000004</v>
       </c>
     </row>
     <row r="345">
@@ -13718,25 +13718,25 @@
         <v>9</v>
       </c>
       <c r="D345" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E345" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F345" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G345" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H345" s="0" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="J345" s="0">
-        <v>196.88849999999999</v>
+        <v>5089.0283</v>
       </c>
     </row>
     <row r="346">
@@ -13753,7 +13753,7 @@
         <v>20</v>
       </c>
       <c r="E346" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F346" s="0" t="s">
         <v>31</v>
@@ -13762,13 +13762,13 @@
         <v>40</v>
       </c>
       <c r="H346" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="J346" s="0">
-        <v>5372.8154000000004</v>
+        <v>623.85149999999999</v>
       </c>
     </row>
     <row r="347">
@@ -13785,7 +13785,7 @@
         <v>20</v>
       </c>
       <c r="E347" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F347" s="0" t="s">
         <v>32</v>
@@ -13794,13 +13794,13 @@
         <v>41</v>
       </c>
       <c r="H347" s="0" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="J347" s="0">
-        <v>5089.0283</v>
+        <v>173.3056</v>
       </c>
     </row>
     <row r="348">
@@ -13817,7 +13817,7 @@
         <v>20</v>
       </c>
       <c r="E348" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F348" s="0" t="s">
         <v>31</v>
@@ -13826,13 +13826,13 @@
         <v>40</v>
       </c>
       <c r="H348" s="0" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="J348" s="0">
-        <v>623.85149999999999</v>
+        <v>414.66230000000002</v>
       </c>
     </row>
     <row r="349">
@@ -13849,22 +13849,22 @@
         <v>20</v>
       </c>
       <c r="E349" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F349" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G349" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H349" s="0" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="J349" s="0">
-        <v>173.3056</v>
+        <v>403.9067</v>
       </c>
     </row>
     <row r="350">
@@ -13884,19 +13884,19 @@
         <v>29</v>
       </c>
       <c r="F350" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G350" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H350" s="0" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="J350" s="0">
-        <v>414.66230000000002</v>
+        <v>374.75290000000001</v>
       </c>
     </row>
     <row r="351">
@@ -13916,19 +13916,19 @@
         <v>29</v>
       </c>
       <c r="F351" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G351" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H351" s="0" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="J351" s="0">
-        <v>403.9067</v>
+        <v>372.04629999999997</v>
       </c>
     </row>
     <row r="352">
@@ -13948,19 +13948,19 @@
         <v>29</v>
       </c>
       <c r="F352" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G352" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H352" s="0" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="J352" s="0">
-        <v>374.75290000000001</v>
+        <v>372.0009</v>
       </c>
     </row>
     <row r="353">
@@ -13980,19 +13980,19 @@
         <v>29</v>
       </c>
       <c r="F353" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G353" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H353" s="0" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I353" s="0" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="J353" s="0">
-        <v>372.04629999999997</v>
+        <v>318.33179999999999</v>
       </c>
     </row>
     <row r="354">
@@ -14012,19 +14012,19 @@
         <v>29</v>
       </c>
       <c r="F354" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G354" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H354" s="0" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I354" s="0" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="J354" s="0">
-        <v>372.0009</v>
+        <v>295.59719999999999</v>
       </c>
     </row>
     <row r="355">
@@ -14044,19 +14044,19 @@
         <v>29</v>
       </c>
       <c r="F355" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G355" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H355" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="I355" s="0" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="J355" s="0">
-        <v>318.33179999999999</v>
+        <v>137.02930000000001</v>
       </c>
     </row>
     <row r="356">
@@ -14070,25 +14070,25 @@
         <v>9</v>
       </c>
       <c r="D356" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E356" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F356" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G356" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H356" s="0" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I356" s="0" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="J356" s="0">
-        <v>295.59719999999999</v>
+        <v>4746.6201000000001</v>
       </c>
     </row>
     <row r="357">
@@ -14102,25 +14102,25 @@
         <v>9</v>
       </c>
       <c r="D357" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E357" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F357" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G357" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H357" s="0" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I357" s="0" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="J357" s="0">
-        <v>137.02930000000001</v>
+        <v>4426.7367999999997</v>
       </c>
     </row>
     <row r="358">
@@ -14137,7 +14137,7 @@
         <v>21</v>
       </c>
       <c r="E358" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F358" s="0" t="s">
         <v>31</v>
@@ -14146,13 +14146,13 @@
         <v>40</v>
       </c>
       <c r="H358" s="0" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I358" s="0" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="J358" s="0">
-        <v>4746.6201000000001</v>
+        <v>502.13749999999999</v>
       </c>
     </row>
     <row r="359">
@@ -14169,22 +14169,22 @@
         <v>21</v>
       </c>
       <c r="E359" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F359" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G359" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H359" s="0" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="I359" s="0" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="J359" s="0">
-        <v>4426.7367999999997</v>
+        <v>439.52850000000001</v>
       </c>
     </row>
     <row r="360">
@@ -14201,22 +14201,22 @@
         <v>21</v>
       </c>
       <c r="E360" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F360" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G360" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H360" s="0" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="I360" s="0" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="J360" s="0">
-        <v>502.13749999999999</v>
+        <v>423.6062</v>
       </c>
     </row>
     <row r="361">
@@ -14236,19 +14236,19 @@
         <v>29</v>
       </c>
       <c r="F361" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G361" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H361" s="0" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="I361" s="0" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="J361" s="0">
-        <v>439.52850000000001</v>
+        <v>388.16570000000002</v>
       </c>
     </row>
     <row r="362">
@@ -14268,19 +14268,19 @@
         <v>29</v>
       </c>
       <c r="F362" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G362" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H362" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I362" s="0" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="J362" s="0">
-        <v>423.6062</v>
+        <v>361.62639999999999</v>
       </c>
     </row>
     <row r="363">
@@ -14300,19 +14300,19 @@
         <v>29</v>
       </c>
       <c r="F363" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G363" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H363" s="0" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I363" s="0" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="J363" s="0">
-        <v>388.16570000000002</v>
+        <v>319.28989999999999</v>
       </c>
     </row>
     <row r="364">
@@ -14332,19 +14332,19 @@
         <v>29</v>
       </c>
       <c r="F364" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G364" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H364" s="0" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I364" s="0" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="J364" s="0">
-        <v>361.62639999999999</v>
+        <v>283.29320000000001</v>
       </c>
     </row>
     <row r="365">
@@ -14364,19 +14364,19 @@
         <v>29</v>
       </c>
       <c r="F365" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G365" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H365" s="0" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="I365" s="0" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="J365" s="0">
-        <v>319.28989999999999</v>
+        <v>254.66130000000001</v>
       </c>
     </row>
     <row r="366">

--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="46193" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49479" uniqueCount="875">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49479" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="52729" uniqueCount="875">
   <si>
     <t>Year</t>
   </si>
@@ -4217,7 +4217,7 @@
         <v>801</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F48" s="0" t="s">
         <v>31</v>
@@ -4226,13 +4226,13 @@
         <v>40</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="J48" s="0">
-        <v>562.13390000000004</v>
+        <v>424.15600000000001</v>
       </c>
     </row>
     <row r="49">
@@ -4252,19 +4252,19 @@
         <v>29</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G49" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="J49" s="0">
-        <v>424.15600000000001</v>
+        <v>387.75049999999999</v>
       </c>
     </row>
     <row r="50">
@@ -4284,19 +4284,19 @@
         <v>29</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G50" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="J50" s="0">
-        <v>387.75049999999999</v>
+        <v>348.00529999999998</v>
       </c>
     </row>
     <row r="51">
@@ -4316,19 +4316,19 @@
         <v>29</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G51" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="J51" s="0">
-        <v>348.00529999999998</v>
+        <v>332.44470000000001</v>
       </c>
     </row>
     <row r="52">
@@ -4348,19 +4348,19 @@
         <v>29</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="J52" s="0">
-        <v>332.44470000000001</v>
+        <v>320.80650000000003</v>
       </c>
     </row>
     <row r="53">
@@ -4380,19 +4380,19 @@
         <v>29</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G53" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="J53" s="0">
-        <v>320.80650000000003</v>
+        <v>310.77530000000002</v>
       </c>
     </row>
     <row r="54">
@@ -4412,19 +4412,19 @@
         <v>29</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G54" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="J54" s="0">
-        <v>310.77530000000002</v>
+        <v>255.58779999999999</v>
       </c>
     </row>
     <row r="55">
@@ -4444,19 +4444,19 @@
         <v>29</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G55" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="J55" s="0">
-        <v>255.58779999999999</v>
+        <v>224.2235</v>
       </c>
     </row>
     <row r="56">
@@ -4470,25 +4470,25 @@
         <v>655</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="J56" s="0">
-        <v>224.2235</v>
+        <v>6088.3633</v>
       </c>
     </row>
     <row r="57">
@@ -4508,19 +4508,19 @@
         <v>27</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="J57" s="0">
-        <v>6088.3633</v>
+        <v>5077.0581000000002</v>
       </c>
     </row>
     <row r="58">
@@ -4537,22 +4537,22 @@
         <v>802</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="J58" s="0">
-        <v>5077.0581000000002</v>
+        <v>728.97640000000001</v>
       </c>
     </row>
     <row r="59">
@@ -4572,19 +4572,19 @@
         <v>28</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="J59" s="0">
-        <v>728.97640000000001</v>
+        <v>681.9529</v>
       </c>
     </row>
     <row r="60">
@@ -4601,22 +4601,22 @@
         <v>802</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="J60" s="0">
-        <v>681.9529</v>
+        <v>460.65499999999997</v>
       </c>
     </row>
     <row r="61">
@@ -4636,19 +4636,19 @@
         <v>29</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G61" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="J61" s="0">
-        <v>460.65499999999997</v>
+        <v>406.1062</v>
       </c>
     </row>
     <row r="62">
@@ -4668,19 +4668,19 @@
         <v>29</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G62" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="J62" s="0">
-        <v>406.1062</v>
+        <v>382.6694</v>
       </c>
     </row>
     <row r="63">
@@ -4700,19 +4700,19 @@
         <v>29</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G63" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="J63" s="0">
-        <v>382.6694</v>
+        <v>369.21839999999998</v>
       </c>
     </row>
     <row r="64">
@@ -4732,19 +4732,19 @@
         <v>29</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="J64" s="0">
-        <v>369.21839999999998</v>
+        <v>341.30959999999999</v>
       </c>
     </row>
     <row r="65">
@@ -4764,19 +4764,19 @@
         <v>29</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G65" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="J65" s="0">
-        <v>341.30959999999999</v>
+        <v>319.78870000000001</v>
       </c>
     </row>
     <row r="66">
@@ -4796,19 +4796,19 @@
         <v>29</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G66" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="J66" s="0">
-        <v>319.78870000000001</v>
+        <v>289.6028</v>
       </c>
     </row>
     <row r="67">
@@ -4828,19 +4828,19 @@
         <v>29</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="J67" s="0">
-        <v>289.6028</v>
+        <v>284.9262</v>
       </c>
     </row>
     <row r="68">
@@ -4854,25 +4854,25 @@
         <v>655</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="J68" s="0">
-        <v>284.9262</v>
+        <v>5367.4771000000001</v>
       </c>
     </row>
     <row r="69">
@@ -4892,19 +4892,19 @@
         <v>27</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="J69" s="0">
-        <v>5367.4771000000001</v>
+        <v>3219.1161999999999</v>
       </c>
     </row>
     <row r="70">
@@ -4921,22 +4921,22 @@
         <v>803</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>684</v>
+        <v>307</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="J70" s="0">
-        <v>3219.1161999999999</v>
+        <v>999.82090000000005</v>
       </c>
     </row>
     <row r="71">
@@ -4956,19 +4956,19 @@
         <v>28</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="J71" s="0">
-        <v>999.82090000000005</v>
+        <v>829.32470000000001</v>
       </c>
     </row>
     <row r="72">
@@ -4985,22 +4985,22 @@
         <v>803</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>308</v>
+        <v>685</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="J72" s="0">
-        <v>829.32470000000001</v>
+        <v>434.72210000000001</v>
       </c>
     </row>
     <row r="73">
@@ -5020,19 +5020,19 @@
         <v>29</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G73" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="J73" s="0">
-        <v>434.72210000000001</v>
+        <v>420.51510000000002</v>
       </c>
     </row>
     <row r="74">
@@ -5052,19 +5052,19 @@
         <v>29</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G74" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="J74" s="0">
-        <v>420.51510000000002</v>
+        <v>416.28559999999999</v>
       </c>
     </row>
     <row r="75">
@@ -5084,19 +5084,19 @@
         <v>29</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G75" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="J75" s="0">
-        <v>416.28559999999999</v>
+        <v>400.9085</v>
       </c>
     </row>
     <row r="76">
@@ -5116,19 +5116,19 @@
         <v>29</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="J76" s="0">
-        <v>400.9085</v>
+        <v>360.4205</v>
       </c>
     </row>
     <row r="77">
@@ -5148,19 +5148,19 @@
         <v>29</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G77" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="J77" s="0">
-        <v>360.4205</v>
+        <v>305.30689999999999</v>
       </c>
     </row>
     <row r="78">
@@ -5180,19 +5180,19 @@
         <v>29</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G78" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="J78" s="0">
-        <v>305.30689999999999</v>
+        <v>293.2808</v>
       </c>
     </row>
     <row r="79">
@@ -5212,19 +5212,19 @@
         <v>29</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G79" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="J79" s="0">
-        <v>293.2808</v>
+        <v>247.7748</v>
       </c>
     </row>
     <row r="80">
@@ -5235,28 +5235,28 @@
         <v>3</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>655</v>
+        <v>8</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>803</v>
+        <v>15</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>692</v>
+        <v>91</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>874</v>
+        <v>390</v>
       </c>
       <c r="J80" s="0">
-        <v>247.7748</v>
+        <v>5813.3739999999998</v>
       </c>
     </row>
     <row r="81">
@@ -5276,19 +5276,19 @@
         <v>27</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J81" s="0">
-        <v>5813.3739999999998</v>
+        <v>3499.9191999999998</v>
       </c>
     </row>
     <row r="82">
@@ -5305,22 +5305,22 @@
         <v>15</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J82" s="0">
-        <v>3499.9191999999998</v>
+        <v>643.7663</v>
       </c>
     </row>
     <row r="83">
@@ -5340,19 +5340,19 @@
         <v>28</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J83" s="0">
-        <v>643.7663</v>
+        <v>507.9119</v>
       </c>
     </row>
     <row r="84">
@@ -5369,22 +5369,22 @@
         <v>15</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J84" s="0">
-        <v>507.9119</v>
+        <v>413.24200000000002</v>
       </c>
     </row>
     <row r="85">
@@ -5404,19 +5404,19 @@
         <v>29</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G85" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J85" s="0">
-        <v>413.24200000000002</v>
+        <v>412.743</v>
       </c>
     </row>
     <row r="86">
@@ -5436,19 +5436,19 @@
         <v>29</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G86" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J86" s="0">
-        <v>412.743</v>
+        <v>365.9803</v>
       </c>
     </row>
     <row r="87">
@@ -5468,19 +5468,19 @@
         <v>29</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G87" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J87" s="0">
-        <v>365.9803</v>
+        <v>362.68889999999999</v>
       </c>
     </row>
     <row r="88">
@@ -5500,19 +5500,19 @@
         <v>29</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J88" s="0">
-        <v>362.68889999999999</v>
+        <v>337.94470000000001</v>
       </c>
     </row>
     <row r="89">
@@ -5532,19 +5532,19 @@
         <v>29</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G89" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J89" s="0">
-        <v>337.94470000000001</v>
+        <v>275.04509999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5564,19 +5564,19 @@
         <v>29</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G90" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J90" s="0">
-        <v>275.04509999999999</v>
+        <v>253.987</v>
       </c>
     </row>
     <row r="91">
@@ -5596,19 +5596,19 @@
         <v>29</v>
       </c>
       <c r="F91" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G91" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J91" s="0">
-        <v>253.987</v>
+        <v>197.0513</v>
       </c>
     </row>
     <row r="92">
@@ -5622,25 +5622,25 @@
         <v>8</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J92" s="0">
-        <v>197.0513</v>
+        <v>6411.3008</v>
       </c>
     </row>
     <row r="93">
@@ -5660,19 +5660,19 @@
         <v>27</v>
       </c>
       <c r="F93" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J93" s="0">
-        <v>6411.3008</v>
+        <v>5363.7114000000001</v>
       </c>
     </row>
     <row r="94">
@@ -5689,22 +5689,22 @@
         <v>16</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="J94" s="0">
-        <v>5363.7114000000001</v>
+        <v>465.0847</v>
       </c>
     </row>
     <row r="95">
@@ -5721,22 +5721,22 @@
         <v>16</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G95" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J95" s="0">
-        <v>495.09269999999998</v>
+        <v>432.71969999999999</v>
       </c>
     </row>
     <row r="96">
@@ -5756,19 +5756,19 @@
         <v>29</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G96" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J96" s="0">
-        <v>465.0847</v>
+        <v>403.6884</v>
       </c>
     </row>
     <row r="97">
@@ -5788,19 +5788,19 @@
         <v>29</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G97" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J97" s="0">
-        <v>432.71969999999999</v>
+        <v>393.85660000000001</v>
       </c>
     </row>
     <row r="98">
@@ -5820,19 +5820,19 @@
         <v>29</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="J98" s="0">
-        <v>403.6884</v>
+        <v>328.83640000000003</v>
       </c>
     </row>
     <row r="99">
@@ -5852,19 +5852,19 @@
         <v>29</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J99" s="0">
-        <v>393.85660000000001</v>
+        <v>289.99919999999997</v>
       </c>
     </row>
     <row r="100">
@@ -5884,19 +5884,19 @@
         <v>29</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G100" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J100" s="0">
-        <v>328.83640000000003</v>
+        <v>253.50819999999999</v>
       </c>
     </row>
     <row r="101">
@@ -5916,19 +5916,19 @@
         <v>29</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G101" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J101" s="0">
-        <v>289.99919999999997</v>
+        <v>156.39179999999999</v>
       </c>
     </row>
     <row r="102">
@@ -5942,25 +5942,25 @@
         <v>8</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E102" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J102" s="0">
-        <v>253.50819999999999</v>
+        <v>5347.2299999999996</v>
       </c>
     </row>
     <row r="103">
@@ -5974,25 +5974,25 @@
         <v>8</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J103" s="0">
-        <v>156.39179999999999</v>
+        <v>832.64940000000001</v>
       </c>
     </row>
     <row r="104">
@@ -6009,22 +6009,22 @@
         <v>17</v>
       </c>
       <c r="E104" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J104" s="0">
-        <v>5347.2299999999996</v>
+        <v>670.97080000000005</v>
       </c>
     </row>
     <row r="105">
@@ -6041,7 +6041,7 @@
         <v>17</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F105" s="0" t="s">
         <v>31</v>
@@ -6050,13 +6050,13 @@
         <v>40</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J105" s="0">
-        <v>832.64940000000001</v>
+        <v>452.6379</v>
       </c>
     </row>
     <row r="106">
@@ -6073,22 +6073,22 @@
         <v>17</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F106" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J106" s="0">
-        <v>670.97080000000005</v>
+        <v>432.76639999999998</v>
       </c>
     </row>
     <row r="107">
@@ -6108,19 +6108,19 @@
         <v>29</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G107" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J107" s="0">
-        <v>452.6379</v>
+        <v>430.21100000000001</v>
       </c>
     </row>
     <row r="108">
@@ -6140,19 +6140,19 @@
         <v>29</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G108" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="J108" s="0">
-        <v>432.76639999999998</v>
+        <v>426.60840000000002</v>
       </c>
     </row>
     <row r="109">
@@ -6172,19 +6172,19 @@
         <v>29</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J109" s="0">
-        <v>430.21100000000001</v>
+        <v>408.17599999999999</v>
       </c>
     </row>
     <row r="110">
@@ -6204,19 +6204,19 @@
         <v>29</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="J110" s="0">
-        <v>426.60840000000002</v>
+        <v>393.9744</v>
       </c>
     </row>
     <row r="111">
@@ -6236,19 +6236,19 @@
         <v>29</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G111" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J111" s="0">
-        <v>408.17599999999999</v>
+        <v>369.06290000000001</v>
       </c>
     </row>
     <row r="112">
@@ -6268,19 +6268,19 @@
         <v>29</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G112" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J112" s="0">
-        <v>393.9744</v>
+        <v>363.61939999999999</v>
       </c>
     </row>
     <row r="113">
@@ -6291,28 +6291,28 @@
         <v>3</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J113" s="0">
-        <v>369.06290000000001</v>
+        <v>5889.4614000000001</v>
       </c>
     </row>
     <row r="114">
@@ -6323,28 +6323,28 @@
         <v>3</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E114" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F114" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G114" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="J114" s="0">
-        <v>363.61939999999999</v>
+        <v>2742.3312999999998</v>
       </c>
     </row>
     <row r="115">
@@ -6361,7 +6361,7 @@
         <v>18</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F115" s="0" t="s">
         <v>31</v>
@@ -6370,13 +6370,13 @@
         <v>40</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J115" s="0">
-        <v>5889.4614000000001</v>
+        <v>673.23270000000002</v>
       </c>
     </row>
     <row r="116">
@@ -6393,7 +6393,7 @@
         <v>18</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F116" s="0" t="s">
         <v>32</v>
@@ -6402,13 +6402,13 @@
         <v>41</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J116" s="0">
-        <v>2742.3312999999998</v>
+        <v>548.54560000000004</v>
       </c>
     </row>
     <row r="117">
@@ -6425,7 +6425,7 @@
         <v>18</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F117" s="0" t="s">
         <v>31</v>
@@ -6434,13 +6434,13 @@
         <v>40</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="J117" s="0">
-        <v>673.23270000000002</v>
+        <v>406.4975</v>
       </c>
     </row>
     <row r="118">
@@ -6457,22 +6457,22 @@
         <v>18</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="J118" s="0">
-        <v>548.54560000000004</v>
+        <v>370.59609999999998</v>
       </c>
     </row>
     <row r="119">
@@ -6492,19 +6492,19 @@
         <v>29</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G119" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J119" s="0">
-        <v>406.4975</v>
+        <v>295.41489999999999</v>
       </c>
     </row>
     <row r="120">
@@ -6524,19 +6524,19 @@
         <v>29</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G120" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J120" s="0">
-        <v>370.59609999999998</v>
+        <v>294.39229999999998</v>
       </c>
     </row>
     <row r="121">
@@ -6556,19 +6556,19 @@
         <v>29</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="J121" s="0">
-        <v>295.41489999999999</v>
+        <v>290.21879999999999</v>
       </c>
     </row>
     <row r="122">
@@ -6588,19 +6588,19 @@
         <v>29</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="J122" s="0">
-        <v>294.39229999999998</v>
+        <v>241.96080000000001</v>
       </c>
     </row>
     <row r="123">
@@ -6620,19 +6620,19 @@
         <v>29</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G123" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="J123" s="0">
-        <v>290.21879999999999</v>
+        <v>208.0266</v>
       </c>
     </row>
     <row r="124">
@@ -6646,25 +6646,25 @@
         <v>9</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E124" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="J124" s="0">
-        <v>241.96080000000001</v>
+        <v>2255.5239000000001</v>
       </c>
     </row>
     <row r="125">
@@ -6678,25 +6678,25 @@
         <v>9</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E125" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="J125" s="0">
-        <v>208.0266</v>
+        <v>784.23540000000003</v>
       </c>
     </row>
     <row r="126">
@@ -6713,22 +6713,22 @@
         <v>19</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="J126" s="0">
-        <v>2255.5239000000001</v>
+        <v>590.41420000000005</v>
       </c>
     </row>
     <row r="127">
@@ -6745,7 +6745,7 @@
         <v>19</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F127" s="0" t="s">
         <v>31</v>
@@ -6754,13 +6754,13 @@
         <v>40</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J127" s="0">
-        <v>784.23540000000003</v>
+        <v>431.26760000000002</v>
       </c>
     </row>
     <row r="128">
@@ -6777,22 +6777,22 @@
         <v>19</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G128" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="J128" s="0">
-        <v>590.41420000000005</v>
+        <v>372.27710000000002</v>
       </c>
     </row>
     <row r="129">
@@ -6812,19 +6812,19 @@
         <v>29</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G129" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J129" s="0">
-        <v>431.26760000000002</v>
+        <v>370.83260000000001</v>
       </c>
     </row>
     <row r="130">
@@ -6844,19 +6844,19 @@
         <v>29</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G130" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J130" s="0">
-        <v>372.27710000000002</v>
+        <v>368.27210000000002</v>
       </c>
     </row>
     <row r="131">
@@ -6876,19 +6876,19 @@
         <v>29</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G131" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="J131" s="0">
-        <v>370.83260000000001</v>
+        <v>345.15750000000003</v>
       </c>
     </row>
     <row r="132">
@@ -6908,19 +6908,19 @@
         <v>29</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G132" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J132" s="0">
-        <v>368.27210000000002</v>
+        <v>335.8723</v>
       </c>
     </row>
     <row r="133">
@@ -6940,19 +6940,19 @@
         <v>29</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G133" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="J133" s="0">
-        <v>345.15750000000003</v>
+        <v>309.04379999999998</v>
       </c>
     </row>
     <row r="134">
@@ -6972,19 +6972,19 @@
         <v>29</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G134" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="J134" s="0">
-        <v>335.8723</v>
+        <v>280.34730000000002</v>
       </c>
     </row>
     <row r="135">
@@ -6998,25 +6998,25 @@
         <v>9</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G135" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H135" s="0" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J135" s="0">
-        <v>309.04379999999998</v>
+        <v>6089.4750999999997</v>
       </c>
     </row>
     <row r="136">
@@ -7030,25 +7030,25 @@
         <v>9</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E136" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G136" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J136" s="0">
-        <v>280.34730000000002</v>
+        <v>4801.2959000000001</v>
       </c>
     </row>
     <row r="137">
@@ -7065,7 +7065,7 @@
         <v>20</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F137" s="0" t="s">
         <v>31</v>
@@ -7074,13 +7074,13 @@
         <v>40</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="J137" s="0">
-        <v>6089.4750999999997</v>
+        <v>729.38409999999999</v>
       </c>
     </row>
     <row r="138">
@@ -7097,22 +7097,22 @@
         <v>20</v>
       </c>
       <c r="E138" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="J138" s="0">
-        <v>4801.2959000000001</v>
+        <v>414.8329</v>
       </c>
     </row>
     <row r="139">
@@ -7129,22 +7129,22 @@
         <v>20</v>
       </c>
       <c r="E139" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G139" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H139" s="0" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J139" s="0">
-        <v>729.38409999999999</v>
+        <v>407.11009999999999</v>
       </c>
     </row>
     <row r="140">
@@ -7164,19 +7164,19 @@
         <v>29</v>
       </c>
       <c r="F140" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G140" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J140" s="0">
-        <v>414.8329</v>
+        <v>390.21910000000003</v>
       </c>
     </row>
     <row r="141">
@@ -7196,19 +7196,19 @@
         <v>29</v>
       </c>
       <c r="F141" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G141" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="J141" s="0">
-        <v>407.11009999999999</v>
+        <v>362.1839</v>
       </c>
     </row>
     <row r="142">
@@ -7228,19 +7228,19 @@
         <v>29</v>
       </c>
       <c r="F142" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G142" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J142" s="0">
-        <v>390.21910000000003</v>
+        <v>349.2903</v>
       </c>
     </row>
     <row r="143">
@@ -7260,19 +7260,19 @@
         <v>29</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J143" s="0">
-        <v>362.1839</v>
+        <v>339.61919999999998</v>
       </c>
     </row>
     <row r="144">
@@ -7292,19 +7292,19 @@
         <v>29</v>
       </c>
       <c r="F144" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G144" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J144" s="0">
-        <v>349.2903</v>
+        <v>321.077</v>
       </c>
     </row>
     <row r="145">
@@ -7324,19 +7324,19 @@
         <v>29</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G145" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H145" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="J145" s="0">
-        <v>339.61919999999998</v>
+        <v>320.34030000000001</v>
       </c>
     </row>
     <row r="146">
@@ -7350,25 +7350,25 @@
         <v>9</v>
       </c>
       <c r="D146" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E146" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F146" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G146" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J146" s="0">
-        <v>321.077</v>
+        <v>4900.8388999999997</v>
       </c>
     </row>
     <row r="147">
@@ -7382,25 +7382,25 @@
         <v>9</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E147" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F147" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G147" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H147" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J147" s="0">
-        <v>320.34030000000001</v>
+        <v>2991.1887000000002</v>
       </c>
     </row>
     <row r="148">
@@ -7417,7 +7417,7 @@
         <v>21</v>
       </c>
       <c r="E148" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F148" s="0" t="s">
         <v>31</v>
@@ -7426,13 +7426,13 @@
         <v>40</v>
       </c>
       <c r="H148" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J148" s="0">
-        <v>4900.8388999999997</v>
+        <v>694.42499999999996</v>
       </c>
     </row>
     <row r="149">
@@ -7449,7 +7449,7 @@
         <v>21</v>
       </c>
       <c r="E149" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F149" s="0" t="s">
         <v>32</v>
@@ -7458,13 +7458,13 @@
         <v>41</v>
       </c>
       <c r="H149" s="0" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J149" s="0">
-        <v>2991.1887000000002</v>
+        <v>590.76210000000003</v>
       </c>
     </row>
     <row r="150">
@@ -7481,7 +7481,7 @@
         <v>21</v>
       </c>
       <c r="E150" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F150" s="0" t="s">
         <v>31</v>
@@ -7490,13 +7490,13 @@
         <v>40</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J150" s="0">
-        <v>694.42499999999996</v>
+        <v>434.02370000000002</v>
       </c>
     </row>
     <row r="151">
@@ -7513,22 +7513,22 @@
         <v>21</v>
       </c>
       <c r="E151" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F151" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G151" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H151" s="0" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J151" s="0">
-        <v>590.76210000000003</v>
+        <v>417.05189999999999</v>
       </c>
     </row>
     <row r="152">
@@ -7548,19 +7548,19 @@
         <v>29</v>
       </c>
       <c r="F152" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G152" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J152" s="0">
-        <v>434.02370000000002</v>
+        <v>407.86430000000001</v>
       </c>
     </row>
     <row r="153">
@@ -7580,19 +7580,19 @@
         <v>29</v>
       </c>
       <c r="F153" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G153" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H153" s="0" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="J153" s="0">
-        <v>417.05189999999999</v>
+        <v>406.37779999999998</v>
       </c>
     </row>
     <row r="154">
@@ -7612,19 +7612,19 @@
         <v>29</v>
       </c>
       <c r="F154" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G154" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H154" s="0" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J154" s="0">
-        <v>407.86430000000001</v>
+        <v>379.51209999999998</v>
       </c>
     </row>
     <row r="155">
@@ -7644,19 +7644,19 @@
         <v>29</v>
       </c>
       <c r="F155" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G155" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H155" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J155" s="0">
-        <v>406.37779999999998</v>
+        <v>361.57029999999998</v>
       </c>
     </row>
     <row r="156">
@@ -7676,19 +7676,19 @@
         <v>29</v>
       </c>
       <c r="F156" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G156" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H156" s="0" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J156" s="0">
-        <v>379.51209999999998</v>
+        <v>324.36189999999999</v>
       </c>
     </row>
     <row r="157">
@@ -7696,31 +7696,31 @@
         <v>1</v>
       </c>
       <c r="B157" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C157" s="0" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D157" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E157" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F157" s="0" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G157" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H157" s="0" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="J157" s="0">
-        <v>361.57029999999998</v>
+        <v>2639.6545000000001</v>
       </c>
     </row>
     <row r="158">
@@ -7728,31 +7728,31 @@
         <v>1</v>
       </c>
       <c r="B158" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C158" s="0" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D158" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E158" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F158" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G158" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H158" s="0" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="J158" s="0">
-        <v>324.36189999999999</v>
+        <v>538.57830000000001</v>
       </c>
     </row>
     <row r="159">
@@ -7769,22 +7769,22 @@
         <v>22</v>
       </c>
       <c r="E159" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F159" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G159" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H159" s="0" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="J159" s="0">
-        <v>2639.6545000000001</v>
+        <v>439.68729999999999</v>
       </c>
     </row>
     <row r="160">
@@ -7801,7 +7801,7 @@
         <v>22</v>
       </c>
       <c r="E160" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F160" s="0" t="s">
         <v>31</v>
@@ -7810,13 +7810,13 @@
         <v>40</v>
       </c>
       <c r="H160" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="J160" s="0">
-        <v>538.57830000000001</v>
+        <v>466.59890000000001</v>
       </c>
     </row>
     <row r="161">
@@ -7833,22 +7833,22 @@
         <v>22</v>
       </c>
       <c r="E161" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F161" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G161" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H161" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="J161" s="0">
-        <v>439.68729999999999</v>
+        <v>348.95269999999999</v>
       </c>
     </row>
     <row r="162">
@@ -7868,19 +7868,19 @@
         <v>29</v>
       </c>
       <c r="F162" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G162" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H162" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="J162" s="0">
-        <v>466.59890000000001</v>
+        <v>320.45060000000001</v>
       </c>
     </row>
     <row r="163">
@@ -7900,19 +7900,19 @@
         <v>29</v>
       </c>
       <c r="F163" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G163" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H163" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="J163" s="0">
-        <v>348.95269999999999</v>
+        <v>306.95499999999999</v>
       </c>
     </row>
     <row r="164">
@@ -7932,19 +7932,19 @@
         <v>29</v>
       </c>
       <c r="F164" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G164" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H164" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="J164" s="0">
-        <v>320.45060000000001</v>
+        <v>286.13639999999998</v>
       </c>
     </row>
     <row r="165">
@@ -7964,19 +7964,19 @@
         <v>29</v>
       </c>
       <c r="F165" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G165" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H165" s="0" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J165" s="0">
-        <v>306.95499999999999</v>
+        <v>270.46800000000002</v>
       </c>
     </row>
     <row r="166">
@@ -7996,19 +7996,19 @@
         <v>29</v>
       </c>
       <c r="F166" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G166" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H166" s="0" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J166" s="0">
-        <v>286.13639999999998</v>
+        <v>266.42959999999999</v>
       </c>
     </row>
     <row r="167">
@@ -8028,19 +8028,19 @@
         <v>29</v>
       </c>
       <c r="F167" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G167" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H167" s="0" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="J167" s="0">
-        <v>270.46800000000002</v>
+        <v>198.7653</v>
       </c>
     </row>
     <row r="168">
@@ -8054,25 +8054,25 @@
         <v>6</v>
       </c>
       <c r="D168" s="0" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E168" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F168" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G168" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H168" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="J168" s="0">
-        <v>266.42959999999999</v>
+        <v>6949.5127000000002</v>
       </c>
     </row>
     <row r="169">
@@ -8086,25 +8086,25 @@
         <v>6</v>
       </c>
       <c r="D169" s="0" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E169" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F169" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G169" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H169" s="0" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="J169" s="0">
-        <v>198.7653</v>
+        <v>1918.3168000000001</v>
       </c>
     </row>
     <row r="170">
@@ -8121,7 +8121,7 @@
         <v>11</v>
       </c>
       <c r="E170" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F170" s="0" t="s">
         <v>31</v>
@@ -8130,13 +8130,13 @@
         <v>40</v>
       </c>
       <c r="H170" s="0" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="J170" s="0">
-        <v>6949.5127000000002</v>
+        <v>842.53420000000006</v>
       </c>
     </row>
     <row r="171">
@@ -8153,7 +8153,7 @@
         <v>11</v>
       </c>
       <c r="E171" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F171" s="0" t="s">
         <v>32</v>
@@ -8162,13 +8162,13 @@
         <v>41</v>
       </c>
       <c r="H171" s="0" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="J171" s="0">
-        <v>1918.3168000000001</v>
+        <v>625.51949999999999</v>
       </c>
     </row>
     <row r="172">
@@ -8185,7 +8185,7 @@
         <v>11</v>
       </c>
       <c r="E172" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F172" s="0" t="s">
         <v>31</v>
@@ -8194,13 +8194,13 @@
         <v>40</v>
       </c>
       <c r="H172" s="0" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="J172" s="0">
-        <v>842.53420000000006</v>
+        <v>403.39569999999998</v>
       </c>
     </row>
     <row r="173">
@@ -8217,22 +8217,22 @@
         <v>11</v>
       </c>
       <c r="E173" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F173" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G173" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H173" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="J173" s="0">
-        <v>625.51949999999999</v>
+        <v>401.83440000000002</v>
       </c>
     </row>
     <row r="174">
@@ -8252,19 +8252,19 @@
         <v>29</v>
       </c>
       <c r="F174" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G174" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H174" s="0" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="J174" s="0">
-        <v>403.39569999999998</v>
+        <v>401.53390000000002</v>
       </c>
     </row>
     <row r="175">
@@ -8284,19 +8284,19 @@
         <v>29</v>
       </c>
       <c r="F175" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G175" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H175" s="0" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="J175" s="0">
-        <v>401.83440000000002</v>
+        <v>325.73790000000002</v>
       </c>
     </row>
     <row r="176">
@@ -8316,19 +8316,19 @@
         <v>29</v>
       </c>
       <c r="F176" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G176" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H176" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="J176" s="0">
-        <v>401.53390000000002</v>
+        <v>306.47129999999999</v>
       </c>
     </row>
     <row r="177">
@@ -8348,19 +8348,19 @@
         <v>29</v>
       </c>
       <c r="F177" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G177" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H177" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="J177" s="0">
-        <v>325.73790000000002</v>
+        <v>297.54129999999998</v>
       </c>
     </row>
     <row r="178">
@@ -8380,19 +8380,19 @@
         <v>29</v>
       </c>
       <c r="F178" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G178" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H178" s="0" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="J178" s="0">
-        <v>306.47129999999999</v>
+        <v>251.23050000000001</v>
       </c>
     </row>
     <row r="179">
@@ -8412,19 +8412,19 @@
         <v>29</v>
       </c>
       <c r="F179" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G179" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H179" s="0" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="J179" s="0">
-        <v>297.54129999999998</v>
+        <v>104.34829999999999</v>
       </c>
     </row>
     <row r="180">
@@ -8438,25 +8438,25 @@
         <v>6</v>
       </c>
       <c r="D180" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E180" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F180" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G180" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H180" s="0" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="J180" s="0">
-        <v>251.23050000000001</v>
+        <v>5196.1244999999999</v>
       </c>
     </row>
     <row r="181">
@@ -8470,25 +8470,25 @@
         <v>6</v>
       </c>
       <c r="D181" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E181" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F181" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G181" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H181" s="0" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="J181" s="0">
-        <v>104.34829999999999</v>
+        <v>2798.9209000000001</v>
       </c>
     </row>
     <row r="182">
@@ -8505,7 +8505,7 @@
         <v>12</v>
       </c>
       <c r="E182" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F182" s="0" t="s">
         <v>31</v>
@@ -8514,13 +8514,13 @@
         <v>40</v>
       </c>
       <c r="H182" s="0" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="J182" s="0">
-        <v>5196.1244999999999</v>
+        <v>554.0693</v>
       </c>
     </row>
     <row r="183">
@@ -8537,7 +8537,7 @@
         <v>12</v>
       </c>
       <c r="E183" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F183" s="0" t="s">
         <v>32</v>
@@ -8546,13 +8546,13 @@
         <v>41</v>
       </c>
       <c r="H183" s="0" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="J183" s="0">
-        <v>2798.9209000000001</v>
+        <v>97.465900000000005</v>
       </c>
     </row>
     <row r="184">
@@ -8569,7 +8569,7 @@
         <v>12</v>
       </c>
       <c r="E184" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F184" s="0" t="s">
         <v>31</v>
@@ -8578,13 +8578,13 @@
         <v>40</v>
       </c>
       <c r="H184" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="J184" s="0">
-        <v>554.0693</v>
+        <v>413.24349999999998</v>
       </c>
     </row>
     <row r="185">
@@ -8601,22 +8601,22 @@
         <v>12</v>
       </c>
       <c r="E185" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F185" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G185" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H185" s="0" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="J185" s="0">
-        <v>97.465900000000005</v>
+        <v>390.69720000000001</v>
       </c>
     </row>
     <row r="186">
@@ -8636,19 +8636,19 @@
         <v>29</v>
       </c>
       <c r="F186" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G186" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H186" s="0" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="J186" s="0">
-        <v>413.24349999999998</v>
+        <v>384.44110000000001</v>
       </c>
     </row>
     <row r="187">
@@ -8668,19 +8668,19 @@
         <v>29</v>
       </c>
       <c r="F187" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G187" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H187" s="0" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="J187" s="0">
-        <v>390.69720000000001</v>
+        <v>369.39760000000001</v>
       </c>
     </row>
     <row r="188">
@@ -8700,19 +8700,19 @@
         <v>29</v>
       </c>
       <c r="F188" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G188" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H188" s="0" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="J188" s="0">
-        <v>384.44110000000001</v>
+        <v>355.85449999999997</v>
       </c>
     </row>
     <row r="189">
@@ -8732,19 +8732,19 @@
         <v>29</v>
       </c>
       <c r="F189" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G189" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H189" s="0" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="J189" s="0">
-        <v>369.39760000000001</v>
+        <v>332.20139999999998</v>
       </c>
     </row>
     <row r="190">
@@ -8764,19 +8764,19 @@
         <v>29</v>
       </c>
       <c r="F190" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G190" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H190" s="0" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="J190" s="0">
-        <v>355.85449999999997</v>
+        <v>304.4751</v>
       </c>
     </row>
     <row r="191">
@@ -8796,19 +8796,19 @@
         <v>29</v>
       </c>
       <c r="F191" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G191" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H191" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J191" s="0">
-        <v>332.20139999999998</v>
+        <v>263.24160000000001</v>
       </c>
     </row>
     <row r="192">
@@ -8819,28 +8819,28 @@
         <v>4</v>
       </c>
       <c r="C192" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D192" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E192" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F192" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G192" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="J192" s="0">
-        <v>304.4751</v>
+        <v>5598.6216000000004</v>
       </c>
     </row>
     <row r="193">
@@ -8851,28 +8851,28 @@
         <v>4</v>
       </c>
       <c r="C193" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D193" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E193" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F193" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G193" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H193" s="0" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="J193" s="0">
-        <v>263.24160000000001</v>
+        <v>4298.6826000000001</v>
       </c>
     </row>
     <row r="194">
@@ -8889,7 +8889,7 @@
         <v>13</v>
       </c>
       <c r="E194" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F194" s="0" t="s">
         <v>31</v>
@@ -8898,13 +8898,13 @@
         <v>40</v>
       </c>
       <c r="H194" s="0" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="J194" s="0">
-        <v>5598.6216000000004</v>
+        <v>831.18269999999996</v>
       </c>
     </row>
     <row r="195">
@@ -8921,7 +8921,7 @@
         <v>13</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F195" s="0" t="s">
         <v>32</v>
@@ -8930,13 +8930,13 @@
         <v>41</v>
       </c>
       <c r="H195" s="0" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J195" s="0">
-        <v>4298.6826000000001</v>
+        <v>746.42259999999999</v>
       </c>
     </row>
     <row r="196">
@@ -8953,7 +8953,7 @@
         <v>13</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F196" s="0" t="s">
         <v>31</v>
@@ -8962,13 +8962,13 @@
         <v>40</v>
       </c>
       <c r="H196" s="0" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="J196" s="0">
-        <v>831.18269999999996</v>
+        <v>477.65440000000001</v>
       </c>
     </row>
     <row r="197">
@@ -8985,22 +8985,22 @@
         <v>13</v>
       </c>
       <c r="E197" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F197" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G197" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H197" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J197" s="0">
-        <v>746.42259999999999</v>
+        <v>455.09550000000002</v>
       </c>
     </row>
     <row r="198">
@@ -9020,19 +9020,19 @@
         <v>29</v>
       </c>
       <c r="F198" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G198" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H198" s="0" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="J198" s="0">
-        <v>477.65440000000001</v>
+        <v>442.9828</v>
       </c>
     </row>
     <row r="199">
@@ -9052,19 +9052,19 @@
         <v>29</v>
       </c>
       <c r="F199" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G199" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H199" s="0" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J199" s="0">
-        <v>455.09550000000002</v>
+        <v>403.95710000000003</v>
       </c>
     </row>
     <row r="200">
@@ -9084,19 +9084,19 @@
         <v>29</v>
       </c>
       <c r="F200" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G200" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H200" s="0" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="J200" s="0">
-        <v>442.9828</v>
+        <v>353.99869999999999</v>
       </c>
     </row>
     <row r="201">
@@ -9116,19 +9116,19 @@
         <v>29</v>
       </c>
       <c r="F201" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G201" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="J201" s="0">
-        <v>403.95710000000003</v>
+        <v>282.62110000000001</v>
       </c>
     </row>
     <row r="202">
@@ -9148,19 +9148,19 @@
         <v>29</v>
       </c>
       <c r="F202" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G202" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H202" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J202" s="0">
-        <v>353.99869999999999</v>
+        <v>251.0352</v>
       </c>
     </row>
     <row r="203">
@@ -9180,19 +9180,19 @@
         <v>29</v>
       </c>
       <c r="F203" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G203" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H203" s="0" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J203" s="0">
-        <v>282.62110000000001</v>
+        <v>226.5855</v>
       </c>
     </row>
     <row r="204">
@@ -9206,25 +9206,25 @@
         <v>7</v>
       </c>
       <c r="D204" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E204" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F204" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G204" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H204" s="0" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="J204" s="0">
-        <v>251.0352</v>
+        <v>3073.4854</v>
       </c>
     </row>
     <row r="205">
@@ -9238,25 +9238,25 @@
         <v>7</v>
       </c>
       <c r="D205" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E205" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G205" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H205" s="0" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="J205" s="0">
-        <v>226.5855</v>
+        <v>1817.3022000000001</v>
       </c>
     </row>
     <row r="206">
@@ -9273,7 +9273,7 @@
         <v>14</v>
       </c>
       <c r="E206" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F206" s="0" t="s">
         <v>31</v>
@@ -9282,13 +9282,13 @@
         <v>40</v>
       </c>
       <c r="H206" s="0" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J206" s="0">
-        <v>3073.4854</v>
+        <v>831.18269999999996</v>
       </c>
     </row>
     <row r="207">
@@ -9305,22 +9305,22 @@
         <v>14</v>
       </c>
       <c r="E207" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F207" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G207" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H207" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="J207" s="0">
-        <v>1817.3022000000001</v>
+        <v>444.28719999999999</v>
       </c>
     </row>
     <row r="208">
@@ -9337,22 +9337,22 @@
         <v>14</v>
       </c>
       <c r="E208" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F208" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G208" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H208" s="0" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J208" s="0">
-        <v>831.18269999999996</v>
+        <v>406.01569999999998</v>
       </c>
     </row>
     <row r="209">
@@ -9372,19 +9372,19 @@
         <v>29</v>
       </c>
       <c r="F209" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G209" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H209" s="0" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="J209" s="0">
-        <v>444.28719999999999</v>
+        <v>377.0512</v>
       </c>
     </row>
     <row r="210">
@@ -9404,19 +9404,19 @@
         <v>29</v>
       </c>
       <c r="F210" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G210" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="J210" s="0">
-        <v>406.01569999999998</v>
+        <v>370.54059999999998</v>
       </c>
     </row>
     <row r="211">
@@ -9436,19 +9436,19 @@
         <v>29</v>
       </c>
       <c r="F211" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G211" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H211" s="0" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="J211" s="0">
-        <v>377.0512</v>
+        <v>364.45699999999999</v>
       </c>
     </row>
     <row r="212">
@@ -9468,19 +9468,19 @@
         <v>29</v>
       </c>
       <c r="F212" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G212" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H212" s="0" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="J212" s="0">
-        <v>370.54059999999998</v>
+        <v>357.5231</v>
       </c>
     </row>
     <row r="213">
@@ -9500,19 +9500,19 @@
         <v>29</v>
       </c>
       <c r="F213" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G213" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J213" s="0">
-        <v>364.45699999999999</v>
+        <v>289.80360000000002</v>
       </c>
     </row>
     <row r="214">
@@ -9532,19 +9532,19 @@
         <v>29</v>
       </c>
       <c r="F214" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G214" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="J214" s="0">
-        <v>357.5231</v>
+        <v>205.23990000000001</v>
       </c>
     </row>
     <row r="215">
@@ -9558,25 +9558,25 @@
         <v>7</v>
       </c>
       <c r="D215" s="0" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E215" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F215" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G215" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="J215" s="0">
-        <v>289.80360000000002</v>
+        <v>5904.6377000000002</v>
       </c>
     </row>
     <row r="216">
@@ -9590,25 +9590,25 @@
         <v>7</v>
       </c>
       <c r="D216" s="0" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E216" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F216" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G216" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J216" s="0">
-        <v>205.23990000000001</v>
+        <v>4907.7012000000004</v>
       </c>
     </row>
     <row r="217">
@@ -9625,7 +9625,7 @@
         <v>23</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F217" s="0" t="s">
         <v>31</v>
@@ -9634,13 +9634,13 @@
         <v>40</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="J217" s="0">
-        <v>5904.6377000000002</v>
+        <v>202.81960000000001</v>
       </c>
     </row>
     <row r="218">
@@ -9657,22 +9657,22 @@
         <v>23</v>
       </c>
       <c r="E218" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F218" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G218" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H218" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="J218" s="0">
-        <v>4907.7012000000004</v>
+        <v>383.23849999999999</v>
       </c>
     </row>
     <row r="219">
@@ -9689,22 +9689,22 @@
         <v>23</v>
       </c>
       <c r="E219" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F219" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G219" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H219" s="0" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="J219" s="0">
-        <v>202.81960000000001</v>
+        <v>363.8911</v>
       </c>
     </row>
     <row r="220">
@@ -9724,19 +9724,19 @@
         <v>29</v>
       </c>
       <c r="F220" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G220" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="J220" s="0">
-        <v>383.23849999999999</v>
+        <v>355.88670000000002</v>
       </c>
     </row>
     <row r="221">
@@ -9756,19 +9756,19 @@
         <v>29</v>
       </c>
       <c r="F221" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G221" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="J221" s="0">
-        <v>363.8911</v>
+        <v>351.3347</v>
       </c>
     </row>
     <row r="222">
@@ -9788,19 +9788,19 @@
         <v>29</v>
       </c>
       <c r="F222" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G222" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J222" s="0">
-        <v>355.88670000000002</v>
+        <v>333.8578</v>
       </c>
     </row>
     <row r="223">
@@ -9820,19 +9820,19 @@
         <v>29</v>
       </c>
       <c r="F223" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G223" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H223" s="0" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="J223" s="0">
-        <v>351.3347</v>
+        <v>313.44380000000001</v>
       </c>
     </row>
     <row r="224">
@@ -9852,19 +9852,19 @@
         <v>29</v>
       </c>
       <c r="F224" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G224" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H224" s="0" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="J224" s="0">
-        <v>333.8578</v>
+        <v>238.27189999999999</v>
       </c>
     </row>
     <row r="225">
@@ -9884,19 +9884,19 @@
         <v>29</v>
       </c>
       <c r="F225" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G225" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H225" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="J225" s="0">
-        <v>313.44380000000001</v>
+        <v>141.53020000000001</v>
       </c>
     </row>
     <row r="226">
@@ -9910,25 +9910,25 @@
         <v>7</v>
       </c>
       <c r="D226" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E226" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F226" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G226" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H226" s="0" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="J226" s="0">
-        <v>238.27189999999999</v>
+        <v>6671.5464000000002</v>
       </c>
     </row>
     <row r="227">
@@ -9942,25 +9942,25 @@
         <v>7</v>
       </c>
       <c r="D227" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E227" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F227" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G227" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H227" s="0" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="J227" s="0">
-        <v>141.53020000000001</v>
+        <v>2604.8850000000002</v>
       </c>
     </row>
     <row r="228">
@@ -9977,7 +9977,7 @@
         <v>24</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F228" s="0" t="s">
         <v>31</v>
@@ -9986,13 +9986,13 @@
         <v>40</v>
       </c>
       <c r="H228" s="0" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="J228" s="0">
-        <v>6671.5464000000002</v>
+        <v>539.66269999999997</v>
       </c>
     </row>
     <row r="229">
@@ -10009,22 +10009,22 @@
         <v>24</v>
       </c>
       <c r="E229" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F229" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G229" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H229" s="0" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="J229" s="0">
-        <v>2604.8850000000002</v>
+        <v>429.82010000000002</v>
       </c>
     </row>
     <row r="230">
@@ -10041,22 +10041,22 @@
         <v>24</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F230" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G230" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H230" s="0" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="J230" s="0">
-        <v>539.66269999999997</v>
+        <v>421.38249999999999</v>
       </c>
     </row>
     <row r="231">
@@ -10076,19 +10076,19 @@
         <v>29</v>
       </c>
       <c r="F231" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G231" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H231" s="0" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="J231" s="0">
-        <v>429.82010000000002</v>
+        <v>417.74880000000002</v>
       </c>
     </row>
     <row r="232">
@@ -10108,19 +10108,19 @@
         <v>29</v>
       </c>
       <c r="F232" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G232" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H232" s="0" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="J232" s="0">
-        <v>421.38249999999999</v>
+        <v>393.11059999999998</v>
       </c>
     </row>
     <row r="233">
@@ -10140,19 +10140,19 @@
         <v>29</v>
       </c>
       <c r="F233" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G233" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H233" s="0" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="J233" s="0">
-        <v>417.74880000000002</v>
+        <v>392.10489999999999</v>
       </c>
     </row>
     <row r="234">
@@ -10172,19 +10172,19 @@
         <v>29</v>
       </c>
       <c r="F234" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G234" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H234" s="0" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="J234" s="0">
-        <v>393.11059999999998</v>
+        <v>387.5043</v>
       </c>
     </row>
     <row r="235">
@@ -10204,19 +10204,19 @@
         <v>29</v>
       </c>
       <c r="F235" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G235" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H235" s="0" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="J235" s="0">
-        <v>392.10489999999999</v>
+        <v>215.23259999999999</v>
       </c>
     </row>
     <row r="236">
@@ -10227,28 +10227,28 @@
         <v>4</v>
       </c>
       <c r="C236" s="0" t="s">
-        <v>7</v>
+        <v>655</v>
       </c>
       <c r="D236" s="0" t="s">
-        <v>24</v>
+        <v>801</v>
       </c>
       <c r="E236" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F236" s="0" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G236" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H236" s="0" t="s">
-        <v>255</v>
+        <v>693</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>556</v>
+        <v>804</v>
       </c>
       <c r="J236" s="0">
-        <v>387.5043</v>
+        <v>6179.7012000000004</v>
       </c>
     </row>
     <row r="237">
@@ -10259,28 +10259,28 @@
         <v>4</v>
       </c>
       <c r="C237" s="0" t="s">
-        <v>7</v>
+        <v>655</v>
       </c>
       <c r="D237" s="0" t="s">
-        <v>24</v>
+        <v>801</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F237" s="0" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G237" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H237" s="0" t="s">
-        <v>256</v>
+        <v>694</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>557</v>
+        <v>805</v>
       </c>
       <c r="J237" s="0">
-        <v>215.23259999999999</v>
+        <v>2590.0304999999999</v>
       </c>
     </row>
     <row r="238">
@@ -10297,7 +10297,7 @@
         <v>801</v>
       </c>
       <c r="E238" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F238" s="0" t="s">
         <v>31</v>
@@ -10306,13 +10306,13 @@
         <v>40</v>
       </c>
       <c r="H238" s="0" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="J238" s="0">
-        <v>6179.7012000000004</v>
+        <v>1052.7577000000001</v>
       </c>
     </row>
     <row r="239">
@@ -10329,7 +10329,7 @@
         <v>801</v>
       </c>
       <c r="E239" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F239" s="0" t="s">
         <v>32</v>
@@ -10338,13 +10338,13 @@
         <v>41</v>
       </c>
       <c r="H239" s="0" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="J239" s="0">
-        <v>2590.0304999999999</v>
+        <v>663.33749999999998</v>
       </c>
     </row>
     <row r="240">
@@ -10361,7 +10361,7 @@
         <v>801</v>
       </c>
       <c r="E240" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F240" s="0" t="s">
         <v>31</v>
@@ -10370,13 +10370,13 @@
         <v>40</v>
       </c>
       <c r="H240" s="0" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="J240" s="0">
-        <v>1052.7577000000001</v>
+        <v>506.81569999999999</v>
       </c>
     </row>
     <row r="241">
@@ -10393,22 +10393,22 @@
         <v>801</v>
       </c>
       <c r="E241" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F241" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G241" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H241" s="0" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="J241" s="0">
-        <v>663.33749999999998</v>
+        <v>408.8279</v>
       </c>
     </row>
     <row r="242">
@@ -10428,19 +10428,19 @@
         <v>29</v>
       </c>
       <c r="F242" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G242" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H242" s="0" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="J242" s="0">
-        <v>506.81569999999999</v>
+        <v>402.4606</v>
       </c>
     </row>
     <row r="243">
@@ -10460,19 +10460,19 @@
         <v>29</v>
       </c>
       <c r="F243" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G243" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H243" s="0" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="J243" s="0">
-        <v>408.8279</v>
+        <v>395.95499999999999</v>
       </c>
     </row>
     <row r="244">
@@ -10492,19 +10492,19 @@
         <v>29</v>
       </c>
       <c r="F244" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G244" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H244" s="0" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="J244" s="0">
-        <v>402.4606</v>
+        <v>384.18630000000002</v>
       </c>
     </row>
     <row r="245">
@@ -10524,19 +10524,19 @@
         <v>29</v>
       </c>
       <c r="F245" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G245" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H245" s="0" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="J245" s="0">
-        <v>395.95499999999999</v>
+        <v>337.53550000000001</v>
       </c>
     </row>
     <row r="246">
@@ -10556,19 +10556,19 @@
         <v>29</v>
       </c>
       <c r="F246" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G246" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H246" s="0" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="J246" s="0">
-        <v>384.18630000000002</v>
+        <v>304.91230000000002</v>
       </c>
     </row>
     <row r="247">
@@ -10588,19 +10588,19 @@
         <v>29</v>
       </c>
       <c r="F247" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G247" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H247" s="0" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="J247" s="0">
-        <v>337.53550000000001</v>
+        <v>125.54000000000001</v>
       </c>
     </row>
     <row r="248">
@@ -10614,25 +10614,25 @@
         <v>655</v>
       </c>
       <c r="D248" s="0" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E248" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F248" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G248" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H248" s="0" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="J248" s="0">
-        <v>304.91230000000002</v>
+        <v>5385.1138000000001</v>
       </c>
     </row>
     <row r="249">
@@ -10646,25 +10646,25 @@
         <v>655</v>
       </c>
       <c r="D249" s="0" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E249" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F249" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G249" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H249" s="0" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="J249" s="0">
-        <v>125.54000000000001</v>
+        <v>2843.9126000000001</v>
       </c>
     </row>
     <row r="250">
@@ -10681,7 +10681,7 @@
         <v>802</v>
       </c>
       <c r="E250" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F250" s="0" t="s">
         <v>31</v>
@@ -10690,13 +10690,13 @@
         <v>40</v>
       </c>
       <c r="H250" s="0" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="J250" s="0">
-        <v>5385.1138000000001</v>
+        <v>710.74549999999999</v>
       </c>
     </row>
     <row r="251">
@@ -10713,7 +10713,7 @@
         <v>802</v>
       </c>
       <c r="E251" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F251" s="0" t="s">
         <v>32</v>
@@ -10722,13 +10722,13 @@
         <v>41</v>
       </c>
       <c r="H251" s="0" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="J251" s="0">
-        <v>2843.9126000000001</v>
+        <v>550.2423</v>
       </c>
     </row>
     <row r="252">
@@ -10745,7 +10745,7 @@
         <v>802</v>
       </c>
       <c r="E252" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F252" s="0" t="s">
         <v>31</v>
@@ -10754,13 +10754,13 @@
         <v>40</v>
       </c>
       <c r="H252" s="0" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="J252" s="0">
-        <v>710.74549999999999</v>
+        <v>438.92590000000001</v>
       </c>
     </row>
     <row r="253">
@@ -10777,22 +10777,22 @@
         <v>802</v>
       </c>
       <c r="E253" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G253" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H253" s="0" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="J253" s="0">
-        <v>550.2423</v>
+        <v>423.42290000000003</v>
       </c>
     </row>
     <row r="254">
@@ -10812,19 +10812,19 @@
         <v>29</v>
       </c>
       <c r="F254" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G254" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H254" s="0" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="J254" s="0">
-        <v>438.92590000000001</v>
+        <v>403.89089999999999</v>
       </c>
     </row>
     <row r="255">
@@ -10844,19 +10844,19 @@
         <v>29</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G255" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H255" s="0" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="J255" s="0">
-        <v>423.42290000000003</v>
+        <v>391.21699999999999</v>
       </c>
     </row>
     <row r="256">
@@ -10876,19 +10876,19 @@
         <v>29</v>
       </c>
       <c r="F256" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G256" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H256" s="0" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="J256" s="0">
-        <v>403.89089999999999</v>
+        <v>383.9436</v>
       </c>
     </row>
     <row r="257">
@@ -10908,19 +10908,19 @@
         <v>29</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G257" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H257" s="0" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="J257" s="0">
-        <v>391.21699999999999</v>
+        <v>312.447</v>
       </c>
     </row>
     <row r="258">
@@ -10940,19 +10940,19 @@
         <v>29</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G258" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H258" s="0" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="J258" s="0">
-        <v>383.9436</v>
+        <v>309.3852</v>
       </c>
     </row>
     <row r="259">
@@ -10972,19 +10972,19 @@
         <v>29</v>
       </c>
       <c r="F259" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G259" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H259" s="0" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="J259" s="0">
-        <v>312.447</v>
+        <v>235.6891</v>
       </c>
     </row>
     <row r="260">
@@ -10998,25 +10998,25 @@
         <v>655</v>
       </c>
       <c r="D260" s="0" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E260" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F260" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G260" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H260" s="0" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="J260" s="0">
-        <v>309.3852</v>
+        <v>6293.9867999999997</v>
       </c>
     </row>
     <row r="261">
@@ -11030,25 +11030,25 @@
         <v>655</v>
       </c>
       <c r="D261" s="0" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E261" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F261" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G261" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H261" s="0" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J261" s="0">
-        <v>235.6891</v>
+        <v>5358.5902999999999</v>
       </c>
     </row>
     <row r="262">
@@ -11065,7 +11065,7 @@
         <v>803</v>
       </c>
       <c r="E262" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F262" s="0" t="s">
         <v>31</v>
@@ -11074,13 +11074,13 @@
         <v>40</v>
       </c>
       <c r="H262" s="0" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="J262" s="0">
-        <v>6293.9867999999997</v>
+        <v>577.04179999999997</v>
       </c>
     </row>
     <row r="263">
@@ -11097,7 +11097,7 @@
         <v>803</v>
       </c>
       <c r="E263" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F263" s="0" t="s">
         <v>32</v>
@@ -11106,13 +11106,13 @@
         <v>41</v>
       </c>
       <c r="H263" s="0" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="J263" s="0">
-        <v>5358.5902999999999</v>
+        <v>518.29719999999998</v>
       </c>
     </row>
     <row r="264">
@@ -11129,7 +11129,7 @@
         <v>803</v>
       </c>
       <c r="E264" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F264" s="0" t="s">
         <v>31</v>
@@ -11138,13 +11138,13 @@
         <v>40</v>
       </c>
       <c r="H264" s="0" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="J264" s="0">
-        <v>577.04179999999997</v>
+        <v>427.73379999999997</v>
       </c>
     </row>
     <row r="265">
@@ -11161,22 +11161,22 @@
         <v>803</v>
       </c>
       <c r="E265" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F265" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G265" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H265" s="0" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="J265" s="0">
-        <v>518.29719999999998</v>
+        <v>404.26459999999997</v>
       </c>
     </row>
     <row r="266">
@@ -11196,19 +11196,19 @@
         <v>29</v>
       </c>
       <c r="F266" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G266" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H266" s="0" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="J266" s="0">
-        <v>427.73379999999997</v>
+        <v>398.51589999999999</v>
       </c>
     </row>
     <row r="267">
@@ -11228,19 +11228,19 @@
         <v>29</v>
       </c>
       <c r="F267" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G267" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H267" s="0" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="J267" s="0">
-        <v>404.26459999999997</v>
+        <v>392.9486</v>
       </c>
     </row>
     <row r="268">
@@ -11260,19 +11260,19 @@
         <v>29</v>
       </c>
       <c r="F268" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G268" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H268" s="0" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J268" s="0">
-        <v>398.51589999999999</v>
+        <v>382.86340000000001</v>
       </c>
     </row>
     <row r="269">
@@ -11292,19 +11292,19 @@
         <v>29</v>
       </c>
       <c r="F269" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G269" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H269" s="0" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="J269" s="0">
-        <v>392.9486</v>
+        <v>368.97640000000001</v>
       </c>
     </row>
     <row r="270">
@@ -11324,19 +11324,19 @@
         <v>29</v>
       </c>
       <c r="F270" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G270" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H270" s="0" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="J270" s="0">
-        <v>382.86340000000001</v>
+        <v>347.17689999999999</v>
       </c>
     </row>
     <row r="271">
@@ -11356,19 +11356,19 @@
         <v>29</v>
       </c>
       <c r="F271" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G271" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H271" s="0" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="J271" s="0">
-        <v>368.97640000000001</v>
+        <v>328.54599999999999</v>
       </c>
     </row>
     <row r="272">
@@ -11379,28 +11379,28 @@
         <v>4</v>
       </c>
       <c r="C272" s="0" t="s">
-        <v>655</v>
+        <v>8</v>
       </c>
       <c r="D272" s="0" t="s">
-        <v>803</v>
+        <v>15</v>
       </c>
       <c r="E272" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F272" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G272" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H272" s="0" t="s">
-        <v>727</v>
+        <v>257</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>838</v>
+        <v>558</v>
       </c>
       <c r="J272" s="0">
-        <v>347.17689999999999</v>
+        <v>5568.125</v>
       </c>
     </row>
     <row r="273">
@@ -11411,28 +11411,28 @@
         <v>4</v>
       </c>
       <c r="C273" s="0" t="s">
-        <v>655</v>
+        <v>8</v>
       </c>
       <c r="D273" s="0" t="s">
-        <v>803</v>
+        <v>15</v>
       </c>
       <c r="E273" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F273" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G273" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H273" s="0" t="s">
-        <v>728</v>
+        <v>258</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>839</v>
+        <v>559</v>
       </c>
       <c r="J273" s="0">
-        <v>328.54599999999999</v>
+        <v>2316.6012999999998</v>
       </c>
     </row>
     <row r="274">
@@ -11449,7 +11449,7 @@
         <v>15</v>
       </c>
       <c r="E274" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F274" s="0" t="s">
         <v>31</v>
@@ -11458,13 +11458,13 @@
         <v>40</v>
       </c>
       <c r="H274" s="0" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="J274" s="0">
-        <v>5568.125</v>
+        <v>504.78460000000001</v>
       </c>
     </row>
     <row r="275">
@@ -11481,7 +11481,7 @@
         <v>15</v>
       </c>
       <c r="E275" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F275" s="0" t="s">
         <v>32</v>
@@ -11490,13 +11490,13 @@
         <v>41</v>
       </c>
       <c r="H275" s="0" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="J275" s="0">
-        <v>2316.6012999999998</v>
+        <v>445.50999999999999</v>
       </c>
     </row>
     <row r="276">
@@ -11513,7 +11513,7 @@
         <v>15</v>
       </c>
       <c r="E276" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F276" s="0" t="s">
         <v>31</v>
@@ -11522,13 +11522,13 @@
         <v>40</v>
       </c>
       <c r="H276" s="0" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="J276" s="0">
-        <v>504.78460000000001</v>
+        <v>401.56920000000002</v>
       </c>
     </row>
     <row r="277">
@@ -11545,22 +11545,22 @@
         <v>15</v>
       </c>
       <c r="E277" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F277" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G277" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H277" s="0" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="J277" s="0">
-        <v>445.50999999999999</v>
+        <v>392.42399999999998</v>
       </c>
     </row>
     <row r="278">
@@ -11580,19 +11580,19 @@
         <v>29</v>
       </c>
       <c r="F278" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G278" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H278" s="0" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="J278" s="0">
-        <v>401.56920000000002</v>
+        <v>368.18880000000001</v>
       </c>
     </row>
     <row r="279">
@@ -11612,19 +11612,19 @@
         <v>29</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G279" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H279" s="0" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="J279" s="0">
-        <v>392.42399999999998</v>
+        <v>366.78320000000002</v>
       </c>
     </row>
     <row r="280">
@@ -11644,19 +11644,19 @@
         <v>29</v>
       </c>
       <c r="F280" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G280" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H280" s="0" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="J280" s="0">
-        <v>368.18880000000001</v>
+        <v>361.8997</v>
       </c>
     </row>
     <row r="281">
@@ -11676,19 +11676,19 @@
         <v>29</v>
       </c>
       <c r="F281" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G281" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="J281" s="0">
-        <v>366.78320000000002</v>
+        <v>322.42989999999998</v>
       </c>
     </row>
     <row r="282">
@@ -11708,19 +11708,19 @@
         <v>29</v>
       </c>
       <c r="F282" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G282" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H282" s="0" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="J282" s="0">
-        <v>361.8997</v>
+        <v>308.6019</v>
       </c>
     </row>
     <row r="283">
@@ -11740,19 +11740,19 @@
         <v>29</v>
       </c>
       <c r="F283" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G283" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H283" s="0" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="J283" s="0">
-        <v>322.42989999999998</v>
+        <v>260.48289999999997</v>
       </c>
     </row>
     <row r="284">
@@ -11766,25 +11766,25 @@
         <v>8</v>
       </c>
       <c r="D284" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E284" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F284" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G284" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H284" s="0" t="s">
-        <v>267</v>
+        <v>103</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="J284" s="0">
-        <v>308.6019</v>
+        <v>6411.3008</v>
       </c>
     </row>
     <row r="285">
@@ -11798,25 +11798,25 @@
         <v>8</v>
       </c>
       <c r="D285" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E285" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F285" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G285" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H285" s="0" t="s">
-        <v>268</v>
+        <v>104</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="J285" s="0">
-        <v>260.48289999999997</v>
+        <v>5363.7114000000001</v>
       </c>
     </row>
     <row r="286">
@@ -11833,7 +11833,7 @@
         <v>16</v>
       </c>
       <c r="E286" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F286" s="0" t="s">
         <v>31</v>
@@ -11842,13 +11842,13 @@
         <v>40</v>
       </c>
       <c r="H286" s="0" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="J286" s="0">
-        <v>6411.3008</v>
+        <v>465.0847</v>
       </c>
     </row>
     <row r="287">
@@ -11865,22 +11865,22 @@
         <v>16</v>
       </c>
       <c r="E287" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F287" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G287" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H287" s="0" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="J287" s="0">
-        <v>5363.7114000000001</v>
+        <v>432.71969999999999</v>
       </c>
     </row>
     <row r="288">
@@ -11897,22 +11897,22 @@
         <v>16</v>
       </c>
       <c r="E288" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F288" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G288" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H288" s="0" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="J288" s="0">
-        <v>561.40689999999995</v>
+        <v>403.6884</v>
       </c>
     </row>
     <row r="289">
@@ -11932,19 +11932,19 @@
         <v>29</v>
       </c>
       <c r="F289" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G289" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H289" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="J289" s="0">
-        <v>465.0847</v>
+        <v>393.85660000000001</v>
       </c>
     </row>
     <row r="290">
@@ -11964,19 +11964,19 @@
         <v>29</v>
       </c>
       <c r="F290" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G290" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H290" s="0" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="J290" s="0">
-        <v>432.71969999999999</v>
+        <v>328.83640000000003</v>
       </c>
     </row>
     <row r="291">
@@ -11996,19 +11996,19 @@
         <v>29</v>
       </c>
       <c r="F291" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G291" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H291" s="0" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="J291" s="0">
-        <v>403.6884</v>
+        <v>289.99919999999997</v>
       </c>
     </row>
     <row r="292">
@@ -12028,19 +12028,19 @@
         <v>29</v>
       </c>
       <c r="F292" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G292" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H292" s="0" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="J292" s="0">
-        <v>393.85660000000001</v>
+        <v>253.50819999999999</v>
       </c>
     </row>
     <row r="293">
@@ -12060,19 +12060,19 @@
         <v>29</v>
       </c>
       <c r="F293" s="0" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G293" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H293" s="0" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="J293" s="0">
-        <v>328.83640000000003</v>
+        <v>156.39179999999999</v>
       </c>
     </row>
     <row r="294">
@@ -12086,25 +12086,25 @@
         <v>8</v>
       </c>
       <c r="D294" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E294" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F294" s="0" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G294" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H294" s="0" t="s">
-        <v>112</v>
+        <v>269</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="J294" s="0">
-        <v>289.99919999999997</v>
+        <v>5610.5132000000003</v>
       </c>
     </row>
     <row r="295">
@@ -12118,25 +12118,25 @@
         <v>8</v>
       </c>
       <c r="D295" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E295" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F295" s="0" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G295" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H295" s="0" t="s">
-        <v>113</v>
+        <v>270</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="J295" s="0">
-        <v>253.50819999999999</v>
+        <v>2526.6718999999998</v>
       </c>
     </row>
     <row r="296">
@@ -12150,25 +12150,25 @@
         <v>8</v>
       </c>
       <c r="D296" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E296" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F296" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G296" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H296" s="0" t="s">
-        <v>114</v>
+        <v>271</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="J296" s="0">
-        <v>156.39179999999999</v>
+        <v>663.2672</v>
       </c>
     </row>
     <row r="297">
@@ -12185,22 +12185,22 @@
         <v>17</v>
       </c>
       <c r="E297" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F297" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G297" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H297" s="0" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="J297" s="0">
-        <v>5610.5132000000003</v>
+        <v>553.69179999999994</v>
       </c>
     </row>
     <row r="298">
@@ -12217,22 +12217,22 @@
         <v>17</v>
       </c>
       <c r="E298" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F298" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G298" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H298" s="0" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="J298" s="0">
-        <v>2526.6718999999998</v>
+        <v>436.38159999999999</v>
       </c>
     </row>
     <row r="299">
@@ -12249,22 +12249,22 @@
         <v>17</v>
       </c>
       <c r="E299" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F299" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G299" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H299" s="0" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="J299" s="0">
-        <v>663.2672</v>
+        <v>411.78269999999998</v>
       </c>
     </row>
     <row r="300">
@@ -12281,22 +12281,22 @@
         <v>17</v>
       </c>
       <c r="E300" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F300" s="0" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G300" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H300" s="0" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="J300" s="0">
-        <v>553.69179999999994</v>
+        <v>407.44670000000002</v>
       </c>
     </row>
     <row r="301">
@@ -12316,19 +12316,19 @@
         <v>29</v>
       </c>
       <c r="F301" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G301" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H301" s="0" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="J301" s="0">
-        <v>436.38159999999999</v>
+        <v>390.17970000000003</v>
       </c>
     </row>
     <row r="302">
@@ -12348,19 +12348,19 @@
         <v>29</v>
       </c>
       <c r="F302" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G302" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H302" s="0" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="J302" s="0">
-        <v>411.78269999999998</v>
+        <v>379.34300000000002</v>
       </c>
     </row>
     <row r="303">
@@ -12380,19 +12380,19 @@
         <v>29</v>
       </c>
       <c r="F303" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G303" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H303" s="0" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="J303" s="0">
-        <v>407.44670000000002</v>
+        <v>378.32549999999998</v>
       </c>
     </row>
     <row r="304">
@@ -12412,19 +12412,19 @@
         <v>29</v>
       </c>
       <c r="F304" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G304" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H304" s="0" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="J304" s="0">
-        <v>390.17970000000003</v>
+        <v>248.1077</v>
       </c>
     </row>
     <row r="305">
@@ -12444,19 +12444,19 @@
         <v>29</v>
       </c>
       <c r="F305" s="0" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G305" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H305" s="0" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="J305" s="0">
-        <v>379.34300000000002</v>
+        <v>155.72280000000001</v>
       </c>
     </row>
     <row r="306">
@@ -12470,25 +12470,25 @@
         <v>8</v>
       </c>
       <c r="D306" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E306" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F306" s="0" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G306" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H306" s="0" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="J306" s="0">
-        <v>378.32549999999998</v>
+        <v>6378.5679</v>
       </c>
     </row>
     <row r="307">
@@ -12502,25 +12502,25 @@
         <v>8</v>
       </c>
       <c r="D307" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E307" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F307" s="0" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G307" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H307" s="0" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="J307" s="0">
-        <v>248.1077</v>
+        <v>3677.8054000000002</v>
       </c>
     </row>
     <row r="308">
@@ -12534,25 +12534,25 @@
         <v>8</v>
       </c>
       <c r="D308" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E308" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F308" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G308" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H308" s="0" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="J308" s="0">
-        <v>155.72280000000001</v>
+        <v>990.75639999999999</v>
       </c>
     </row>
     <row r="309">
@@ -12569,22 +12569,22 @@
         <v>25</v>
       </c>
       <c r="E309" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F309" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G309" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H309" s="0" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="J309" s="0">
-        <v>6378.5679</v>
+        <v>912.61609999999996</v>
       </c>
     </row>
     <row r="310">
@@ -12601,22 +12601,22 @@
         <v>25</v>
       </c>
       <c r="E310" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F310" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G310" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H310" s="0" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="J310" s="0">
-        <v>3677.8054000000002</v>
+        <v>448.30200000000002</v>
       </c>
     </row>
     <row r="311">
@@ -12633,22 +12633,22 @@
         <v>25</v>
       </c>
       <c r="E311" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F311" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G311" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H311" s="0" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="J311" s="0">
-        <v>990.75639999999999</v>
+        <v>415.84109999999998</v>
       </c>
     </row>
     <row r="312">
@@ -12665,22 +12665,22 @@
         <v>25</v>
       </c>
       <c r="E312" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F312" s="0" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G312" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H312" s="0" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="J312" s="0">
-        <v>912.61609999999996</v>
+        <v>380.94420000000002</v>
       </c>
     </row>
     <row r="313">
@@ -12700,19 +12700,19 @@
         <v>29</v>
       </c>
       <c r="F313" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G313" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H313" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="J313" s="0">
-        <v>448.30200000000002</v>
+        <v>359.60860000000002</v>
       </c>
     </row>
     <row r="314">
@@ -12732,19 +12732,19 @@
         <v>29</v>
       </c>
       <c r="F314" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G314" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H314" s="0" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="J314" s="0">
-        <v>415.84109999999998</v>
+        <v>338.8168</v>
       </c>
     </row>
     <row r="315">
@@ -12764,19 +12764,19 @@
         <v>29</v>
       </c>
       <c r="F315" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G315" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H315" s="0" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="J315" s="0">
-        <v>380.94420000000002</v>
+        <v>320.63470000000001</v>
       </c>
     </row>
     <row r="316">
@@ -12796,19 +12796,19 @@
         <v>29</v>
       </c>
       <c r="F316" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G316" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H316" s="0" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="J316" s="0">
-        <v>359.60860000000002</v>
+        <v>287.04489999999999</v>
       </c>
     </row>
     <row r="317">
@@ -12828,19 +12828,19 @@
         <v>29</v>
       </c>
       <c r="F317" s="0" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G317" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H317" s="0" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="J317" s="0">
-        <v>338.8168</v>
+        <v>107.8788</v>
       </c>
     </row>
     <row r="318">
@@ -12851,28 +12851,28 @@
         <v>4</v>
       </c>
       <c r="C318" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D318" s="0" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E318" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F318" s="0" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G318" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H318" s="0" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="J318" s="0">
-        <v>320.63470000000001</v>
+        <v>5099.2568000000001</v>
       </c>
     </row>
     <row r="319">
@@ -12883,28 +12883,28 @@
         <v>4</v>
       </c>
       <c r="C319" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D319" s="0" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E319" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F319" s="0" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G319" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H319" s="0" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="J319" s="0">
-        <v>287.04489999999999</v>
+        <v>2383.1239999999998</v>
       </c>
     </row>
     <row r="320">
@@ -12915,28 +12915,28 @@
         <v>4</v>
       </c>
       <c r="C320" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D320" s="0" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E320" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F320" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G320" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H320" s="0" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="J320" s="0">
-        <v>107.8788</v>
+        <v>670.93709999999999</v>
       </c>
     </row>
     <row r="321">
@@ -12953,22 +12953,22 @@
         <v>18</v>
       </c>
       <c r="E321" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F321" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G321" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H321" s="0" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="J321" s="0">
-        <v>5099.2568000000001</v>
+        <v>459.24430000000001</v>
       </c>
     </row>
     <row r="322">
@@ -12985,22 +12985,22 @@
         <v>18</v>
       </c>
       <c r="E322" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F322" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G322" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H322" s="0" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="J322" s="0">
-        <v>2383.1239999999998</v>
+        <v>415.84710000000001</v>
       </c>
     </row>
     <row r="323">
@@ -13017,22 +13017,22 @@
         <v>18</v>
       </c>
       <c r="E323" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F323" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G323" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H323" s="0" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="J323" s="0">
-        <v>670.93709999999999</v>
+        <v>404.09039999999999</v>
       </c>
     </row>
     <row r="324">
@@ -13049,22 +13049,22 @@
         <v>18</v>
       </c>
       <c r="E324" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F324" s="0" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G324" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H324" s="0" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="J324" s="0">
-        <v>459.24430000000001</v>
+        <v>370.1207</v>
       </c>
     </row>
     <row r="325">
@@ -13084,19 +13084,19 @@
         <v>29</v>
       </c>
       <c r="F325" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G325" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H325" s="0" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="J325" s="0">
-        <v>415.84710000000001</v>
+        <v>369.87549999999999</v>
       </c>
     </row>
     <row r="326">
@@ -13116,19 +13116,19 @@
         <v>29</v>
       </c>
       <c r="F326" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G326" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H326" s="0" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="J326" s="0">
-        <v>404.09039999999999</v>
+        <v>332.15789999999998</v>
       </c>
     </row>
     <row r="327">
@@ -13148,19 +13148,19 @@
         <v>29</v>
       </c>
       <c r="F327" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G327" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H327" s="0" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="J327" s="0">
-        <v>370.1207</v>
+        <v>310.02600000000001</v>
       </c>
     </row>
     <row r="328">
@@ -13180,19 +13180,19 @@
         <v>29</v>
       </c>
       <c r="F328" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G328" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H328" s="0" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="J328" s="0">
-        <v>369.87549999999999</v>
+        <v>137.19120000000001</v>
       </c>
     </row>
     <row r="329">
@@ -13206,25 +13206,25 @@
         <v>9</v>
       </c>
       <c r="D329" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E329" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F329" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G329" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H329" s="0" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="J329" s="0">
-        <v>332.15789999999998</v>
+        <v>6147.9931999999999</v>
       </c>
     </row>
     <row r="330">
@@ -13238,25 +13238,25 @@
         <v>9</v>
       </c>
       <c r="D330" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E330" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F330" s="0" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G330" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H330" s="0" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="J330" s="0">
-        <v>310.02600000000001</v>
+        <v>4509.7578000000003</v>
       </c>
     </row>
     <row r="331">
@@ -13270,25 +13270,25 @@
         <v>9</v>
       </c>
       <c r="D331" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E331" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F331" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G331" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H331" s="0" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="J331" s="0">
-        <v>137.19120000000001</v>
+        <v>999.82090000000005</v>
       </c>
     </row>
     <row r="332">
@@ -13305,22 +13305,22 @@
         <v>19</v>
       </c>
       <c r="E332" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F332" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G332" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H332" s="0" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="J332" s="0">
-        <v>6147.9931999999999</v>
+        <v>829.32470000000001</v>
       </c>
     </row>
     <row r="333">
@@ -13337,22 +13337,22 @@
         <v>19</v>
       </c>
       <c r="E333" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F333" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G333" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H333" s="0" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="J333" s="0">
-        <v>4509.7578000000003</v>
+        <v>460.868</v>
       </c>
     </row>
     <row r="334">
@@ -13369,22 +13369,22 @@
         <v>19</v>
       </c>
       <c r="E334" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F334" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G334" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H334" s="0" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="J334" s="0">
-        <v>999.82090000000005</v>
+        <v>418.91930000000002</v>
       </c>
     </row>
     <row r="335">
@@ -13401,22 +13401,22 @@
         <v>19</v>
       </c>
       <c r="E335" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F335" s="0" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G335" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H335" s="0" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="J335" s="0">
-        <v>829.32470000000001</v>
+        <v>377.29809999999998</v>
       </c>
     </row>
     <row r="336">
@@ -13436,19 +13436,19 @@
         <v>29</v>
       </c>
       <c r="F336" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G336" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H336" s="0" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="J336" s="0">
-        <v>460.868</v>
+        <v>376.07799999999998</v>
       </c>
     </row>
     <row r="337">
@@ -13468,19 +13468,19 @@
         <v>29</v>
       </c>
       <c r="F337" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G337" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H337" s="0" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="J337" s="0">
-        <v>418.91930000000002</v>
+        <v>345.4522</v>
       </c>
     </row>
     <row r="338">
@@ -13500,19 +13500,19 @@
         <v>29</v>
       </c>
       <c r="F338" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G338" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H338" s="0" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="J338" s="0">
-        <v>377.29809999999998</v>
+        <v>333.1805</v>
       </c>
     </row>
     <row r="339">
@@ -13532,19 +13532,19 @@
         <v>29</v>
       </c>
       <c r="F339" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G339" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H339" s="0" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="J339" s="0">
-        <v>376.07799999999998</v>
+        <v>297.38940000000002</v>
       </c>
     </row>
     <row r="340">
@@ -13564,19 +13564,19 @@
         <v>29</v>
       </c>
       <c r="F340" s="0" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G340" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H340" s="0" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="J340" s="0">
-        <v>345.4522</v>
+        <v>196.88849999999999</v>
       </c>
     </row>
     <row r="341">
@@ -13590,25 +13590,25 @@
         <v>9</v>
       </c>
       <c r="D341" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E341" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F341" s="0" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G341" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H341" s="0" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="J341" s="0">
-        <v>333.1805</v>
+        <v>5372.8154000000004</v>
       </c>
     </row>
     <row r="342">
@@ -13622,25 +13622,25 @@
         <v>9</v>
       </c>
       <c r="D342" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E342" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F342" s="0" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G342" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H342" s="0" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="J342" s="0">
-        <v>297.38940000000002</v>
+        <v>5089.0283</v>
       </c>
     </row>
     <row r="343">
@@ -13654,25 +13654,25 @@
         <v>9</v>
       </c>
       <c r="D343" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E343" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F343" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G343" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H343" s="0" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="J343" s="0">
-        <v>196.88849999999999</v>
+        <v>173.3056</v>
       </c>
     </row>
     <row r="344">
@@ -13689,7 +13689,7 @@
         <v>20</v>
       </c>
       <c r="E344" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F344" s="0" t="s">
         <v>31</v>
@@ -13698,13 +13698,13 @@
         <v>40</v>
       </c>
       <c r="H344" s="0" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="J344" s="0">
-        <v>5372.8154000000004</v>
+        <v>414.66230000000002</v>
       </c>
     </row>
     <row r="345">
@@ -13721,22 +13721,22 @@
         <v>20</v>
       </c>
       <c r="E345" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F345" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G345" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H345" s="0" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="J345" s="0">
-        <v>5089.0283</v>
+        <v>403.9067</v>
       </c>
     </row>
     <row r="346">
@@ -13753,22 +13753,22 @@
         <v>20</v>
       </c>
       <c r="E346" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F346" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G346" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H346" s="0" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="J346" s="0">
-        <v>623.85149999999999</v>
+        <v>374.75290000000001</v>
       </c>
     </row>
     <row r="347">
@@ -13785,22 +13785,22 @@
         <v>20</v>
       </c>
       <c r="E347" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F347" s="0" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G347" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H347" s="0" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="J347" s="0">
-        <v>173.3056</v>
+        <v>372.04629999999997</v>
       </c>
     </row>
     <row r="348">
@@ -13820,19 +13820,19 @@
         <v>29</v>
       </c>
       <c r="F348" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G348" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H348" s="0" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="J348" s="0">
-        <v>414.66230000000002</v>
+        <v>372.0009</v>
       </c>
     </row>
     <row r="349">
@@ -13852,19 +13852,19 @@
         <v>29</v>
       </c>
       <c r="F349" s="0" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G349" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H349" s="0" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="J349" s="0">
-        <v>403.9067</v>
+        <v>318.33179999999999</v>
       </c>
     </row>
     <row r="350">
@@ -13884,19 +13884,19 @@
         <v>29</v>
       </c>
       <c r="F350" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G350" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H350" s="0" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="J350" s="0">
-        <v>374.75290000000001</v>
+        <v>295.59719999999999</v>
       </c>
     </row>
     <row r="351">
@@ -13916,19 +13916,19 @@
         <v>29</v>
       </c>
       <c r="F351" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G351" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H351" s="0" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="J351" s="0">
-        <v>372.04629999999997</v>
+        <v>137.02930000000001</v>
       </c>
     </row>
     <row r="352">
@@ -13942,25 +13942,25 @@
         <v>9</v>
       </c>
       <c r="D352" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E352" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F352" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G352" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H352" s="0" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="J352" s="0">
-        <v>372.0009</v>
+        <v>4746.6201000000001</v>
       </c>
     </row>
     <row r="353">
@@ -13974,25 +13974,25 @@
         <v>9</v>
       </c>
       <c r="D353" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E353" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F353" s="0" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G353" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H353" s="0" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I353" s="0" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="J353" s="0">
-        <v>318.33179999999999</v>
+        <v>4426.7367999999997</v>
       </c>
     </row>
     <row r="354">
@@ -14006,25 +14006,25 @@
         <v>9</v>
       </c>
       <c r="D354" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E354" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F354" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G354" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H354" s="0" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="I354" s="0" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="J354" s="0">
-        <v>295.59719999999999</v>
+        <v>502.13749999999999</v>
       </c>
     </row>
     <row r="355">
@@ -14038,25 +14038,25 @@
         <v>9</v>
       </c>
       <c r="D355" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E355" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F355" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G355" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H355" s="0" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="I355" s="0" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="J355" s="0">
-        <v>137.02930000000001</v>
+        <v>439.52850000000001</v>
       </c>
     </row>
     <row r="356">
@@ -14073,22 +14073,22 @@
         <v>21</v>
       </c>
       <c r="E356" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F356" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G356" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H356" s="0" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="I356" s="0" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="J356" s="0">
-        <v>4746.6201000000001</v>
+        <v>423.6062</v>
       </c>
     </row>
     <row r="357">
@@ -14105,22 +14105,22 @@
         <v>21</v>
       </c>
       <c r="E357" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F357" s="0" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G357" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H357" s="0" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="I357" s="0" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="J357" s="0">
-        <v>4426.7367999999997</v>
+        <v>388.16570000000002</v>
       </c>
     </row>
     <row r="358">
@@ -14137,22 +14137,22 @@
         <v>21</v>
       </c>
       <c r="E358" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F358" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G358" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H358" s="0" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="I358" s="0" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="J358" s="0">
-        <v>502.13749999999999</v>
+        <v>361.62639999999999</v>
       </c>
     </row>
     <row r="359">
@@ -14172,19 +14172,19 @@
         <v>29</v>
       </c>
       <c r="F359" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G359" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H359" s="0" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="I359" s="0" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="J359" s="0">
-        <v>439.52850000000001</v>
+        <v>319.28989999999999</v>
       </c>
     </row>
     <row r="360">
@@ -14204,19 +14204,19 @@
         <v>29</v>
       </c>
       <c r="F360" s="0" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G360" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H360" s="0" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="I360" s="0" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="J360" s="0">
-        <v>423.6062</v>
+        <v>283.29320000000001</v>
       </c>
     </row>
     <row r="361">
@@ -14236,19 +14236,19 @@
         <v>29</v>
       </c>
       <c r="F361" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G361" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H361" s="0" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="I361" s="0" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="J361" s="0">
-        <v>388.16570000000002</v>
+        <v>254.66130000000001</v>
       </c>
     </row>
     <row r="362">

--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="52729" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="75308" uniqueCount="875">
   <si>
     <t>Year</t>
   </si>
@@ -7810,13 +7810,13 @@
         <v>40</v>
       </c>
       <c r="H160" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J160" s="0">
-        <v>466.59890000000001</v>
+        <v>348.95269999999999</v>
       </c>
     </row>
     <row r="161">
@@ -7842,13 +7842,13 @@
         <v>40</v>
       </c>
       <c r="H161" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J161" s="0">
-        <v>348.95269999999999</v>
+        <v>320.45060000000001</v>
       </c>
     </row>
     <row r="162">
@@ -7874,13 +7874,13 @@
         <v>40</v>
       </c>
       <c r="H162" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J162" s="0">
-        <v>320.45060000000001</v>
+        <v>306.95499999999999</v>
       </c>
     </row>
     <row r="163">
@@ -7906,13 +7906,13 @@
         <v>40</v>
       </c>
       <c r="H163" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J163" s="0">
-        <v>306.95499999999999</v>
+        <v>286.13639999999998</v>
       </c>
     </row>
     <row r="164">
@@ -7938,13 +7938,13 @@
         <v>41</v>
       </c>
       <c r="H164" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J164" s="0">
-        <v>286.13639999999998</v>
+        <v>270.46800000000002</v>
       </c>
     </row>
     <row r="165">
@@ -7970,13 +7970,13 @@
         <v>41</v>
       </c>
       <c r="H165" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J165" s="0">
-        <v>270.46800000000002</v>
+        <v>266.42959999999999</v>
       </c>
     </row>
     <row r="166">
@@ -8002,13 +8002,13 @@
         <v>41</v>
       </c>
       <c r="H166" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J166" s="0">
-        <v>266.42959999999999</v>
+        <v>198.7653</v>
       </c>
     </row>
     <row r="167">
@@ -8022,25 +8022,25 @@
         <v>6</v>
       </c>
       <c r="D167" s="0" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E167" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F167" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G167" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H167" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J167" s="0">
-        <v>198.7653</v>
+        <v>6949.5127000000002</v>
       </c>
     </row>
     <row r="168">
@@ -8060,19 +8060,19 @@
         <v>27</v>
       </c>
       <c r="F168" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G168" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H168" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J168" s="0">
-        <v>6949.5127000000002</v>
+        <v>1918.3168000000001</v>
       </c>
     </row>
     <row r="169">
@@ -8089,22 +8089,22 @@
         <v>11</v>
       </c>
       <c r="E169" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F169" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G169" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H169" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J169" s="0">
-        <v>1918.3168000000001</v>
+        <v>842.53420000000006</v>
       </c>
     </row>
     <row r="170">
@@ -8124,19 +8124,19 @@
         <v>28</v>
       </c>
       <c r="F170" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G170" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H170" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J170" s="0">
-        <v>842.53420000000006</v>
+        <v>625.51949999999999</v>
       </c>
     </row>
     <row r="171">
@@ -8153,22 +8153,22 @@
         <v>11</v>
       </c>
       <c r="E171" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F171" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G171" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H171" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J171" s="0">
-        <v>625.51949999999999</v>
+        <v>403.39569999999998</v>
       </c>
     </row>
     <row r="172">
@@ -8188,19 +8188,19 @@
         <v>29</v>
       </c>
       <c r="F172" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G172" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H172" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J172" s="0">
-        <v>403.39569999999998</v>
+        <v>401.83440000000002</v>
       </c>
     </row>
     <row r="173">
@@ -8220,19 +8220,19 @@
         <v>29</v>
       </c>
       <c r="F173" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G173" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H173" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J173" s="0">
-        <v>401.83440000000002</v>
+        <v>401.53390000000002</v>
       </c>
     </row>
     <row r="174">
@@ -8252,19 +8252,19 @@
         <v>29</v>
       </c>
       <c r="F174" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G174" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H174" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J174" s="0">
-        <v>401.53390000000002</v>
+        <v>325.73790000000002</v>
       </c>
     </row>
     <row r="175">
@@ -8284,19 +8284,19 @@
         <v>29</v>
       </c>
       <c r="F175" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G175" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H175" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J175" s="0">
-        <v>325.73790000000002</v>
+        <v>306.47129999999999</v>
       </c>
     </row>
     <row r="176">
@@ -8316,19 +8316,19 @@
         <v>29</v>
       </c>
       <c r="F176" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G176" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H176" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J176" s="0">
-        <v>306.47129999999999</v>
+        <v>297.54129999999998</v>
       </c>
     </row>
     <row r="177">
@@ -8348,19 +8348,19 @@
         <v>29</v>
       </c>
       <c r="F177" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G177" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H177" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J177" s="0">
-        <v>297.54129999999998</v>
+        <v>251.23050000000001</v>
       </c>
     </row>
     <row r="178">
@@ -8380,19 +8380,19 @@
         <v>29</v>
       </c>
       <c r="F178" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G178" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H178" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J178" s="0">
-        <v>251.23050000000001</v>
+        <v>104.34829999999999</v>
       </c>
     </row>
     <row r="179">
@@ -8406,25 +8406,25 @@
         <v>6</v>
       </c>
       <c r="D179" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E179" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F179" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G179" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H179" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J179" s="0">
-        <v>104.34829999999999</v>
+        <v>5196.1244999999999</v>
       </c>
     </row>
     <row r="180">
@@ -8441,7 +8441,7 @@
         <v>12</v>
       </c>
       <c r="E180" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F180" s="0" t="s">
         <v>31</v>
@@ -8450,13 +8450,13 @@
         <v>40</v>
       </c>
       <c r="H180" s="0" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="J180" s="0">
-        <v>5196.1244999999999</v>
+        <v>554.0693</v>
       </c>
     </row>
     <row r="181">
@@ -8473,7 +8473,7 @@
         <v>12</v>
       </c>
       <c r="E181" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F181" s="0" t="s">
         <v>32</v>
@@ -8482,13 +8482,13 @@
         <v>41</v>
       </c>
       <c r="H181" s="0" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="J181" s="0">
-        <v>2798.9209000000001</v>
+        <v>97.465900000000005</v>
       </c>
     </row>
     <row r="182">
@@ -8505,7 +8505,7 @@
         <v>12</v>
       </c>
       <c r="E182" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F182" s="0" t="s">
         <v>31</v>
@@ -8514,13 +8514,13 @@
         <v>40</v>
       </c>
       <c r="H182" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="J182" s="0">
-        <v>554.0693</v>
+        <v>413.24349999999998</v>
       </c>
     </row>
     <row r="183">
@@ -8537,22 +8537,22 @@
         <v>12</v>
       </c>
       <c r="E183" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F183" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G183" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H183" s="0" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="J183" s="0">
-        <v>97.465900000000005</v>
+        <v>390.69720000000001</v>
       </c>
     </row>
     <row r="184">
@@ -8572,19 +8572,19 @@
         <v>29</v>
       </c>
       <c r="F184" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G184" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H184" s="0" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="J184" s="0">
-        <v>413.24349999999998</v>
+        <v>384.44110000000001</v>
       </c>
     </row>
     <row r="185">
@@ -8604,19 +8604,19 @@
         <v>29</v>
       </c>
       <c r="F185" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G185" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H185" s="0" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="J185" s="0">
-        <v>390.69720000000001</v>
+        <v>369.39760000000001</v>
       </c>
     </row>
     <row r="186">
@@ -8636,19 +8636,19 @@
         <v>29</v>
       </c>
       <c r="F186" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G186" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H186" s="0" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="J186" s="0">
-        <v>384.44110000000001</v>
+        <v>355.85449999999997</v>
       </c>
     </row>
     <row r="187">
@@ -8668,19 +8668,19 @@
         <v>29</v>
       </c>
       <c r="F187" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G187" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H187" s="0" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="J187" s="0">
-        <v>369.39760000000001</v>
+        <v>332.20139999999998</v>
       </c>
     </row>
     <row r="188">
@@ -8700,19 +8700,19 @@
         <v>29</v>
       </c>
       <c r="F188" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G188" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H188" s="0" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="J188" s="0">
-        <v>355.85449999999997</v>
+        <v>304.4751</v>
       </c>
     </row>
     <row r="189">
@@ -8732,19 +8732,19 @@
         <v>29</v>
       </c>
       <c r="F189" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G189" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H189" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J189" s="0">
-        <v>332.20139999999998</v>
+        <v>263.24160000000001</v>
       </c>
     </row>
     <row r="190">
@@ -8755,28 +8755,28 @@
         <v>4</v>
       </c>
       <c r="C190" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D190" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E190" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F190" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G190" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H190" s="0" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="J190" s="0">
-        <v>304.4751</v>
+        <v>5598.6216000000004</v>
       </c>
     </row>
     <row r="191">
@@ -8787,28 +8787,28 @@
         <v>4</v>
       </c>
       <c r="C191" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D191" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E191" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F191" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G191" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H191" s="0" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="J191" s="0">
-        <v>263.24160000000001</v>
+        <v>4298.6826000000001</v>
       </c>
     </row>
     <row r="192">
@@ -8825,7 +8825,7 @@
         <v>13</v>
       </c>
       <c r="E192" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F192" s="0" t="s">
         <v>31</v>
@@ -8834,13 +8834,13 @@
         <v>40</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="J192" s="0">
-        <v>5598.6216000000004</v>
+        <v>831.18269999999996</v>
       </c>
     </row>
     <row r="193">
@@ -8857,7 +8857,7 @@
         <v>13</v>
       </c>
       <c r="E193" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F193" s="0" t="s">
         <v>32</v>
@@ -8866,13 +8866,13 @@
         <v>41</v>
       </c>
       <c r="H193" s="0" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J193" s="0">
-        <v>4298.6826000000001</v>
+        <v>746.42259999999999</v>
       </c>
     </row>
     <row r="194">
@@ -8889,7 +8889,7 @@
         <v>13</v>
       </c>
       <c r="E194" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F194" s="0" t="s">
         <v>31</v>
@@ -8898,13 +8898,13 @@
         <v>40</v>
       </c>
       <c r="H194" s="0" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="J194" s="0">
-        <v>831.18269999999996</v>
+        <v>477.65440000000001</v>
       </c>
     </row>
     <row r="195">
@@ -8921,22 +8921,22 @@
         <v>13</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F195" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G195" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H195" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J195" s="0">
-        <v>746.42259999999999</v>
+        <v>455.09550000000002</v>
       </c>
     </row>
     <row r="196">
@@ -8956,19 +8956,19 @@
         <v>29</v>
       </c>
       <c r="F196" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G196" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H196" s="0" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="J196" s="0">
-        <v>477.65440000000001</v>
+        <v>442.9828</v>
       </c>
     </row>
     <row r="197">
@@ -8988,19 +8988,19 @@
         <v>29</v>
       </c>
       <c r="F197" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G197" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H197" s="0" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J197" s="0">
-        <v>455.09550000000002</v>
+        <v>403.95710000000003</v>
       </c>
     </row>
     <row r="198">
@@ -9020,19 +9020,19 @@
         <v>29</v>
       </c>
       <c r="F198" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G198" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H198" s="0" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="J198" s="0">
-        <v>442.9828</v>
+        <v>353.99869999999999</v>
       </c>
     </row>
     <row r="199">
@@ -9052,19 +9052,19 @@
         <v>29</v>
       </c>
       <c r="F199" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G199" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H199" s="0" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="J199" s="0">
-        <v>403.95710000000003</v>
+        <v>282.62110000000001</v>
       </c>
     </row>
     <row r="200">
@@ -9084,19 +9084,19 @@
         <v>29</v>
       </c>
       <c r="F200" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G200" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H200" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J200" s="0">
-        <v>353.99869999999999</v>
+        <v>251.0352</v>
       </c>
     </row>
     <row r="201">
@@ -9116,19 +9116,19 @@
         <v>29</v>
       </c>
       <c r="F201" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G201" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J201" s="0">
-        <v>282.62110000000001</v>
+        <v>226.5855</v>
       </c>
     </row>
     <row r="202">
@@ -9142,25 +9142,25 @@
         <v>7</v>
       </c>
       <c r="D202" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E202" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F202" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G202" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H202" s="0" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="J202" s="0">
-        <v>251.0352</v>
+        <v>3073.4854</v>
       </c>
     </row>
     <row r="203">
@@ -9174,25 +9174,25 @@
         <v>7</v>
       </c>
       <c r="D203" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E203" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F203" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G203" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H203" s="0" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="J203" s="0">
-        <v>226.5855</v>
+        <v>1817.3022000000001</v>
       </c>
     </row>
     <row r="204">
@@ -9209,7 +9209,7 @@
         <v>14</v>
       </c>
       <c r="E204" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F204" s="0" t="s">
         <v>31</v>
@@ -9218,13 +9218,13 @@
         <v>40</v>
       </c>
       <c r="H204" s="0" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J204" s="0">
-        <v>3073.4854</v>
+        <v>831.18269999999996</v>
       </c>
     </row>
     <row r="205">
@@ -9241,22 +9241,22 @@
         <v>14</v>
       </c>
       <c r="E205" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G205" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H205" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="J205" s="0">
-        <v>1817.3022000000001</v>
+        <v>444.28719999999999</v>
       </c>
     </row>
     <row r="206">
@@ -9273,22 +9273,22 @@
         <v>14</v>
       </c>
       <c r="E206" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F206" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G206" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H206" s="0" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J206" s="0">
-        <v>831.18269999999996</v>
+        <v>406.01569999999998</v>
       </c>
     </row>
     <row r="207">
@@ -9308,19 +9308,19 @@
         <v>29</v>
       </c>
       <c r="F207" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G207" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H207" s="0" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="J207" s="0">
-        <v>444.28719999999999</v>
+        <v>377.0512</v>
       </c>
     </row>
     <row r="208">
@@ -9340,19 +9340,19 @@
         <v>29</v>
       </c>
       <c r="F208" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G208" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H208" s="0" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="J208" s="0">
-        <v>406.01569999999998</v>
+        <v>370.54059999999998</v>
       </c>
     </row>
     <row r="209">
@@ -9372,19 +9372,19 @@
         <v>29</v>
       </c>
       <c r="F209" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G209" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H209" s="0" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="J209" s="0">
-        <v>377.0512</v>
+        <v>364.45699999999999</v>
       </c>
     </row>
     <row r="210">
@@ -9404,19 +9404,19 @@
         <v>29</v>
       </c>
       <c r="F210" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G210" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="J210" s="0">
-        <v>370.54059999999998</v>
+        <v>357.5231</v>
       </c>
     </row>
     <row r="211">
@@ -9436,19 +9436,19 @@
         <v>29</v>
       </c>
       <c r="F211" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G211" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H211" s="0" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J211" s="0">
-        <v>364.45699999999999</v>
+        <v>289.80360000000002</v>
       </c>
     </row>
     <row r="212">
@@ -9468,19 +9468,19 @@
         <v>29</v>
       </c>
       <c r="F212" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G212" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H212" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="J212" s="0">
-        <v>357.5231</v>
+        <v>205.23990000000001</v>
       </c>
     </row>
     <row r="213">
@@ -9494,25 +9494,25 @@
         <v>7</v>
       </c>
       <c r="D213" s="0" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E213" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F213" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G213" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="J213" s="0">
-        <v>289.80360000000002</v>
+        <v>5904.6377000000002</v>
       </c>
     </row>
     <row r="214">
@@ -9526,25 +9526,25 @@
         <v>7</v>
       </c>
       <c r="D214" s="0" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E214" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F214" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G214" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J214" s="0">
-        <v>205.23990000000001</v>
+        <v>4907.7012000000004</v>
       </c>
     </row>
     <row r="215">
@@ -9561,7 +9561,7 @@
         <v>23</v>
       </c>
       <c r="E215" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F215" s="0" t="s">
         <v>31</v>
@@ -9570,13 +9570,13 @@
         <v>40</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="J215" s="0">
-        <v>5904.6377000000002</v>
+        <v>202.81960000000001</v>
       </c>
     </row>
     <row r="216">
@@ -9593,22 +9593,22 @@
         <v>23</v>
       </c>
       <c r="E216" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F216" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G216" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="J216" s="0">
-        <v>4907.7012000000004</v>
+        <v>383.23849999999999</v>
       </c>
     </row>
     <row r="217">
@@ -9625,22 +9625,22 @@
         <v>23</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F217" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G217" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="J217" s="0">
-        <v>202.81960000000001</v>
+        <v>363.8911</v>
       </c>
     </row>
     <row r="218">
@@ -9660,19 +9660,19 @@
         <v>29</v>
       </c>
       <c r="F218" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G218" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H218" s="0" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="J218" s="0">
-        <v>383.23849999999999</v>
+        <v>355.88670000000002</v>
       </c>
     </row>
     <row r="219">
@@ -9692,19 +9692,19 @@
         <v>29</v>
       </c>
       <c r="F219" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G219" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H219" s="0" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="J219" s="0">
-        <v>363.8911</v>
+        <v>351.3347</v>
       </c>
     </row>
     <row r="220">
@@ -9724,19 +9724,19 @@
         <v>29</v>
       </c>
       <c r="F220" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G220" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J220" s="0">
-        <v>355.88670000000002</v>
+        <v>333.8578</v>
       </c>
     </row>
     <row r="221">
@@ -9756,19 +9756,19 @@
         <v>29</v>
       </c>
       <c r="F221" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G221" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="J221" s="0">
-        <v>351.3347</v>
+        <v>313.44380000000001</v>
       </c>
     </row>
     <row r="222">
@@ -9788,19 +9788,19 @@
         <v>29</v>
       </c>
       <c r="F222" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G222" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="J222" s="0">
-        <v>333.8578</v>
+        <v>238.27189999999999</v>
       </c>
     </row>
     <row r="223">
@@ -9820,19 +9820,19 @@
         <v>29</v>
       </c>
       <c r="F223" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G223" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H223" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="J223" s="0">
-        <v>313.44380000000001</v>
+        <v>141.53020000000001</v>
       </c>
     </row>
     <row r="224">
@@ -9846,25 +9846,25 @@
         <v>7</v>
       </c>
       <c r="D224" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E224" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F224" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G224" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H224" s="0" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="J224" s="0">
-        <v>238.27189999999999</v>
+        <v>6671.5464000000002</v>
       </c>
     </row>
     <row r="225">
@@ -9878,25 +9878,25 @@
         <v>7</v>
       </c>
       <c r="D225" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E225" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F225" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G225" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H225" s="0" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="J225" s="0">
-        <v>141.53020000000001</v>
+        <v>2604.8850000000002</v>
       </c>
     </row>
     <row r="226">
@@ -9913,7 +9913,7 @@
         <v>24</v>
       </c>
       <c r="E226" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F226" s="0" t="s">
         <v>31</v>
@@ -9922,13 +9922,13 @@
         <v>40</v>
       </c>
       <c r="H226" s="0" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="J226" s="0">
-        <v>6671.5464000000002</v>
+        <v>539.66269999999997</v>
       </c>
     </row>
     <row r="227">
@@ -9945,22 +9945,22 @@
         <v>24</v>
       </c>
       <c r="E227" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F227" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G227" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H227" s="0" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="J227" s="0">
-        <v>2604.8850000000002</v>
+        <v>429.82010000000002</v>
       </c>
     </row>
     <row r="228">
@@ -9977,22 +9977,22 @@
         <v>24</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F228" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G228" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H228" s="0" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="J228" s="0">
-        <v>539.66269999999997</v>
+        <v>421.38249999999999</v>
       </c>
     </row>
     <row r="229">
@@ -10012,19 +10012,19 @@
         <v>29</v>
       </c>
       <c r="F229" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G229" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H229" s="0" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="J229" s="0">
-        <v>429.82010000000002</v>
+        <v>417.74880000000002</v>
       </c>
     </row>
     <row r="230">
@@ -10044,19 +10044,19 @@
         <v>29</v>
       </c>
       <c r="F230" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G230" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H230" s="0" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="J230" s="0">
-        <v>421.38249999999999</v>
+        <v>393.11059999999998</v>
       </c>
     </row>
     <row r="231">
@@ -10076,19 +10076,19 @@
         <v>29</v>
       </c>
       <c r="F231" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G231" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H231" s="0" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="J231" s="0">
-        <v>417.74880000000002</v>
+        <v>392.10489999999999</v>
       </c>
     </row>
     <row r="232">
@@ -10108,19 +10108,19 @@
         <v>29</v>
       </c>
       <c r="F232" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G232" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H232" s="0" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="J232" s="0">
-        <v>393.11059999999998</v>
+        <v>387.5043</v>
       </c>
     </row>
     <row r="233">
@@ -10140,19 +10140,19 @@
         <v>29</v>
       </c>
       <c r="F233" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G233" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H233" s="0" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="J233" s="0">
-        <v>392.10489999999999</v>
+        <v>215.23259999999999</v>
       </c>
     </row>
     <row r="234">
@@ -10163,28 +10163,28 @@
         <v>4</v>
       </c>
       <c r="C234" s="0" t="s">
-        <v>7</v>
+        <v>655</v>
       </c>
       <c r="D234" s="0" t="s">
-        <v>24</v>
+        <v>801</v>
       </c>
       <c r="E234" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F234" s="0" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G234" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H234" s="0" t="s">
-        <v>255</v>
+        <v>693</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>556</v>
+        <v>804</v>
       </c>
       <c r="J234" s="0">
-        <v>387.5043</v>
+        <v>6179.7012000000004</v>
       </c>
     </row>
     <row r="235">
@@ -10195,28 +10195,28 @@
         <v>4</v>
       </c>
       <c r="C235" s="0" t="s">
-        <v>7</v>
+        <v>655</v>
       </c>
       <c r="D235" s="0" t="s">
-        <v>24</v>
+        <v>801</v>
       </c>
       <c r="E235" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F235" s="0" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G235" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H235" s="0" t="s">
-        <v>256</v>
+        <v>694</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>557</v>
+        <v>805</v>
       </c>
       <c r="J235" s="0">
-        <v>215.23259999999999</v>
+        <v>2590.0304999999999</v>
       </c>
     </row>
     <row r="236">
@@ -10233,7 +10233,7 @@
         <v>801</v>
       </c>
       <c r="E236" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F236" s="0" t="s">
         <v>31</v>
@@ -10242,13 +10242,13 @@
         <v>40</v>
       </c>
       <c r="H236" s="0" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="J236" s="0">
-        <v>6179.7012000000004</v>
+        <v>1052.7577000000001</v>
       </c>
     </row>
     <row r="237">
@@ -10265,7 +10265,7 @@
         <v>801</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F237" s="0" t="s">
         <v>32</v>
@@ -10274,13 +10274,13 @@
         <v>41</v>
       </c>
       <c r="H237" s="0" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="J237" s="0">
-        <v>2590.0304999999999</v>
+        <v>663.33749999999998</v>
       </c>
     </row>
     <row r="238">
@@ -10297,7 +10297,7 @@
         <v>801</v>
       </c>
       <c r="E238" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F238" s="0" t="s">
         <v>31</v>
@@ -10306,13 +10306,13 @@
         <v>40</v>
       </c>
       <c r="H238" s="0" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="J238" s="0">
-        <v>1052.7577000000001</v>
+        <v>506.81569999999999</v>
       </c>
     </row>
     <row r="239">
@@ -10329,22 +10329,22 @@
         <v>801</v>
       </c>
       <c r="E239" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F239" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G239" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H239" s="0" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="J239" s="0">
-        <v>663.33749999999998</v>
+        <v>408.8279</v>
       </c>
     </row>
     <row r="240">
@@ -10364,19 +10364,19 @@
         <v>29</v>
       </c>
       <c r="F240" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G240" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H240" s="0" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="J240" s="0">
-        <v>506.81569999999999</v>
+        <v>402.4606</v>
       </c>
     </row>
     <row r="241">
@@ -10396,19 +10396,19 @@
         <v>29</v>
       </c>
       <c r="F241" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G241" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H241" s="0" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="J241" s="0">
-        <v>408.8279</v>
+        <v>395.95499999999999</v>
       </c>
     </row>
     <row r="242">
@@ -10428,19 +10428,19 @@
         <v>29</v>
       </c>
       <c r="F242" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G242" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H242" s="0" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="J242" s="0">
-        <v>402.4606</v>
+        <v>384.18630000000002</v>
       </c>
     </row>
     <row r="243">
@@ -10460,19 +10460,19 @@
         <v>29</v>
       </c>
       <c r="F243" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G243" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H243" s="0" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="J243" s="0">
-        <v>395.95499999999999</v>
+        <v>337.53550000000001</v>
       </c>
     </row>
     <row r="244">
@@ -10492,19 +10492,19 @@
         <v>29</v>
       </c>
       <c r="F244" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G244" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H244" s="0" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="J244" s="0">
-        <v>384.18630000000002</v>
+        <v>304.91230000000002</v>
       </c>
     </row>
     <row r="245">
@@ -10524,19 +10524,19 @@
         <v>29</v>
       </c>
       <c r="F245" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G245" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H245" s="0" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="J245" s="0">
-        <v>337.53550000000001</v>
+        <v>125.54000000000001</v>
       </c>
     </row>
     <row r="246">
@@ -10550,25 +10550,25 @@
         <v>655</v>
       </c>
       <c r="D246" s="0" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E246" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F246" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G246" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H246" s="0" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="J246" s="0">
-        <v>304.91230000000002</v>
+        <v>5385.1138000000001</v>
       </c>
     </row>
     <row r="247">
@@ -10582,25 +10582,25 @@
         <v>655</v>
       </c>
       <c r="D247" s="0" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E247" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F247" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G247" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H247" s="0" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="J247" s="0">
-        <v>125.54000000000001</v>
+        <v>2843.9126000000001</v>
       </c>
     </row>
     <row r="248">
@@ -10617,7 +10617,7 @@
         <v>802</v>
       </c>
       <c r="E248" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F248" s="0" t="s">
         <v>31</v>
@@ -10626,13 +10626,13 @@
         <v>40</v>
       </c>
       <c r="H248" s="0" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="J248" s="0">
-        <v>5385.1138000000001</v>
+        <v>710.74549999999999</v>
       </c>
     </row>
     <row r="249">
@@ -10649,7 +10649,7 @@
         <v>802</v>
       </c>
       <c r="E249" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F249" s="0" t="s">
         <v>32</v>
@@ -10658,13 +10658,13 @@
         <v>41</v>
       </c>
       <c r="H249" s="0" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="J249" s="0">
-        <v>2843.9126000000001</v>
+        <v>550.2423</v>
       </c>
     </row>
     <row r="250">
@@ -10681,7 +10681,7 @@
         <v>802</v>
       </c>
       <c r="E250" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F250" s="0" t="s">
         <v>31</v>
@@ -10690,13 +10690,13 @@
         <v>40</v>
       </c>
       <c r="H250" s="0" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="J250" s="0">
-        <v>710.74549999999999</v>
+        <v>438.92590000000001</v>
       </c>
     </row>
     <row r="251">
@@ -10713,22 +10713,22 @@
         <v>802</v>
       </c>
       <c r="E251" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F251" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G251" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H251" s="0" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="J251" s="0">
-        <v>550.2423</v>
+        <v>423.42290000000003</v>
       </c>
     </row>
     <row r="252">
@@ -10748,19 +10748,19 @@
         <v>29</v>
       </c>
       <c r="F252" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G252" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H252" s="0" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="J252" s="0">
-        <v>438.92590000000001</v>
+        <v>403.89089999999999</v>
       </c>
     </row>
     <row r="253">
@@ -10780,19 +10780,19 @@
         <v>29</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G253" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H253" s="0" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="J253" s="0">
-        <v>423.42290000000003</v>
+        <v>391.21699999999999</v>
       </c>
     </row>
     <row r="254">
@@ -10812,19 +10812,19 @@
         <v>29</v>
       </c>
       <c r="F254" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G254" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H254" s="0" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="J254" s="0">
-        <v>403.89089999999999</v>
+        <v>383.9436</v>
       </c>
     </row>
     <row r="255">
@@ -10844,19 +10844,19 @@
         <v>29</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G255" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H255" s="0" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="J255" s="0">
-        <v>391.21699999999999</v>
+        <v>312.447</v>
       </c>
     </row>
     <row r="256">
@@ -10876,19 +10876,19 @@
         <v>29</v>
       </c>
       <c r="F256" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G256" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H256" s="0" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="J256" s="0">
-        <v>383.9436</v>
+        <v>309.3852</v>
       </c>
     </row>
     <row r="257">
@@ -10908,19 +10908,19 @@
         <v>29</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G257" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H257" s="0" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="J257" s="0">
-        <v>312.447</v>
+        <v>235.6891</v>
       </c>
     </row>
     <row r="258">
@@ -10934,25 +10934,25 @@
         <v>655</v>
       </c>
       <c r="D258" s="0" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E258" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G258" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H258" s="0" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="J258" s="0">
-        <v>309.3852</v>
+        <v>6293.9867999999997</v>
       </c>
     </row>
     <row r="259">
@@ -10966,25 +10966,25 @@
         <v>655</v>
       </c>
       <c r="D259" s="0" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E259" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F259" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G259" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H259" s="0" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J259" s="0">
-        <v>235.6891</v>
+        <v>5358.5902999999999</v>
       </c>
     </row>
     <row r="260">
@@ -11001,7 +11001,7 @@
         <v>803</v>
       </c>
       <c r="E260" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F260" s="0" t="s">
         <v>31</v>
@@ -11010,13 +11010,13 @@
         <v>40</v>
       </c>
       <c r="H260" s="0" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="J260" s="0">
-        <v>6293.9867999999997</v>
+        <v>577.04179999999997</v>
       </c>
     </row>
     <row r="261">
@@ -11033,7 +11033,7 @@
         <v>803</v>
       </c>
       <c r="E261" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F261" s="0" t="s">
         <v>32</v>
@@ -11042,13 +11042,13 @@
         <v>41</v>
       </c>
       <c r="H261" s="0" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="J261" s="0">
-        <v>5358.5902999999999</v>
+        <v>518.29719999999998</v>
       </c>
     </row>
     <row r="262">
@@ -11065,7 +11065,7 @@
         <v>803</v>
       </c>
       <c r="E262" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F262" s="0" t="s">
         <v>31</v>
@@ -11074,13 +11074,13 @@
         <v>40</v>
       </c>
       <c r="H262" s="0" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="J262" s="0">
-        <v>577.04179999999997</v>
+        <v>427.73379999999997</v>
       </c>
     </row>
     <row r="263">
@@ -11097,22 +11097,22 @@
         <v>803</v>
       </c>
       <c r="E263" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F263" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G263" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H263" s="0" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="J263" s="0">
-        <v>518.29719999999998</v>
+        <v>404.26459999999997</v>
       </c>
     </row>
     <row r="264">
@@ -11132,19 +11132,19 @@
         <v>29</v>
       </c>
       <c r="F264" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G264" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H264" s="0" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="J264" s="0">
-        <v>427.73379999999997</v>
+        <v>398.51589999999999</v>
       </c>
     </row>
     <row r="265">
@@ -11164,19 +11164,19 @@
         <v>29</v>
       </c>
       <c r="F265" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G265" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H265" s="0" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="J265" s="0">
-        <v>404.26459999999997</v>
+        <v>392.9486</v>
       </c>
     </row>
     <row r="266">
@@ -11196,19 +11196,19 @@
         <v>29</v>
       </c>
       <c r="F266" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G266" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H266" s="0" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J266" s="0">
-        <v>398.51589999999999</v>
+        <v>382.86340000000001</v>
       </c>
     </row>
     <row r="267">
@@ -11228,19 +11228,19 @@
         <v>29</v>
       </c>
       <c r="F267" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G267" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H267" s="0" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="J267" s="0">
-        <v>392.9486</v>
+        <v>368.97640000000001</v>
       </c>
     </row>
     <row r="268">
@@ -11260,19 +11260,19 @@
         <v>29</v>
       </c>
       <c r="F268" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G268" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H268" s="0" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="J268" s="0">
-        <v>382.86340000000001</v>
+        <v>347.17689999999999</v>
       </c>
     </row>
     <row r="269">
@@ -11292,19 +11292,19 @@
         <v>29</v>
       </c>
       <c r="F269" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G269" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H269" s="0" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="J269" s="0">
-        <v>368.97640000000001</v>
+        <v>328.54599999999999</v>
       </c>
     </row>
     <row r="270">
@@ -11315,28 +11315,28 @@
         <v>4</v>
       </c>
       <c r="C270" s="0" t="s">
-        <v>655</v>
+        <v>8</v>
       </c>
       <c r="D270" s="0" t="s">
-        <v>803</v>
+        <v>15</v>
       </c>
       <c r="E270" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F270" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G270" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H270" s="0" t="s">
-        <v>727</v>
+        <v>257</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>838</v>
+        <v>558</v>
       </c>
       <c r="J270" s="0">
-        <v>347.17689999999999</v>
+        <v>5568.125</v>
       </c>
     </row>
     <row r="271">
@@ -11347,28 +11347,28 @@
         <v>4</v>
       </c>
       <c r="C271" s="0" t="s">
-        <v>655</v>
+        <v>8</v>
       </c>
       <c r="D271" s="0" t="s">
-        <v>803</v>
+        <v>15</v>
       </c>
       <c r="E271" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F271" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G271" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H271" s="0" t="s">
-        <v>728</v>
+        <v>258</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>839</v>
+        <v>559</v>
       </c>
       <c r="J271" s="0">
-        <v>328.54599999999999</v>
+        <v>2316.6012999999998</v>
       </c>
     </row>
     <row r="272">
@@ -11385,7 +11385,7 @@
         <v>15</v>
       </c>
       <c r="E272" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F272" s="0" t="s">
         <v>31</v>
@@ -11394,13 +11394,13 @@
         <v>40</v>
       </c>
       <c r="H272" s="0" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="J272" s="0">
-        <v>5568.125</v>
+        <v>504.78460000000001</v>
       </c>
     </row>
     <row r="273">
@@ -11417,7 +11417,7 @@
         <v>15</v>
       </c>
       <c r="E273" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F273" s="0" t="s">
         <v>32</v>
@@ -11426,13 +11426,13 @@
         <v>41</v>
       </c>
       <c r="H273" s="0" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="J273" s="0">
-        <v>2316.6012999999998</v>
+        <v>445.50999999999999</v>
       </c>
     </row>
     <row r="274">
@@ -11449,7 +11449,7 @@
         <v>15</v>
       </c>
       <c r="E274" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F274" s="0" t="s">
         <v>31</v>
@@ -11458,13 +11458,13 @@
         <v>40</v>
       </c>
       <c r="H274" s="0" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="J274" s="0">
-        <v>504.78460000000001</v>
+        <v>401.56920000000002</v>
       </c>
     </row>
     <row r="275">
@@ -11481,22 +11481,22 @@
         <v>15</v>
       </c>
       <c r="E275" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F275" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G275" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H275" s="0" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="J275" s="0">
-        <v>445.50999999999999</v>
+        <v>392.42399999999998</v>
       </c>
     </row>
     <row r="276">
@@ -11516,19 +11516,19 @@
         <v>29</v>
       </c>
       <c r="F276" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G276" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H276" s="0" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="J276" s="0">
-        <v>401.56920000000002</v>
+        <v>368.18880000000001</v>
       </c>
     </row>
     <row r="277">
@@ -11548,19 +11548,19 @@
         <v>29</v>
       </c>
       <c r="F277" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G277" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H277" s="0" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="J277" s="0">
-        <v>392.42399999999998</v>
+        <v>366.78320000000002</v>
       </c>
     </row>
     <row r="278">
@@ -11580,19 +11580,19 @@
         <v>29</v>
       </c>
       <c r="F278" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G278" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H278" s="0" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="J278" s="0">
-        <v>368.18880000000001</v>
+        <v>361.8997</v>
       </c>
     </row>
     <row r="279">
@@ -11612,19 +11612,19 @@
         <v>29</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G279" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H279" s="0" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="J279" s="0">
-        <v>366.78320000000002</v>
+        <v>322.42989999999998</v>
       </c>
     </row>
     <row r="280">
@@ -11644,19 +11644,19 @@
         <v>29</v>
       </c>
       <c r="F280" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G280" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H280" s="0" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="J280" s="0">
-        <v>361.8997</v>
+        <v>308.6019</v>
       </c>
     </row>
     <row r="281">
@@ -11676,19 +11676,19 @@
         <v>29</v>
       </c>
       <c r="F281" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G281" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="J281" s="0">
-        <v>322.42989999999998</v>
+        <v>260.48289999999997</v>
       </c>
     </row>
     <row r="282">
@@ -11702,25 +11702,25 @@
         <v>8</v>
       </c>
       <c r="D282" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E282" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F282" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G282" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H282" s="0" t="s">
-        <v>267</v>
+        <v>103</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="J282" s="0">
-        <v>308.6019</v>
+        <v>6411.3008</v>
       </c>
     </row>
     <row r="283">
@@ -11734,25 +11734,25 @@
         <v>8</v>
       </c>
       <c r="D283" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E283" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F283" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G283" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H283" s="0" t="s">
-        <v>268</v>
+        <v>104</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="J283" s="0">
-        <v>260.48289999999997</v>
+        <v>5363.7114000000001</v>
       </c>
     </row>
     <row r="284">
@@ -11769,7 +11769,7 @@
         <v>16</v>
       </c>
       <c r="E284" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F284" s="0" t="s">
         <v>31</v>
@@ -11778,13 +11778,13 @@
         <v>40</v>
       </c>
       <c r="H284" s="0" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="J284" s="0">
-        <v>6411.3008</v>
+        <v>465.0847</v>
       </c>
     </row>
     <row r="285">
@@ -11801,22 +11801,22 @@
         <v>16</v>
       </c>
       <c r="E285" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F285" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G285" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H285" s="0" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="J285" s="0">
-        <v>5363.7114000000001</v>
+        <v>432.71969999999999</v>
       </c>
     </row>
     <row r="286">
@@ -11836,19 +11836,19 @@
         <v>29</v>
       </c>
       <c r="F286" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G286" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H286" s="0" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="J286" s="0">
-        <v>465.0847</v>
+        <v>403.6884</v>
       </c>
     </row>
     <row r="287">
@@ -11868,19 +11868,19 @@
         <v>29</v>
       </c>
       <c r="F287" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G287" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H287" s="0" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="J287" s="0">
-        <v>432.71969999999999</v>
+        <v>393.85660000000001</v>
       </c>
     </row>
     <row r="288">
@@ -11900,19 +11900,19 @@
         <v>29</v>
       </c>
       <c r="F288" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G288" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H288" s="0" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="J288" s="0">
-        <v>403.6884</v>
+        <v>328.83640000000003</v>
       </c>
     </row>
     <row r="289">
@@ -11932,19 +11932,19 @@
         <v>29</v>
       </c>
       <c r="F289" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G289" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H289" s="0" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="J289" s="0">
-        <v>393.85660000000001</v>
+        <v>289.99919999999997</v>
       </c>
     </row>
     <row r="290">
@@ -11964,19 +11964,19 @@
         <v>29</v>
       </c>
       <c r="F290" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G290" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H290" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="J290" s="0">
-        <v>328.83640000000003</v>
+        <v>253.50819999999999</v>
       </c>
     </row>
     <row r="291">
@@ -11996,19 +11996,19 @@
         <v>29</v>
       </c>
       <c r="F291" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G291" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H291" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="J291" s="0">
-        <v>289.99919999999997</v>
+        <v>156.39179999999999</v>
       </c>
     </row>
     <row r="292">
@@ -12022,25 +12022,25 @@
         <v>8</v>
       </c>
       <c r="D292" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E292" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F292" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G292" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H292" s="0" t="s">
-        <v>113</v>
+        <v>269</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="J292" s="0">
-        <v>253.50819999999999</v>
+        <v>5610.5132000000003</v>
       </c>
     </row>
     <row r="293">
@@ -12054,25 +12054,25 @@
         <v>8</v>
       </c>
       <c r="D293" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E293" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F293" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G293" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H293" s="0" t="s">
-        <v>114</v>
+        <v>270</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="J293" s="0">
-        <v>156.39179999999999</v>
+        <v>2526.6718999999998</v>
       </c>
     </row>
     <row r="294">
@@ -12089,7 +12089,7 @@
         <v>17</v>
       </c>
       <c r="E294" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F294" s="0" t="s">
         <v>31</v>
@@ -12098,13 +12098,13 @@
         <v>40</v>
       </c>
       <c r="H294" s="0" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="J294" s="0">
-        <v>5610.5132000000003</v>
+        <v>663.2672</v>
       </c>
     </row>
     <row r="295">
@@ -12121,7 +12121,7 @@
         <v>17</v>
       </c>
       <c r="E295" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F295" s="0" t="s">
         <v>32</v>
@@ -12130,13 +12130,13 @@
         <v>41</v>
       </c>
       <c r="H295" s="0" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="J295" s="0">
-        <v>2526.6718999999998</v>
+        <v>553.69179999999994</v>
       </c>
     </row>
     <row r="296">
@@ -12153,7 +12153,7 @@
         <v>17</v>
       </c>
       <c r="E296" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F296" s="0" t="s">
         <v>31</v>
@@ -12162,13 +12162,13 @@
         <v>40</v>
       </c>
       <c r="H296" s="0" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="J296" s="0">
-        <v>663.2672</v>
+        <v>436.38159999999999</v>
       </c>
     </row>
     <row r="297">
@@ -12185,22 +12185,22 @@
         <v>17</v>
       </c>
       <c r="E297" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F297" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G297" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H297" s="0" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="J297" s="0">
-        <v>553.69179999999994</v>
+        <v>411.78269999999998</v>
       </c>
     </row>
     <row r="298">
@@ -12220,19 +12220,19 @@
         <v>29</v>
       </c>
       <c r="F298" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G298" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H298" s="0" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="J298" s="0">
-        <v>436.38159999999999</v>
+        <v>407.44670000000002</v>
       </c>
     </row>
     <row r="299">
@@ -12252,19 +12252,19 @@
         <v>29</v>
       </c>
       <c r="F299" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G299" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H299" s="0" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="J299" s="0">
-        <v>411.78269999999998</v>
+        <v>390.17970000000003</v>
       </c>
     </row>
     <row r="300">
@@ -12284,19 +12284,19 @@
         <v>29</v>
       </c>
       <c r="F300" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G300" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H300" s="0" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="J300" s="0">
-        <v>407.44670000000002</v>
+        <v>379.34300000000002</v>
       </c>
     </row>
     <row r="301">
@@ -12316,19 +12316,19 @@
         <v>29</v>
       </c>
       <c r="F301" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G301" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H301" s="0" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="J301" s="0">
-        <v>390.17970000000003</v>
+        <v>378.32549999999998</v>
       </c>
     </row>
     <row r="302">
@@ -12348,19 +12348,19 @@
         <v>29</v>
       </c>
       <c r="F302" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G302" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H302" s="0" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="J302" s="0">
-        <v>379.34300000000002</v>
+        <v>248.1077</v>
       </c>
     </row>
     <row r="303">
@@ -12380,19 +12380,19 @@
         <v>29</v>
       </c>
       <c r="F303" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G303" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H303" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="J303" s="0">
-        <v>378.32549999999998</v>
+        <v>155.72280000000001</v>
       </c>
     </row>
     <row r="304">
@@ -12406,25 +12406,25 @@
         <v>8</v>
       </c>
       <c r="D304" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E304" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F304" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G304" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H304" s="0" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="J304" s="0">
-        <v>248.1077</v>
+        <v>6378.5679</v>
       </c>
     </row>
     <row r="305">
@@ -12438,25 +12438,25 @@
         <v>8</v>
       </c>
       <c r="D305" s="0" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E305" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F305" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G305" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H305" s="0" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="J305" s="0">
-        <v>155.72280000000001</v>
+        <v>3677.8054000000002</v>
       </c>
     </row>
     <row r="306">
@@ -12473,7 +12473,7 @@
         <v>25</v>
       </c>
       <c r="E306" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F306" s="0" t="s">
         <v>31</v>
@@ -12482,13 +12482,13 @@
         <v>40</v>
       </c>
       <c r="H306" s="0" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="J306" s="0">
-        <v>6378.5679</v>
+        <v>990.75639999999999</v>
       </c>
     </row>
     <row r="307">
@@ -12505,7 +12505,7 @@
         <v>25</v>
       </c>
       <c r="E307" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F307" s="0" t="s">
         <v>32</v>
@@ -12514,13 +12514,13 @@
         <v>41</v>
       </c>
       <c r="H307" s="0" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="J307" s="0">
-        <v>3677.8054000000002</v>
+        <v>912.61609999999996</v>
       </c>
     </row>
     <row r="308">
@@ -12537,7 +12537,7 @@
         <v>25</v>
       </c>
       <c r="E308" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F308" s="0" t="s">
         <v>31</v>
@@ -12546,13 +12546,13 @@
         <v>40</v>
       </c>
       <c r="H308" s="0" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="J308" s="0">
-        <v>990.75639999999999</v>
+        <v>448.30200000000002</v>
       </c>
     </row>
     <row r="309">
@@ -12569,22 +12569,22 @@
         <v>25</v>
       </c>
       <c r="E309" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F309" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G309" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H309" s="0" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="J309" s="0">
-        <v>912.61609999999996</v>
+        <v>415.84109999999998</v>
       </c>
     </row>
     <row r="310">
@@ -12604,19 +12604,19 @@
         <v>29</v>
       </c>
       <c r="F310" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G310" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H310" s="0" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="J310" s="0">
-        <v>448.30200000000002</v>
+        <v>380.94420000000002</v>
       </c>
     </row>
     <row r="311">
@@ -12636,19 +12636,19 @@
         <v>29</v>
       </c>
       <c r="F311" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G311" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H311" s="0" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="J311" s="0">
-        <v>415.84109999999998</v>
+        <v>359.60860000000002</v>
       </c>
     </row>
     <row r="312">
@@ -12668,19 +12668,19 @@
         <v>29</v>
       </c>
       <c r="F312" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G312" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H312" s="0" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="J312" s="0">
-        <v>380.94420000000002</v>
+        <v>338.8168</v>
       </c>
     </row>
     <row r="313">
@@ -12700,19 +12700,19 @@
         <v>29</v>
       </c>
       <c r="F313" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G313" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H313" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="J313" s="0">
-        <v>359.60860000000002</v>
+        <v>320.63470000000001</v>
       </c>
     </row>
     <row r="314">
@@ -12732,19 +12732,19 @@
         <v>29</v>
       </c>
       <c r="F314" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G314" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H314" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="J314" s="0">
-        <v>338.8168</v>
+        <v>287.04489999999999</v>
       </c>
     </row>
     <row r="315">
@@ -12764,19 +12764,19 @@
         <v>29</v>
       </c>
       <c r="F315" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G315" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H315" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="J315" s="0">
-        <v>320.63470000000001</v>
+        <v>107.8788</v>
       </c>
     </row>
     <row r="316">
@@ -12787,28 +12787,28 @@
         <v>4</v>
       </c>
       <c r="C316" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D316" s="0" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E316" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F316" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G316" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H316" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="J316" s="0">
-        <v>287.04489999999999</v>
+        <v>5099.2568000000001</v>
       </c>
     </row>
     <row r="317">
@@ -12819,28 +12819,28 @@
         <v>4</v>
       </c>
       <c r="C317" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D317" s="0" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E317" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F317" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G317" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H317" s="0" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="J317" s="0">
-        <v>107.8788</v>
+        <v>2383.1239999999998</v>
       </c>
     </row>
     <row r="318">
@@ -12857,7 +12857,7 @@
         <v>18</v>
       </c>
       <c r="E318" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F318" s="0" t="s">
         <v>31</v>
@@ -12866,13 +12866,13 @@
         <v>40</v>
       </c>
       <c r="H318" s="0" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="J318" s="0">
-        <v>5099.2568000000001</v>
+        <v>670.93709999999999</v>
       </c>
     </row>
     <row r="319">
@@ -12889,7 +12889,7 @@
         <v>18</v>
       </c>
       <c r="E319" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F319" s="0" t="s">
         <v>32</v>
@@ -12898,13 +12898,13 @@
         <v>41</v>
       </c>
       <c r="H319" s="0" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="J319" s="0">
-        <v>2383.1239999999998</v>
+        <v>459.24430000000001</v>
       </c>
     </row>
     <row r="320">
@@ -12921,7 +12921,7 @@
         <v>18</v>
       </c>
       <c r="E320" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F320" s="0" t="s">
         <v>31</v>
@@ -12930,13 +12930,13 @@
         <v>40</v>
       </c>
       <c r="H320" s="0" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="J320" s="0">
-        <v>670.93709999999999</v>
+        <v>415.84710000000001</v>
       </c>
     </row>
     <row r="321">
@@ -12953,22 +12953,22 @@
         <v>18</v>
       </c>
       <c r="E321" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F321" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G321" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H321" s="0" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="J321" s="0">
-        <v>459.24430000000001</v>
+        <v>404.09039999999999</v>
       </c>
     </row>
     <row r="322">
@@ -12988,19 +12988,19 @@
         <v>29</v>
       </c>
       <c r="F322" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G322" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H322" s="0" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="J322" s="0">
-        <v>415.84710000000001</v>
+        <v>370.1207</v>
       </c>
     </row>
     <row r="323">
@@ -13020,19 +13020,19 @@
         <v>29</v>
       </c>
       <c r="F323" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G323" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H323" s="0" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="J323" s="0">
-        <v>404.09039999999999</v>
+        <v>369.87549999999999</v>
       </c>
     </row>
     <row r="324">
@@ -13052,19 +13052,19 @@
         <v>29</v>
       </c>
       <c r="F324" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G324" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H324" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="J324" s="0">
-        <v>370.1207</v>
+        <v>332.15789999999998</v>
       </c>
     </row>
     <row r="325">
@@ -13084,19 +13084,19 @@
         <v>29</v>
       </c>
       <c r="F325" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G325" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H325" s="0" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="J325" s="0">
-        <v>369.87549999999999</v>
+        <v>310.02600000000001</v>
       </c>
     </row>
     <row r="326">
@@ -13116,19 +13116,19 @@
         <v>29</v>
       </c>
       <c r="F326" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G326" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H326" s="0" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="J326" s="0">
-        <v>332.15789999999998</v>
+        <v>137.19120000000001</v>
       </c>
     </row>
     <row r="327">
@@ -13142,25 +13142,25 @@
         <v>9</v>
       </c>
       <c r="D327" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E327" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F327" s="0" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G327" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H327" s="0" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="J327" s="0">
-        <v>310.02600000000001</v>
+        <v>6147.9931999999999</v>
       </c>
     </row>
     <row r="328">
@@ -13174,25 +13174,25 @@
         <v>9</v>
       </c>
       <c r="D328" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E328" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F328" s="0" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G328" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H328" s="0" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="J328" s="0">
-        <v>137.19120000000001</v>
+        <v>4509.7578000000003</v>
       </c>
     </row>
     <row r="329">
@@ -13209,7 +13209,7 @@
         <v>19</v>
       </c>
       <c r="E329" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F329" s="0" t="s">
         <v>31</v>
@@ -13218,13 +13218,13 @@
         <v>40</v>
       </c>
       <c r="H329" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="J329" s="0">
-        <v>6147.9931999999999</v>
+        <v>999.82090000000005</v>
       </c>
     </row>
     <row r="330">
@@ -13241,7 +13241,7 @@
         <v>19</v>
       </c>
       <c r="E330" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F330" s="0" t="s">
         <v>32</v>
@@ -13250,13 +13250,13 @@
         <v>41</v>
       </c>
       <c r="H330" s="0" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="J330" s="0">
-        <v>4509.7578000000003</v>
+        <v>829.32470000000001</v>
       </c>
     </row>
     <row r="331">
@@ -13273,7 +13273,7 @@
         <v>19</v>
       </c>
       <c r="E331" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F331" s="0" t="s">
         <v>31</v>
@@ -13282,13 +13282,13 @@
         <v>40</v>
       </c>
       <c r="H331" s="0" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="J331" s="0">
-        <v>999.82090000000005</v>
+        <v>460.868</v>
       </c>
     </row>
     <row r="332">
@@ -13305,22 +13305,22 @@
         <v>19</v>
       </c>
       <c r="E332" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F332" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G332" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H332" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="J332" s="0">
-        <v>829.32470000000001</v>
+        <v>418.91930000000002</v>
       </c>
     </row>
     <row r="333">
@@ -13340,19 +13340,19 @@
         <v>29</v>
       </c>
       <c r="F333" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G333" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H333" s="0" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="J333" s="0">
-        <v>460.868</v>
+        <v>377.29809999999998</v>
       </c>
     </row>
     <row r="334">
@@ -13372,19 +13372,19 @@
         <v>29</v>
       </c>
       <c r="F334" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G334" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H334" s="0" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="J334" s="0">
-        <v>418.91930000000002</v>
+        <v>376.07799999999998</v>
       </c>
     </row>
     <row r="335">
@@ -13404,19 +13404,19 @@
         <v>29</v>
       </c>
       <c r="F335" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G335" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H335" s="0" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="J335" s="0">
-        <v>377.29809999999998</v>
+        <v>345.4522</v>
       </c>
     </row>
     <row r="336">
@@ -13436,19 +13436,19 @@
         <v>29</v>
       </c>
       <c r="F336" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G336" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H336" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="J336" s="0">
-        <v>376.07799999999998</v>
+        <v>333.1805</v>
       </c>
     </row>
     <row r="337">
@@ -13468,19 +13468,19 @@
         <v>29</v>
       </c>
       <c r="F337" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G337" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H337" s="0" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="J337" s="0">
-        <v>345.4522</v>
+        <v>297.38940000000002</v>
       </c>
     </row>
     <row r="338">
@@ -13500,19 +13500,19 @@
         <v>29</v>
       </c>
       <c r="F338" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G338" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H338" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="J338" s="0">
-        <v>333.1805</v>
+        <v>196.88849999999999</v>
       </c>
     </row>
     <row r="339">
@@ -13526,25 +13526,25 @@
         <v>9</v>
       </c>
       <c r="D339" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E339" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F339" s="0" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G339" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H339" s="0" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="J339" s="0">
-        <v>297.38940000000002</v>
+        <v>5372.8154000000004</v>
       </c>
     </row>
     <row r="340">
@@ -13558,25 +13558,25 @@
         <v>9</v>
       </c>
       <c r="D340" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E340" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F340" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G340" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H340" s="0" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="J340" s="0">
-        <v>196.88849999999999</v>
+        <v>5089.0283</v>
       </c>
     </row>
     <row r="341">
@@ -13593,7 +13593,7 @@
         <v>20</v>
       </c>
       <c r="E341" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F341" s="0" t="s">
         <v>31</v>
@@ -13602,13 +13602,13 @@
         <v>40</v>
       </c>
       <c r="H341" s="0" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="J341" s="0">
-        <v>5372.8154000000004</v>
+        <v>414.66230000000002</v>
       </c>
     </row>
     <row r="342">
@@ -13625,22 +13625,22 @@
         <v>20</v>
       </c>
       <c r="E342" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F342" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G342" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H342" s="0" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="J342" s="0">
-        <v>5089.0283</v>
+        <v>403.9067</v>
       </c>
     </row>
     <row r="343">
@@ -13657,22 +13657,22 @@
         <v>20</v>
       </c>
       <c r="E343" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F343" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G343" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H343" s="0" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="J343" s="0">
-        <v>173.3056</v>
+        <v>374.75290000000001</v>
       </c>
     </row>
     <row r="344">
@@ -13692,19 +13692,19 @@
         <v>29</v>
       </c>
       <c r="F344" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G344" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H344" s="0" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="J344" s="0">
-        <v>414.66230000000002</v>
+        <v>372.04629999999997</v>
       </c>
     </row>
     <row r="345">
@@ -13724,19 +13724,19 @@
         <v>29</v>
       </c>
       <c r="F345" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G345" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H345" s="0" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="J345" s="0">
-        <v>403.9067</v>
+        <v>372.0009</v>
       </c>
     </row>
     <row r="346">
@@ -13756,19 +13756,19 @@
         <v>29</v>
       </c>
       <c r="F346" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G346" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H346" s="0" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="J346" s="0">
-        <v>374.75290000000001</v>
+        <v>318.33179999999999</v>
       </c>
     </row>
     <row r="347">
@@ -13788,19 +13788,19 @@
         <v>29</v>
       </c>
       <c r="F347" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G347" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H347" s="0" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="J347" s="0">
-        <v>372.04629999999997</v>
+        <v>295.59719999999999</v>
       </c>
     </row>
     <row r="348">
@@ -13820,19 +13820,19 @@
         <v>29</v>
       </c>
       <c r="F348" s="0" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G348" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H348" s="0" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="J348" s="0">
-        <v>372.0009</v>
+        <v>137.02930000000001</v>
       </c>
     </row>
     <row r="349">
@@ -13846,25 +13846,25 @@
         <v>9</v>
       </c>
       <c r="D349" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E349" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F349" s="0" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G349" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H349" s="0" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="J349" s="0">
-        <v>318.33179999999999</v>
+        <v>4746.6201000000001</v>
       </c>
     </row>
     <row r="350">
@@ -13878,25 +13878,25 @@
         <v>9</v>
       </c>
       <c r="D350" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E350" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F350" s="0" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G350" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H350" s="0" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="J350" s="0">
-        <v>295.59719999999999</v>
+        <v>4426.7367999999997</v>
       </c>
     </row>
     <row r="351">
@@ -13910,25 +13910,25 @@
         <v>9</v>
       </c>
       <c r="D351" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E351" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F351" s="0" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G351" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H351" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="J351" s="0">
-        <v>137.02930000000001</v>
+        <v>502.13749999999999</v>
       </c>
     </row>
     <row r="352">
@@ -13945,7 +13945,7 @@
         <v>21</v>
       </c>
       <c r="E352" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F352" s="0" t="s">
         <v>31</v>
@@ -13954,13 +13954,13 @@
         <v>40</v>
       </c>
       <c r="H352" s="0" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="J352" s="0">
-        <v>4746.6201000000001</v>
+        <v>439.52850000000001</v>
       </c>
     </row>
     <row r="353">
@@ -13977,22 +13977,22 @@
         <v>21</v>
       </c>
       <c r="E353" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F353" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G353" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H353" s="0" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="I353" s="0" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="J353" s="0">
-        <v>4426.7367999999997</v>
+        <v>423.6062</v>
       </c>
     </row>
     <row r="354">
@@ -14009,22 +14009,22 @@
         <v>21</v>
       </c>
       <c r="E354" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F354" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G354" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H354" s="0" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I354" s="0" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="J354" s="0">
-        <v>502.13749999999999</v>
+        <v>388.16570000000002</v>
       </c>
     </row>
     <row r="355">
@@ -14044,19 +14044,19 @@
         <v>29</v>
       </c>
       <c r="F355" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G355" s="0" t="s">
         <v>40</v>
       </c>
       <c r="H355" s="0" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="I355" s="0" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="J355" s="0">
-        <v>439.52850000000001</v>
+        <v>361.62639999999999</v>
       </c>
     </row>
     <row r="356">
@@ -14076,19 +14076,19 @@
         <v>29</v>
       </c>
       <c r="F356" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G356" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H356" s="0" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="I356" s="0" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="J356" s="0">
-        <v>423.6062</v>
+        <v>319.28989999999999</v>
       </c>
     </row>
     <row r="357">
@@ -14108,19 +14108,19 @@
         <v>29</v>
       </c>
       <c r="F357" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G357" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H357" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I357" s="0" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="J357" s="0">
-        <v>388.16570000000002</v>
+        <v>283.29320000000001</v>
       </c>
     </row>
     <row r="358">
@@ -14140,19 +14140,19 @@
         <v>29</v>
       </c>
       <c r="F358" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G358" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H358" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="I358" s="0" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="J358" s="0">
-        <v>361.62639999999999</v>
+        <v>254.66130000000001</v>
       </c>
     </row>
     <row r="359">
@@ -14172,19 +14172,19 @@
         <v>29</v>
       </c>
       <c r="F359" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G359" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H359" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I359" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="J359" s="0">
-        <v>319.28989999999999</v>
+        <v>283.29320000000001</v>
       </c>
     </row>
     <row r="360">
@@ -14204,19 +14204,19 @@
         <v>29</v>
       </c>
       <c r="F360" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G360" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H360" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I360" s="0" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="J360" s="0">
-        <v>283.29320000000001</v>
+        <v>254.66130000000001</v>
       </c>
     </row>
     <row r="361">

--- a/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2026_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="75308" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="78531" uniqueCount="875">
   <si>
     <t>Year</t>
   </si>
